--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Educacion\Desktop\constancia 22 junio impulso educativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E1CD7B-BB5E-481A-86B9-CA42BCBE9776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0083C2-CB24-4400-B622-62E1A8546059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="2850" windowWidth="16020" windowHeight="10095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="964">
   <si>
     <t>Nombre</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>SANCHEZ DENIZ MARIANA NAIR</t>
-  </si>
-  <si>
-    <t>30631696</t>
   </si>
   <si>
     <t>27196572</t>
@@ -3249,136 +3246,136 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="A2">
+        <v>30631696</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -3386,602 +3383,602 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -3989,84 +3986,84 @@
         <v>27043049</v>
       </c>
       <c r="B94" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" t="s">
         <v>6</v>
@@ -4074,127 +4071,127 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B113" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B114" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
@@ -4202,983 +4199,983 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B134" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B136" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B137" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B138" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B140" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B141" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B142" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B143" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B144" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B145" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B147" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B148" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B149" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B151" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B153" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B154" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B155" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B156" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B157" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B158" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B159" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B160" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B163" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B164" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B165" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B167" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B168" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B169" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B170" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B171" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B173" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B174" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B175" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B176" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B177" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B178" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B179" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B181" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B182" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B183" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B184" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B185" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B186" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B187" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B188" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B190" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B192" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B195" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B197" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B200" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B202" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B203" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B204" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B205" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B207" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B208" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B209" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B210" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B211" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B212" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B213" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B214" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B216" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B217" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B218" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B219" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B220" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B221" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B222" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B223" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B226" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B227" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B228" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B230" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B234" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B235" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B236" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B237" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B238" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B239" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B240" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B241" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B242" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B243" t="s">
         <v>6</v>
@@ -5186,1607 +5183,1607 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B244" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B246" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B247" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B248" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B249" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B250" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B251" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B252" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B253" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B254" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B255" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B256" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B257" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B258" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B259" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B260" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B261" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B262" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B263" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B264" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B265" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B266" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B267" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B268" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B269" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B270" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B271" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B272" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B273" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B274" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B275" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B276" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B277" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B278" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B279" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B280" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B281" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B282" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B283" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B284" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B285" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B286" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B287" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B288" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B289" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B290" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B291" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B292" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B293" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B294" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B295" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B296" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B297" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B298" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B299" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B300" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B301" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B302" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B303" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B305" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B306" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B307" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B308" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B309" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B310" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B311" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B312" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B313" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B314" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B315" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B316" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B317" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B318" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B319" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B320" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B321" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B322" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B323" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B324" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B325" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B326" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B327" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B328" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B329" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B330" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B331" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B332" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B333" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B334" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B335" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B336" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B337" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B338" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B339" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B340" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B341" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B342" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B343" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B344" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B345" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B346" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B347" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B348" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B349" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B350" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B351" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B352" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B353" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B354" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B355" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B356" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B357" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B358" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B359" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B360" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B361" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B362" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B363" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B364" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B365" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B366" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B367" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B368" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B369" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B370" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B371" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B372" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B373" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B374" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B375" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B376" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B377" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B378" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B379" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B380" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B381" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B382" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B383" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B384" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B385" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B386" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B387" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B388" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B389" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B390" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B391" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B392" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B393" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B394" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B395" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B396" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B397" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B398" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B399" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B400" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B401" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B402" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B403" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B404" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B405" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B406" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B407" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B408" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B409" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B410" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B411" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B412" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B413" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B414" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B415" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B416" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B417" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B418" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B419" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B420" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B421" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B422" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B423" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B424" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B425" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B426" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B427" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B428" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B429" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B430" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B431" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B432" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B433" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B434" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B435" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B436" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B437" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B438" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B439" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B440" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B441" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B442" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B443" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B444" t="s">
         <v>2</v>
@@ -6794,95 +6791,95 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B445" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B446" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B447" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B448" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B449" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B450" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B451" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B452" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B453" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B454" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B455" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B456" t="s">
         <v>5</v>
@@ -6890,394 +6887,394 @@
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B457" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B458" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B459" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B460" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B461" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B462" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B463" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B464" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B465" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B466" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B467" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B468" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B469" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B470" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B471" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B472" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B473" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B474" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B475" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B476" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B477" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B478" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B479" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B480" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B481" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B482" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B483" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B484" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B485" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B486" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B487" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B488" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B489" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B490" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B491" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B492" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B493" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B494" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B495" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B496" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B497" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B498" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B499" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B500" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B501" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B502" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B503" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B504" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B505" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
@@ -7285,7 +7282,7 @@
         <v>26287740</v>
       </c>
       <c r="B506" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Educacion\Desktop\constancia 22 junio impulso educativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0083C2-CB24-4400-B622-62E1A8546059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5073A2E-9EB5-4BAA-B141-B46F437A6FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="2850" windowWidth="16020" windowHeight="10095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2952,8 +2952,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3236,4056 +3237,4060 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B506"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>30631696</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="A94" s="1">
         <v>27043049</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="1" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="1" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="1" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="1" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="1" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="1" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="1" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="1" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="1" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="1" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="1" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="1" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="1" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="1" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="1" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="1" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="1" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="1" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="1" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="1" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="1" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="1" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="1" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="1" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="1" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="1" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="1" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="1" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="1" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="1" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="1" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="1" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="1" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="1" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="1" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="1" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="1" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="1" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="1" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="1" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="1" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="1" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="1" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="1" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="1" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="1" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="1" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="1" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="1" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="1" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="1" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="1" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="1" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="1" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="1" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="1" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="1" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="1" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="1" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="1" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="1" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="1" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="1" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="1" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="1" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="1" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="1" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="1" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="1" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="1" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="1" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="A202" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="1" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="A203" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="1" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="A204" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="1" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="A205" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="1" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="A206" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="1" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="A207" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="1" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="A208" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="1" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="A209" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="1" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="A210" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="1" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="A211" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="1" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="A212" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="1" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="A213" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="1" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="A214" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="1" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="A215" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="1" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="A216" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="1" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="A217" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="1" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="A218" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="1" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="A219" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="1" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="A220" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="1" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="A221" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="1" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="A222" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="1" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="A223" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="1" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="A224" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="1" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="A225" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="1" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="A226" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="1" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="A227" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="1" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="A228" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="1" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="A229" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="1" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+      <c r="A230" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="1" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="A231" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="1" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="A232" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="1" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="A233" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="1" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+      <c r="A234" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="1" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="A235" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="1" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+      <c r="A236" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="1" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="A237" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="1" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+      <c r="A238" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="1" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+      <c r="A239" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="1" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+      <c r="A240" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="1" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+      <c r="A241" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="1" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+      <c r="A242" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="1" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+      <c r="A243" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+      <c r="A244" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="1" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="A245" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="1" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="A246" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="1" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+      <c r="A247" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="1" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="A248" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="1" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+      <c r="A249" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="1" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+      <c r="A250" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="1" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="A251" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="1" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+      <c r="A252" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="1" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+      <c r="A253" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="1" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+      <c r="A254" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="1" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="A255" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="1" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="A256" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="1" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="A257" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="1" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+      <c r="A258" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="1" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
+      <c r="A259" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="1" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="A260" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="1" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="A261" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="1" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="A262" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="1" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
+      <c r="A263" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="1" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+      <c r="A264" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="1" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="A265" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="1" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="A266" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="1" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
+      <c r="A267" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="1" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="A268" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="1" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
+      <c r="A269" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="1" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
+      <c r="A270" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="1" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+      <c r="A271" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="1" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="1" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="A273" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="1" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
+      <c r="A274" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="1" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="A275" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="1" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+      <c r="A276" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="1" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
+      <c r="A277" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="1" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="A278" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="1" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="A279" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="1" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+      <c r="A280" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="1" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+      <c r="A281" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="1" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="A282" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="1" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="A283" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="1" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="A284" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="1" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
+      <c r="A285" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="1" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+      <c r="A286" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="1" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
+      <c r="A287" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="1" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+      <c r="A288" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="1" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
+      <c r="A289" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="1" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+      <c r="A290" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="1" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
+      <c r="A291" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="1" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
+      <c r="A292" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="1" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
+      <c r="A293" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="1" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
+      <c r="A294" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="1" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
+      <c r="A295" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="1" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
+      <c r="A296" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="1" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="A297" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="1" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
+      <c r="A298" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="1" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
+      <c r="A299" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="1" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="A300" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="1" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="A301" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="1" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
+      <c r="A302" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="1" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+      <c r="A303" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B303" s="1" t="s">
         <v>762</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
+      <c r="A304" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B304" s="1" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
+      <c r="A305" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="1" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+      <c r="A306" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="1" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="A307" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="1" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="A308" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="1" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
+      <c r="A309" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="1" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="A310" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="1" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="A311" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="1" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
+      <c r="A312" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="1" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="A313" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="1" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="A314" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="1" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
+      <c r="A315" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="1" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
+      <c r="A316" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="1" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+      <c r="A317" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="1" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
+      <c r="A318" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="1" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
+      <c r="A319" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="1" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="A320" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="1" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+      <c r="A321" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B321" s="1" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
+      <c r="A322" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B322" s="1" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
+      <c r="A323" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B323" s="1" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
+      <c r="A324" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B324" s="1" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
+      <c r="A325" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B325" s="1" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
+      <c r="A326" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="1" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
+      <c r="A327" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="1" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+      <c r="A328" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="1" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+      <c r="A329" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="1" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+      <c r="A330" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="1" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
+      <c r="A331" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="1" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
+      <c r="A332" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="1" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
+      <c r="A333" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="1" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
+      <c r="A334" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="1" t="s">
         <v>793</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
+      <c r="A335" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="1" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
+      <c r="A336" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="1" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
+      <c r="A337" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="1" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
+      <c r="A338" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="1" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
+      <c r="A339" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="1" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
+      <c r="A340" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="1" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
+      <c r="A341" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="1" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
+      <c r="A342" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="1" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
+      <c r="A343" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="1" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
+      <c r="A344" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="1" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
+      <c r="A345" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="1" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
+      <c r="A346" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="1" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
+      <c r="A347" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="1" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
+      <c r="A348" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="1" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
+      <c r="A349" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="1" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
+      <c r="A350" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="1" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
+      <c r="A351" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="1" t="s">
         <v>810</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
+      <c r="A352" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="1" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
+      <c r="A353" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="1" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
+      <c r="A354" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="1" t="s">
         <v>813</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
+      <c r="A355" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="1" t="s">
         <v>814</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
+      <c r="A356" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="1" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
+      <c r="A357" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="1" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
+      <c r="A358" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="1" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
+      <c r="A359" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B359" s="1" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
+      <c r="A360" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B360" s="1" t="s">
         <v>819</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
+      <c r="A361" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B361" s="1" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
+      <c r="A362" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B362" s="1" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
+      <c r="A363" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B363" s="1" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
+      <c r="A364" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="1" t="s">
         <v>823</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
+      <c r="A365" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="1" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
+      <c r="A366" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="1" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
+      <c r="A367" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="1" t="s">
         <v>826</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
+      <c r="A368" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="1" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
+      <c r="A369" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="1" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
+      <c r="A370" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="1" t="s">
         <v>829</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
+      <c r="A371" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B371" s="1" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372" t="s">
+      <c r="A372" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="1" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
+      <c r="A373" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="1" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
+      <c r="A374" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="1" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
+      <c r="A375" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="1" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376" t="s">
+      <c r="A376" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="1" t="s">
         <v>835</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
+      <c r="A377" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="1" t="s">
         <v>836</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378" t="s">
+      <c r="A378" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B378" s="1" t="s">
         <v>837</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379" t="s">
+      <c r="A379" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B379" s="1" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380" t="s">
+      <c r="A380" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B380" s="1" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381" t="s">
+      <c r="A381" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B381" s="1" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382" t="s">
+      <c r="A382" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B382" s="1" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383" t="s">
+      <c r="A383" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B383" s="1" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384" t="s">
+      <c r="A384" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B384" s="1" t="s">
         <v>843</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
+      <c r="A385" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B385" s="1" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
+      <c r="A386" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B386" s="1" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
+      <c r="A387" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B387" s="1" t="s">
         <v>846</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
+      <c r="A388" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B388" s="1" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
+      <c r="A389" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B389" s="1" t="s">
         <v>848</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
+      <c r="A390" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B390" s="1" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
+      <c r="A391" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B391" s="1" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
+      <c r="A392" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B392" s="1" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
+      <c r="A393" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="1" t="s">
         <v>852</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
+      <c r="A394" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B394" s="1" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
+      <c r="A395" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B395" t="s">
+      <c r="B395" s="1" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
+      <c r="A396" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B396" s="1" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
+      <c r="A397" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B397" t="s">
+      <c r="B397" s="1" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
+      <c r="A398" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B398" t="s">
+      <c r="B398" s="1" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
+      <c r="A399" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B399" t="s">
+      <c r="B399" s="1" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
+      <c r="A400" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B400" s="1" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
+      <c r="A401" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B401" s="1" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
+      <c r="A402" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B402" t="s">
+      <c r="B402" s="1" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
+      <c r="A403" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B403" t="s">
+      <c r="B403" s="1" t="s">
         <v>862</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
+      <c r="A404" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B404" t="s">
+      <c r="B404" s="1" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
+      <c r="A405" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B405" t="s">
+      <c r="B405" s="1" t="s">
         <v>864</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
+      <c r="A406" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B406" t="s">
+      <c r="B406" s="1" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
+      <c r="A407" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B407" s="1" t="s">
         <v>866</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
+      <c r="A408" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B408" t="s">
+      <c r="B408" s="1" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
+      <c r="A409" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B409" t="s">
+      <c r="B409" s="1" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
+      <c r="A410" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B410" t="s">
+      <c r="B410" s="1" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
+      <c r="A411" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B411" t="s">
+      <c r="B411" s="1" t="s">
         <v>870</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
+      <c r="A412" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B412" t="s">
+      <c r="B412" s="1" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
+      <c r="A413" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B413" t="s">
+      <c r="B413" s="1" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
+      <c r="A414" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B414" t="s">
+      <c r="B414" s="1" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
+      <c r="A415" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B415" t="s">
+      <c r="B415" s="1" t="s">
         <v>874</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
+      <c r="A416" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B416" s="1" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
+      <c r="A417" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B417" s="1" t="s">
         <v>876</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
+      <c r="A418" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B418" s="1" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
+      <c r="A419" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B419" s="1" t="s">
         <v>878</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
+      <c r="A420" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B420" s="1" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
+      <c r="A421" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B421" t="s">
+      <c r="B421" s="1" t="s">
         <v>880</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
+      <c r="A422" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B422" s="1" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
+      <c r="A423" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B423" s="1" t="s">
         <v>882</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
+      <c r="A424" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="1" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
+      <c r="A425" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B425" t="s">
+      <c r="B425" s="1" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
+      <c r="A426" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B426" s="1" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
+      <c r="A427" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B427" s="1" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
+      <c r="A428" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B428" s="1" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
+      <c r="A429" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B429" s="1" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
+      <c r="A430" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B430" s="1" t="s">
         <v>889</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
+      <c r="A431" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B431" s="1" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
+      <c r="A432" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B432" s="1" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
+      <c r="A433" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B433" s="1" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
+      <c r="A434" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B434" s="1" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
+      <c r="A435" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B435" s="1" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
+      <c r="A436" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="1" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
+      <c r="A437" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B437" s="1" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
+      <c r="A438" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B438" t="s">
+      <c r="B438" s="1" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
+      <c r="A439" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B439" s="1" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
+      <c r="A440" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B440" s="1" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
+      <c r="A441" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B441" s="1" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
+      <c r="A442" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B442" s="1" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
+      <c r="A443" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B443" t="s">
+      <c r="B443" s="1" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
+      <c r="A444" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
+      <c r="A445" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="1" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
+      <c r="A446" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B446" s="1" t="s">
         <v>904</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
+      <c r="A447" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B447" s="1" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
+      <c r="A448" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B448" s="1" t="s">
         <v>906</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
+      <c r="A449" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B449" s="1" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
+      <c r="A450" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B450" s="1" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
+      <c r="A451" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B451" t="s">
+      <c r="B451" s="1" t="s">
         <v>909</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
+      <c r="A452" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B452" s="1" t="s">
         <v>910</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
+      <c r="A453" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B453" s="1" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
+      <c r="A454" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B454" s="1" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
+      <c r="A455" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B455" s="1" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
+      <c r="A456" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B456" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
+      <c r="A457" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B457" t="s">
+      <c r="B457" s="1" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
+      <c r="A458" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B458" s="1" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
+      <c r="A459" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B459" s="1" t="s">
         <v>916</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
+      <c r="A460" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B460" s="1" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
+      <c r="A461" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="1" t="s">
         <v>918</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
+      <c r="A462" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="1" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
+      <c r="A463" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="1" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
+      <c r="A464" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="1" t="s">
         <v>921</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
+      <c r="A465" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="1" t="s">
         <v>922</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
+      <c r="A466" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="1" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
+      <c r="A467" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="1" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
+      <c r="A468" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="1" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
+      <c r="A469" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B469" s="1" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
+      <c r="A470" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B470" s="1" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
+      <c r="A471" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B471" s="1" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
+      <c r="A472" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B472" s="1" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
+      <c r="A473" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="1" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
+      <c r="A474" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B474" s="1" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
+      <c r="A475" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B475" s="1" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
+      <c r="A476" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="1" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
+      <c r="A477" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B477" s="1" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
+      <c r="A478" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B478" s="1" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
+      <c r="A479" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B479" s="1" t="s">
         <v>936</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
+      <c r="A480" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B480" t="s">
+      <c r="B480" s="1" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
+      <c r="A481" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B481" t="s">
+      <c r="B481" s="1" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A482" t="s">
+      <c r="A482" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B482" s="1" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
+      <c r="A483" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B483" s="1" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
+      <c r="A484" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B484" s="1" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
+      <c r="A485" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B485" t="s">
+      <c r="B485" s="1" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
+      <c r="A486" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B486" s="1" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
+      <c r="A487" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B487" s="1" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
+      <c r="A488" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B488" s="1" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
+      <c r="A489" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B489" s="1" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
+      <c r="A490" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B490" t="s">
+      <c r="B490" s="1" t="s">
         <v>947</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
+      <c r="A491" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B491" s="1" t="s">
         <v>948</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
+      <c r="A492" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B492" s="1" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
+      <c r="A493" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B493" t="s">
+      <c r="B493" s="1" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
+      <c r="A494" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B494" s="1" t="s">
         <v>951</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
+      <c r="A495" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B495" t="s">
+      <c r="B495" s="1" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
+      <c r="A496" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B496" t="s">
+      <c r="B496" s="1" t="s">
         <v>953</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+      <c r="A497" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B497" s="1" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+      <c r="A498" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B498" s="1" t="s">
         <v>955</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+      <c r="A499" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B499" s="1" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
+      <c r="A500" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B500" t="s">
+      <c r="B500" s="1" t="s">
         <v>957</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
+      <c r="A501" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B501" s="1" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
+      <c r="A502" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B502" s="1" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
+      <c r="A503" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B503" s="1" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
+      <c r="A504" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B504" s="1" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
+      <c r="A505" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="1" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A506">
+      <c r="A506" s="1">
         <v>26287740</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B506" s="1" t="s">
         <v>963</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Educacion\Desktop\constancia 22 junio impulso educativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5073A2E-9EB5-4BAA-B141-B46F437A6FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6880FF98-DEAE-4598-852A-9B927F5E7A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="825" windowWidth="16020" windowHeight="10095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="486">
   <si>
     <t>Nombre</t>
   </si>
@@ -48,1441 +48,7 @@
     <t>SANCHEZ DENIZ MARIANA NAIR</t>
   </si>
   <si>
-    <t>27196572</t>
-  </si>
-  <si>
-    <t>20465404</t>
-  </si>
-  <si>
-    <t>23071321</t>
-  </si>
-  <si>
-    <t>36864805</t>
-  </si>
-  <si>
-    <t>33438505</t>
-  </si>
-  <si>
-    <t>23058073</t>
-  </si>
-  <si>
-    <t>25252365</t>
-  </si>
-  <si>
-    <t>22958332</t>
-  </si>
-  <si>
-    <t>21955804</t>
-  </si>
-  <si>
-    <t>33629423</t>
-  </si>
-  <si>
-    <t>39009689</t>
-  </si>
-  <si>
-    <t>20634242</t>
-  </si>
-  <si>
-    <t>20448237</t>
-  </si>
-  <si>
-    <t>22159296</t>
-  </si>
-  <si>
-    <t>24879536</t>
-  </si>
-  <si>
-    <t>30091185</t>
-  </si>
-  <si>
-    <t>35848352</t>
-  </si>
-  <si>
-    <t>38463632</t>
-  </si>
-  <si>
-    <t>22997121</t>
-  </si>
-  <si>
-    <t>24948758</t>
-  </si>
-  <si>
-    <t>20969813</t>
-  </si>
-  <si>
-    <t>33047056</t>
-  </si>
-  <si>
-    <t>22754820</t>
-  </si>
-  <si>
-    <t>20801301</t>
-  </si>
-  <si>
-    <t>38459487</t>
-  </si>
-  <si>
-    <t>25830677</t>
-  </si>
-  <si>
-    <t>40779269</t>
-  </si>
-  <si>
-    <t>20131102</t>
-  </si>
-  <si>
-    <t>27196571</t>
-  </si>
-  <si>
-    <t>25859978</t>
-  </si>
-  <si>
-    <t>28720645</t>
-  </si>
-  <si>
-    <t>39376818</t>
-  </si>
-  <si>
-    <t>28478006</t>
-  </si>
-  <si>
-    <t>25649151</t>
-  </si>
-  <si>
-    <t>39182272</t>
-  </si>
-  <si>
-    <t>33848770</t>
-  </si>
-  <si>
-    <t>35849088</t>
-  </si>
-  <si>
-    <t>24689578</t>
-  </si>
-  <si>
-    <t>24343120</t>
-  </si>
-  <si>
-    <t>31227295</t>
-  </si>
-  <si>
-    <t>28836394</t>
-  </si>
-  <si>
-    <t>22014234</t>
-  </si>
-  <si>
-    <t>22959661</t>
-  </si>
-  <si>
-    <t>34696809</t>
-  </si>
-  <si>
-    <t>29835342</t>
-  </si>
-  <si>
-    <t>26287329</t>
-  </si>
-  <si>
-    <t>20942703</t>
-  </si>
-  <si>
-    <t>20279612</t>
-  </si>
-  <si>
-    <t>39376371</t>
-  </si>
-  <si>
-    <t>21361485</t>
-  </si>
-  <si>
-    <t>21955849</t>
-  </si>
-  <si>
-    <t>24091572</t>
-  </si>
-  <si>
-    <t>23380244</t>
-  </si>
-  <si>
-    <t>30690077</t>
-  </si>
-  <si>
-    <t>38015504</t>
-  </si>
-  <si>
-    <t>22159164</t>
-  </si>
-  <si>
-    <t>38079089</t>
-  </si>
-  <si>
-    <t>23381615</t>
-  </si>
-  <si>
-    <t>37833876</t>
-  </si>
-  <si>
-    <t>25823517</t>
-  </si>
-  <si>
-    <t>31065160</t>
-  </si>
-  <si>
-    <t>26629513</t>
-  </si>
-  <si>
-    <t>35507732</t>
-  </si>
-  <si>
-    <t>27379145</t>
-  </si>
-  <si>
-    <t>23545081</t>
-  </si>
-  <si>
-    <t>26287544</t>
-  </si>
-  <si>
-    <t>21361842</t>
-  </si>
-  <si>
-    <t>23977864</t>
-  </si>
-  <si>
-    <t>22218270</t>
-  </si>
-  <si>
-    <t>30805061</t>
-  </si>
-  <si>
-    <t>21994008</t>
-  </si>
-  <si>
-    <t>25939077</t>
-  </si>
-  <si>
-    <t>27350993</t>
-  </si>
-  <si>
-    <t>28786182</t>
-  </si>
-  <si>
-    <t>23735654</t>
-  </si>
-  <si>
-    <t>24266803</t>
-  </si>
-  <si>
-    <t>17120081</t>
-  </si>
-  <si>
-    <t>29351642</t>
-  </si>
-  <si>
-    <t>30157608</t>
-  </si>
-  <si>
-    <t>41272329</t>
-  </si>
-  <si>
-    <t>29911944</t>
-  </si>
-  <si>
-    <t>21357726</t>
-  </si>
-  <si>
-    <t>29149294</t>
-  </si>
-  <si>
-    <t>24362061</t>
-  </si>
-  <si>
-    <t>43763679</t>
-  </si>
-  <si>
-    <t>20943569</t>
-  </si>
-  <si>
-    <t>26678946</t>
-  </si>
-  <si>
-    <t>33319111</t>
-  </si>
-  <si>
-    <t>32723512</t>
-  </si>
-  <si>
-    <t>24244922</t>
-  </si>
-  <si>
-    <t>24234998</t>
-  </si>
-  <si>
-    <t>23545310</t>
-  </si>
-  <si>
-    <t>22358149</t>
-  </si>
-  <si>
-    <t>36253033</t>
-  </si>
-  <si>
-    <t>33018441</t>
-  </si>
-  <si>
-    <t>36424177</t>
-  </si>
-  <si>
-    <t>32627275</t>
-  </si>
-  <si>
-    <t>31510692</t>
-  </si>
-  <si>
-    <t>39954847</t>
-  </si>
-  <si>
-    <t>21361920</t>
-  </si>
-  <si>
-    <t>40995577</t>
-  </si>
-  <si>
-    <t>29507880</t>
-  </si>
-  <si>
-    <t>17505151</t>
-  </si>
-  <si>
-    <t>22358123</t>
-  </si>
-  <si>
-    <t>24168512</t>
-  </si>
-  <si>
-    <t>24793449</t>
-  </si>
-  <si>
-    <t>20303185</t>
-  </si>
-  <si>
-    <t>26878138</t>
-  </si>
-  <si>
-    <t>32399820</t>
-  </si>
-  <si>
-    <t>27548540</t>
-  </si>
-  <si>
-    <t>28487592</t>
-  </si>
-  <si>
-    <t>23840920</t>
-  </si>
-  <si>
-    <t>34194266</t>
-  </si>
-  <si>
-    <t>31510814</t>
-  </si>
-  <si>
-    <t>42081919</t>
-  </si>
-  <si>
-    <t>24948199</t>
-  </si>
-  <si>
-    <t>22227351</t>
-  </si>
-  <si>
-    <t>23752125</t>
-  </si>
-  <si>
-    <t>32083615</t>
-  </si>
-  <si>
-    <t>37531313</t>
-  </si>
-  <si>
-    <t>38075082</t>
-  </si>
-  <si>
-    <t>39376722</t>
-  </si>
-  <si>
-    <t>28888597</t>
-  </si>
-  <si>
-    <t>23380997</t>
-  </si>
-  <si>
-    <t>29636852</t>
-  </si>
-  <si>
-    <t>23058124</t>
-  </si>
-  <si>
-    <t>20444577</t>
-  </si>
-  <si>
-    <t>23498367</t>
-  </si>
-  <si>
-    <t>23638504</t>
-  </si>
-  <si>
-    <t>24234660</t>
-  </si>
-  <si>
-    <t>42356698</t>
-  </si>
-  <si>
-    <t>21357987</t>
-  </si>
-  <si>
-    <t>32354486</t>
-  </si>
-  <si>
-    <t>22958612</t>
-  </si>
-  <si>
-    <t>24724157</t>
-  </si>
-  <si>
-    <t>22227448</t>
-  </si>
-  <si>
-    <t>23634505</t>
-  </si>
-  <si>
-    <t>21609851</t>
-  </si>
-  <si>
-    <t>35857151</t>
-  </si>
-  <si>
-    <t>39651378</t>
-  </si>
-  <si>
-    <t>22815124</t>
-  </si>
-  <si>
-    <t>21625757</t>
-  </si>
-  <si>
-    <t>24480169</t>
-  </si>
-  <si>
-    <t>29690710</t>
-  </si>
-  <si>
-    <t>24658216</t>
-  </si>
-  <si>
-    <t>35209877</t>
-  </si>
-  <si>
-    <t>34698237</t>
-  </si>
-  <si>
-    <t>38219512</t>
-  </si>
-  <si>
-    <t>31185857</t>
-  </si>
-  <si>
-    <t>24689513</t>
-  </si>
-  <si>
-    <t>23381514</t>
-  </si>
-  <si>
-    <t>24972023</t>
-  </si>
-  <si>
-    <t>20303267</t>
-  </si>
-  <si>
-    <t>32352838</t>
-  </si>
-  <si>
-    <t>21742130</t>
-  </si>
-  <si>
-    <t>28005299</t>
-  </si>
-  <si>
-    <t>25549517</t>
-  </si>
-  <si>
-    <t>24362216</t>
-  </si>
-  <si>
-    <t>39424964</t>
-  </si>
-  <si>
-    <t>20303279</t>
-  </si>
-  <si>
-    <t>31642578</t>
-  </si>
-  <si>
-    <t>34918289</t>
-  </si>
-  <si>
-    <t>43763381</t>
-  </si>
-  <si>
-    <t>30152625</t>
-  </si>
-  <si>
-    <t>29351681</t>
-  </si>
-  <si>
-    <t>22227237</t>
-  </si>
-  <si>
-    <t>21181901</t>
-  </si>
-  <si>
-    <t>36864641</t>
-  </si>
-  <si>
-    <t>36864870</t>
-  </si>
-  <si>
-    <t>30483503</t>
-  </si>
-  <si>
-    <t>33336188</t>
-  </si>
-  <si>
-    <t>20942624</t>
-  </si>
-  <si>
-    <t>20802105</t>
-  </si>
-  <si>
-    <t>34245270</t>
-  </si>
-  <si>
-    <t>23977606</t>
-  </si>
-  <si>
-    <t>22291718</t>
-  </si>
-  <si>
-    <t>36031750</t>
-  </si>
-  <si>
-    <t>29889291</t>
-  </si>
-  <si>
-    <t>14961536</t>
-  </si>
-  <si>
-    <t>31510739</t>
-  </si>
-  <si>
-    <t>22659477</t>
-  </si>
-  <si>
-    <t>35510657</t>
-  </si>
-  <si>
-    <t>21362663</t>
-  </si>
-  <si>
-    <t>31621878</t>
-  </si>
-  <si>
-    <t>22788303</t>
-  </si>
-  <si>
-    <t>37742935</t>
-  </si>
-  <si>
-    <t>22788270</t>
-  </si>
-  <si>
-    <t>24972336</t>
-  </si>
-  <si>
-    <t>32095401</t>
-  </si>
-  <si>
-    <t>22168783</t>
-  </si>
-  <si>
-    <t>30071374</t>
-  </si>
-  <si>
-    <t>38593260</t>
-  </si>
-  <si>
-    <t>26527791</t>
-  </si>
-  <si>
-    <t>22157191</t>
-  </si>
-  <si>
-    <t>34920278</t>
-  </si>
-  <si>
-    <t>22358400</t>
-  </si>
-  <si>
-    <t>26880974</t>
-  </si>
-  <si>
-    <t>25412637</t>
-  </si>
-  <si>
-    <t>25405703</t>
-  </si>
-  <si>
-    <t>25321998</t>
-  </si>
-  <si>
-    <t>28595959</t>
-  </si>
-  <si>
-    <t>24234594</t>
-  </si>
-  <si>
-    <t>17592148</t>
-  </si>
-  <si>
-    <t>26611055</t>
-  </si>
-  <si>
-    <t>30819377</t>
-  </si>
-  <si>
-    <t>35852581</t>
-  </si>
-  <si>
-    <t>24362575</t>
-  </si>
-  <si>
-    <t>24362494</t>
-  </si>
-  <si>
-    <t>21361349</t>
-  </si>
-  <si>
-    <t>27276036</t>
-  </si>
-  <si>
-    <t>25252170</t>
-  </si>
-  <si>
-    <t>27047787</t>
-  </si>
-  <si>
-    <t>35735583</t>
-  </si>
-  <si>
-    <t>34059920</t>
-  </si>
-  <si>
-    <t>26287080</t>
-  </si>
-  <si>
-    <t>32748561</t>
-  </si>
-  <si>
-    <t>34100810</t>
-  </si>
-  <si>
-    <t>26175061</t>
-  </si>
-  <si>
-    <t>32808204</t>
-  </si>
-  <si>
-    <t>26288259</t>
-  </si>
-  <si>
-    <t>33836577</t>
-  </si>
-  <si>
-    <t>36254114</t>
-  </si>
-  <si>
-    <t>37627564</t>
-  </si>
-  <si>
-    <t>34918277</t>
-  </si>
-  <si>
-    <t>23027912</t>
-  </si>
-  <si>
-    <t>31870932</t>
-  </si>
-  <si>
-    <t>22958944</t>
-  </si>
-  <si>
-    <t>37741946</t>
-  </si>
-  <si>
-    <t>41321909</t>
-  </si>
-  <si>
-    <t>23016360</t>
-  </si>
-  <si>
-    <t>24283743</t>
-  </si>
-  <si>
-    <t>36252044</t>
-  </si>
-  <si>
-    <t>44665690</t>
-  </si>
-  <si>
-    <t>22063346</t>
-  </si>
-  <si>
-    <t>33058571</t>
-  </si>
-  <si>
-    <t>18357372</t>
-  </si>
-  <si>
-    <t>42917666</t>
-  </si>
-  <si>
-    <t>27685008</t>
-  </si>
-  <si>
-    <t>38764011</t>
-  </si>
-  <si>
-    <t>25412179</t>
-  </si>
-  <si>
-    <t>28262734</t>
-  </si>
-  <si>
-    <t>22289822</t>
-  </si>
-  <si>
-    <t>38461651</t>
-  </si>
-  <si>
-    <t>30839346</t>
-  </si>
-  <si>
-    <t>22011661</t>
-  </si>
-  <si>
-    <t>23982667</t>
-  </si>
-  <si>
-    <t>21358069</t>
-  </si>
-  <si>
-    <t>35505636</t>
-  </si>
-  <si>
-    <t>94120990</t>
-  </si>
-  <si>
-    <t>36423198</t>
-  </si>
-  <si>
-    <t>24168538</t>
-  </si>
-  <si>
-    <t>28720656</t>
-  </si>
-  <si>
-    <t>35923623</t>
-  </si>
-  <si>
-    <t>32454491</t>
-  </si>
-  <si>
-    <t>22003244</t>
-  </si>
-  <si>
-    <t>24426178</t>
-  </si>
-  <si>
-    <t>24691206</t>
-  </si>
-  <si>
-    <t>28538570</t>
-  </si>
-  <si>
-    <t>40470047</t>
-  </si>
-  <si>
-    <t>23027976</t>
-  </si>
-  <si>
-    <t>31324264</t>
-  </si>
-  <si>
-    <t>20943378</t>
-  </si>
-  <si>
-    <t>36034749</t>
-  </si>
-  <si>
-    <t>30246776</t>
-  </si>
-  <si>
-    <t>39183400</t>
-  </si>
-  <si>
-    <t>42516938</t>
-  </si>
-  <si>
-    <t>22957809</t>
-  </si>
-  <si>
-    <t>38592131</t>
-  </si>
-  <si>
-    <t>22359886</t>
-  </si>
-  <si>
-    <t>24689413</t>
-  </si>
-  <si>
-    <t>40592734</t>
-  </si>
-  <si>
-    <t>29098020</t>
-  </si>
-  <si>
-    <t>22014027</t>
-  </si>
-  <si>
-    <t>25321963</t>
-  </si>
-  <si>
-    <t>25823793</t>
-  </si>
-  <si>
-    <t>25939441</t>
-  </si>
-  <si>
-    <t>37924320</t>
-  </si>
-  <si>
-    <t>23791715</t>
-  </si>
-  <si>
-    <t>25991951</t>
-  </si>
-  <si>
-    <t>33960311</t>
-  </si>
-  <si>
-    <t>24266713</t>
-  </si>
-  <si>
-    <t>24464114</t>
-  </si>
-  <si>
-    <t>22159387</t>
-  </si>
-  <si>
-    <t>17078888</t>
-  </si>
-  <si>
-    <t>23545633</t>
-  </si>
-  <si>
-    <t>26511903</t>
-  </si>
-  <si>
-    <t>20655436</t>
-  </si>
-  <si>
-    <t>38460901</t>
-  </si>
-  <si>
-    <t>24972537</t>
-  </si>
-  <si>
-    <t>36034208</t>
-  </si>
-  <si>
-    <t>24091818</t>
-  </si>
-  <si>
-    <t>23735583</t>
-  </si>
-  <si>
-    <t>27350486</t>
-  </si>
-  <si>
-    <t>29358159</t>
-  </si>
-  <si>
-    <t>40368952</t>
-  </si>
-  <si>
-    <t>28967371</t>
-  </si>
-  <si>
-    <t>23545559</t>
-  </si>
-  <si>
-    <t>21362237</t>
-  </si>
-  <si>
-    <t>21926671</t>
-  </si>
-  <si>
-    <t>31005272</t>
-  </si>
-  <si>
-    <t>24689541</t>
-  </si>
-  <si>
-    <t>24948406</t>
-  </si>
-  <si>
-    <t>34697514</t>
-  </si>
-  <si>
-    <t>28040884</t>
-  </si>
-  <si>
-    <t>22714928</t>
-  </si>
-  <si>
-    <t>22063563</t>
-  </si>
-  <si>
-    <t>32353281</t>
-  </si>
-  <si>
-    <t>21895303</t>
-  </si>
-  <si>
-    <t>23380945</t>
-  </si>
-  <si>
-    <t>34915707</t>
-  </si>
-  <si>
-    <t>29165845</t>
-  </si>
-  <si>
-    <t>37506972</t>
-  </si>
-  <si>
-    <t>30725182</t>
-  </si>
-  <si>
-    <t>29302709</t>
-  </si>
-  <si>
-    <t>32083544</t>
-  </si>
-  <si>
-    <t>21181864</t>
-  </si>
-  <si>
-    <t>32860358</t>
-  </si>
-  <si>
-    <t>23634590</t>
-  </si>
-  <si>
-    <t>32693363</t>
-  </si>
-  <si>
-    <t>37647939</t>
-  </si>
-  <si>
-    <t>42188332</t>
-  </si>
-  <si>
-    <t>29621457</t>
-  </si>
-  <si>
-    <t>35209926</t>
-  </si>
-  <si>
-    <t>23735777</t>
-  </si>
-  <si>
-    <t>35852888</t>
-  </si>
-  <si>
-    <t>22705601</t>
-  </si>
-  <si>
-    <t>40779566</t>
-  </si>
-  <si>
-    <t>38462345</t>
-  </si>
-  <si>
-    <t>35209826</t>
-  </si>
-  <si>
-    <t>23378799</t>
-  </si>
-  <si>
-    <t>21591896</t>
-  </si>
-  <si>
-    <t>23381001</t>
-  </si>
-  <si>
-    <t>25135290</t>
-  </si>
-  <si>
-    <t>30157764</t>
-  </si>
-  <si>
-    <t>20386732</t>
-  </si>
-  <si>
-    <t>29774845</t>
-  </si>
-  <si>
-    <t>29176116</t>
-  </si>
-  <si>
-    <t>25462802</t>
-  </si>
-  <si>
-    <t>38460584</t>
-  </si>
-  <si>
-    <t>21113917</t>
-  </si>
-  <si>
-    <t>21331530</t>
-  </si>
-  <si>
-    <t>21359584</t>
-  </si>
-  <si>
-    <t>24426718</t>
-  </si>
-  <si>
-    <t>29740911</t>
-  </si>
-  <si>
-    <t>40592351</t>
-  </si>
-  <si>
-    <t>27350707</t>
-  </si>
-  <si>
-    <t>38217860</t>
-  </si>
-  <si>
-    <t>35736626</t>
-  </si>
-  <si>
-    <t>41157267</t>
-  </si>
-  <si>
-    <t>28263027</t>
-  </si>
-  <si>
-    <t>20943015</t>
-  </si>
-  <si>
-    <t>22227467</t>
-  </si>
-  <si>
-    <t>17470975</t>
-  </si>
-  <si>
-    <t>36250663</t>
-  </si>
-  <si>
-    <t>23638433</t>
-  </si>
-  <si>
-    <t>27685079</t>
-  </si>
-  <si>
-    <t>22107249</t>
-  </si>
-  <si>
-    <t>23721828</t>
-  </si>
-  <si>
-    <t>25167554</t>
-  </si>
-  <si>
-    <t>23977750</t>
-  </si>
-  <si>
-    <t>26590440</t>
-  </si>
-  <si>
-    <t>22658377</t>
-  </si>
-  <si>
-    <t>22998098</t>
-  </si>
-  <si>
-    <t>34754541</t>
-  </si>
-  <si>
-    <t>33022964</t>
-  </si>
-  <si>
-    <t>27682747</t>
-  </si>
-  <si>
-    <t>18582264</t>
-  </si>
-  <si>
-    <t>23634716</t>
-  </si>
-  <si>
-    <t>30542371</t>
-  </si>
-  <si>
-    <t>32353264</t>
-  </si>
-  <si>
-    <t>26678986</t>
-  </si>
-  <si>
-    <t>27043160</t>
-  </si>
-  <si>
-    <t>20132367</t>
-  </si>
-  <si>
-    <t>26643306</t>
-  </si>
-  <si>
-    <t>16210504</t>
-  </si>
-  <si>
-    <t>24693692</t>
-  </si>
-  <si>
-    <t>21592155</t>
-  </si>
-  <si>
-    <t>28487749</t>
-  </si>
-  <si>
-    <t>22754849</t>
-  </si>
-  <si>
-    <t>30839554</t>
-  </si>
-  <si>
-    <t>20275867</t>
-  </si>
-  <si>
-    <t>20935981</t>
-  </si>
-  <si>
-    <t>29149188</t>
-  </si>
-  <si>
-    <t>28005762</t>
-  </si>
-  <si>
-    <t>35381994</t>
-  </si>
-  <si>
-    <t>23134190</t>
-  </si>
-  <si>
-    <t>35192507</t>
-  </si>
-  <si>
-    <t>25195096</t>
-  </si>
-  <si>
-    <t>23297764</t>
-  </si>
-  <si>
-    <t>29345396</t>
-  </si>
-  <si>
-    <t>33836286</t>
-  </si>
-  <si>
-    <t>21609794</t>
-  </si>
-  <si>
-    <t>34915882</t>
-  </si>
-  <si>
-    <t>41321591</t>
-  </si>
-  <si>
-    <t>38460036</t>
-  </si>
-  <si>
-    <t>28691607</t>
-  </si>
-  <si>
-    <t>22659558</t>
-  </si>
-  <si>
-    <t>28525815</t>
-  </si>
-  <si>
-    <t>22754977</t>
-  </si>
-  <si>
-    <t>25695492</t>
-  </si>
-  <si>
-    <t>26908791</t>
-  </si>
-  <si>
-    <t>22159245</t>
-  </si>
-  <si>
-    <t>23943704</t>
-  </si>
-  <si>
-    <t>33630294</t>
-  </si>
-  <si>
-    <t>26510270</t>
-  </si>
-  <si>
-    <t>22058632</t>
-  </si>
-  <si>
-    <t>23364568</t>
-  </si>
-  <si>
-    <t>26872125</t>
-  </si>
-  <si>
-    <t>39651061</t>
-  </si>
-  <si>
-    <t>18769981</t>
-  </si>
-  <si>
-    <t>35734655</t>
-  </si>
-  <si>
-    <t>36544343</t>
-  </si>
-  <si>
-    <t>32632990</t>
-  </si>
-  <si>
-    <t>24561015</t>
-  </si>
-  <si>
-    <t>26791183</t>
-  </si>
-  <si>
-    <t>30145582</t>
-  </si>
-  <si>
-    <t>25549159</t>
-  </si>
-  <si>
-    <t>29540715</t>
-  </si>
-  <si>
-    <t>29812570</t>
-  </si>
-  <si>
-    <t>35735457</t>
-  </si>
-  <si>
-    <t>24343147</t>
-  </si>
-  <si>
-    <t>22788401</t>
-  </si>
-  <si>
-    <t>31979348</t>
-  </si>
-  <si>
-    <t>21610323</t>
-  </si>
-  <si>
-    <t>35850413</t>
-  </si>
-  <si>
-    <t>28040622</t>
-  </si>
-  <si>
-    <t>31612043</t>
-  </si>
-  <si>
-    <t>28904948</t>
-  </si>
-  <si>
-    <t>32690087</t>
-  </si>
-  <si>
-    <t>39524184</t>
-  </si>
-  <si>
-    <t>26231472</t>
-  </si>
-  <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>28416683</t>
-  </si>
-  <si>
-    <t>36254561</t>
-  </si>
-  <si>
-    <t>20989790</t>
-  </si>
-  <si>
-    <t>25001083</t>
-  </si>
-  <si>
-    <t>35506028</t>
-  </si>
-  <si>
-    <t>25939866</t>
-  </si>
-  <si>
-    <t>38463986</t>
-  </si>
-  <si>
-    <t>25462001</t>
-  </si>
-  <si>
-    <t>20462239</t>
-  </si>
-  <si>
-    <t>35736736</t>
-  </si>
-  <si>
-    <t>37742216</t>
-  </si>
-  <si>
-    <t>22358058</t>
-  </si>
-  <si>
-    <t>24660435</t>
-  </si>
-  <si>
-    <t>32351220</t>
-  </si>
-  <si>
-    <t>32033627</t>
-  </si>
-  <si>
-    <t>35734525</t>
-  </si>
-  <si>
-    <t>33236890</t>
-  </si>
-  <si>
-    <t>39954725</t>
-  </si>
-  <si>
-    <t>40592181</t>
-  </si>
-  <si>
-    <t>31044246</t>
-  </si>
-  <si>
-    <t>38593247</t>
-  </si>
-  <si>
-    <t>20133097</t>
-  </si>
-  <si>
-    <t>24480361</t>
-  </si>
-  <si>
-    <t>32750544</t>
-  </si>
-  <si>
-    <t>35189008</t>
-  </si>
-  <si>
-    <t>21742241</t>
-  </si>
-  <si>
-    <t>24879167</t>
-  </si>
-  <si>
-    <t>37297387</t>
-  </si>
-  <si>
-    <t>25118471</t>
-  </si>
-  <si>
-    <t>36251995</t>
-  </si>
-  <si>
-    <t>30631277</t>
-  </si>
-  <si>
-    <t>18011287</t>
-  </si>
-  <si>
-    <t>27276160</t>
-  </si>
-  <si>
-    <t>25649193</t>
-  </si>
-  <si>
-    <t>37462200</t>
-  </si>
-  <si>
-    <t>34657161</t>
-  </si>
-  <si>
-    <t>35857624</t>
-  </si>
-  <si>
-    <t>35506984</t>
-  </si>
-  <si>
-    <t>24795163</t>
-  </si>
-  <si>
-    <t>31633471</t>
-  </si>
-  <si>
-    <t>31871375</t>
-  </si>
-  <si>
-    <t>28904783</t>
-  </si>
-  <si>
-    <t>37298151</t>
-  </si>
-  <si>
-    <t>24793376</t>
-  </si>
-  <si>
-    <t>23634370</t>
-  </si>
-  <si>
-    <t>23381812</t>
-  </si>
-  <si>
-    <t>23488413</t>
   </si>
   <si>
     <t>CHAPARRO ANALIA CAROLINA</t>
@@ -2952,9 +1518,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3250,739 +1817,739 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>30631696</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>486</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
+      <c r="A3" s="2">
+        <v>27196572</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>487</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
+      <c r="A4" s="2">
+        <v>20465404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>488</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
+      <c r="A5" s="2">
+        <v>23071321</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>489</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
+      <c r="A6" s="2">
+        <v>36864805</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>490</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
+      <c r="A7" s="2">
+        <v>33438505</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>491</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
+      <c r="A8" s="2">
+        <v>23058073</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>492</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
+      <c r="A9" s="2">
+        <v>25252365</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>493</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
+      <c r="A10" s="2">
+        <v>22958332</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>494</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
+      <c r="A11" s="2">
+        <v>21955804</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>495</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
+      <c r="A12" s="2">
+        <v>33629423</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>496</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
+      <c r="A13" s="2">
+        <v>39009689</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>497</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
+      <c r="A14" s="2">
+        <v>20634242</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>498</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
+      <c r="A15" s="2">
+        <v>20448237</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>499</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
+      <c r="A16" s="2">
+        <v>22159296</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>500</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>21</v>
+      <c r="A17" s="2">
+        <v>24879536</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>22</v>
+      <c r="A18" s="2">
+        <v>30091185</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
+      <c r="A19" s="2">
+        <v>35848352</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>502</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
+      <c r="A20" s="2">
+        <v>38463632</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>503</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
+      <c r="A21" s="2">
+        <v>22997121</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>504</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
+      <c r="A22" s="2">
+        <v>24948758</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>505</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>27</v>
+      <c r="A23" s="2">
+        <v>20969813</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>506</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>28</v>
+      <c r="A24" s="2">
+        <v>33047056</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>507</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>29</v>
+      <c r="A25" s="2">
+        <v>22754820</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>508</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
+      <c r="A26" s="2">
+        <v>20801301</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>509</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>31</v>
+      <c r="A27" s="2">
+        <v>38459487</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>510</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
+      <c r="A28" s="2">
+        <v>25830677</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>511</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
+      <c r="A29" s="2">
+        <v>40779269</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>512</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>34</v>
+      <c r="A30" s="2">
+        <v>20131102</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>513</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
+      <c r="A31" s="2">
+        <v>27196571</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>514</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>36</v>
+      <c r="A32" s="2">
+        <v>25859978</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>515</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>37</v>
+      <c r="A33" s="2">
+        <v>28720645</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>516</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>38</v>
+      <c r="A34" s="2">
+        <v>39376818</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>517</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>39</v>
+      <c r="A35" s="2">
+        <v>28478006</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>518</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>40</v>
+      <c r="A36" s="2">
+        <v>25649151</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>519</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>41</v>
+      <c r="A37" s="2">
+        <v>39182272</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>520</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>42</v>
+      <c r="A38" s="2">
+        <v>33848770</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>521</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>43</v>
+      <c r="A39" s="2">
+        <v>35849088</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>522</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>44</v>
+      <c r="A40" s="2">
+        <v>24689578</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>523</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>45</v>
+      <c r="A41" s="2">
+        <v>24343120</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>524</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>46</v>
+      <c r="A42" s="2">
+        <v>31227295</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>525</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>47</v>
+      <c r="A43" s="2">
+        <v>28836394</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>526</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>48</v>
+      <c r="A44" s="2">
+        <v>22014234</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>527</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>49</v>
+      <c r="A45" s="2">
+        <v>22959661</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>528</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>50</v>
+      <c r="A46" s="2">
+        <v>34696809</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>529</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>51</v>
+      <c r="A47" s="2">
+        <v>29835342</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>530</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>52</v>
+      <c r="A48" s="2">
+        <v>26287329</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>531</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>53</v>
+      <c r="A49" s="2">
+        <v>20942703</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>532</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>54</v>
+      <c r="A50" s="2">
+        <v>20279612</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>533</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>55</v>
+      <c r="A51" s="2">
+        <v>39376371</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>534</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>56</v>
+      <c r="A52" s="2">
+        <v>21361485</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>535</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>57</v>
+      <c r="A53" s="2">
+        <v>21955849</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>536</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
+      <c r="A54" s="2">
+        <v>24091572</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>537</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>59</v>
+      <c r="A55" s="2">
+        <v>23380244</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>538</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>60</v>
+      <c r="A56" s="2">
+        <v>30690077</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>539</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>61</v>
+      <c r="A57" s="2">
+        <v>38015504</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>540</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>62</v>
+      <c r="A58" s="2">
+        <v>22159164</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>63</v>
+      <c r="A59" s="2">
+        <v>38079089</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>542</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>64</v>
+      <c r="A60" s="2">
+        <v>23381615</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>543</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>65</v>
+      <c r="A61" s="2">
+        <v>37833876</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>66</v>
+      <c r="A62" s="2">
+        <v>25823517</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>545</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>67</v>
+      <c r="A63" s="2">
+        <v>31065160</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>546</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>68</v>
+      <c r="A64" s="2">
+        <v>26629513</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>547</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>69</v>
+      <c r="A65" s="2">
+        <v>35507732</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>548</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>70</v>
+      <c r="A66" s="2">
+        <v>27379145</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>549</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>71</v>
+      <c r="A67" s="2">
+        <v>23545081</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>550</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>72</v>
+      <c r="A68" s="2">
+        <v>26287544</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>551</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>73</v>
+      <c r="A69" s="2">
+        <v>21361842</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>552</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>74</v>
+      <c r="A70" s="2">
+        <v>23977864</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>553</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>75</v>
+      <c r="A71" s="2">
+        <v>22218270</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>554</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>76</v>
+      <c r="A72" s="2">
+        <v>30805061</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>555</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>77</v>
+      <c r="A73" s="2">
+        <v>21994008</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>556</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>78</v>
+      <c r="A74" s="2">
+        <v>25939077</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>557</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>79</v>
+      <c r="A75" s="2">
+        <v>27350993</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>558</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>80</v>
+      <c r="A76" s="2">
+        <v>28786182</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>559</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>81</v>
+      <c r="A77" s="2">
+        <v>23735654</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>560</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>82</v>
+      <c r="A78" s="2">
+        <v>24266803</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>561</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>83</v>
+      <c r="A79" s="2">
+        <v>17120081</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>562</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>84</v>
+      <c r="A80" s="2">
+        <v>29351642</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>563</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>85</v>
+      <c r="A81" s="2">
+        <v>30157608</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>564</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>86</v>
+      <c r="A82" s="2">
+        <v>41272329</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>565</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>87</v>
+      <c r="A83" s="2">
+        <v>29911944</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>566</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>88</v>
+      <c r="A84" s="2">
+        <v>21357726</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>567</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>89</v>
+      <c r="A85" s="2">
+        <v>29149294</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>568</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>90</v>
+      <c r="A86" s="2">
+        <v>24362061</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>569</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>91</v>
+      <c r="A87" s="2">
+        <v>43763679</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>570</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>92</v>
+      <c r="A88" s="2">
+        <v>20943569</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>571</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>93</v>
+      <c r="A89" s="2">
+        <v>26678946</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>572</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>94</v>
+      <c r="A90" s="2">
+        <v>33319111</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>573</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>95</v>
+      <c r="A91" s="2">
+        <v>32723512</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>574</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>96</v>
+      <c r="A92" s="2">
+        <v>24244922</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>575</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>97</v>
+      <c r="A93" s="2">
+        <v>24234998</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>576</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -3990,3295 +2557,3295 @@
         <v>27043049</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>577</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>98</v>
+      <c r="A95" s="2">
+        <v>23545310</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>99</v>
+      <c r="A96" s="2">
+        <v>22358149</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>579</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>100</v>
+      <c r="A97" s="2">
+        <v>36253033</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>580</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>101</v>
+      <c r="A98" s="2">
+        <v>33018441</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>581</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>102</v>
+      <c r="A99" s="2">
+        <v>36424177</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>582</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>103</v>
+      <c r="A100" s="2">
+        <v>32627275</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>583</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>104</v>
+      <c r="A101" s="2">
+        <v>31510692</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>584</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>105</v>
+      <c r="A102" s="2">
+        <v>39954847</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>585</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>106</v>
+      <c r="A103" s="2">
+        <v>21361920</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>586</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>107</v>
+      <c r="A104" s="2">
+        <v>40995577</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>108</v>
+      <c r="A105" s="2">
+        <v>29507880</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>587</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>109</v>
+      <c r="A106" s="2">
+        <v>17505151</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>588</v>
+        <v>110</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>110</v>
+      <c r="A107" s="2">
+        <v>22358123</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>589</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>111</v>
+      <c r="A108" s="2">
+        <v>24168512</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>590</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>112</v>
+      <c r="A109" s="2">
+        <v>24793449</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>591</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>113</v>
+      <c r="A110" s="2">
+        <v>20303185</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>592</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>114</v>
+      <c r="A111" s="2">
+        <v>26878138</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>593</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>115</v>
+      <c r="A112" s="2">
+        <v>32399820</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>594</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>116</v>
+      <c r="A113" s="2">
+        <v>27548540</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>595</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>117</v>
+      <c r="A114" s="2">
+        <v>28487592</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>596</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>118</v>
+      <c r="A115" s="2">
+        <v>23840920</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>597</v>
+        <v>119</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>119</v>
+      <c r="A116" s="2">
+        <v>34194266</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>598</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>120</v>
+      <c r="A117" s="2">
+        <v>31510814</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>599</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>121</v>
+      <c r="A118" s="2">
+        <v>42081919</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>600</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>122</v>
+      <c r="A119" s="2">
+        <v>24948199</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>601</v>
+        <v>123</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>123</v>
+      <c r="A120" s="2">
+        <v>22227351</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="2">
+        <v>23752125</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>602</v>
-      </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="2">
+        <v>32083615</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>603</v>
-      </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="2">
+        <v>37531313</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>604</v>
-      </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="2">
+        <v>38075082</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>605</v>
-      </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="2">
+        <v>39376722</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>606</v>
-      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="2">
+        <v>28888597</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="2">
+        <v>23380997</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>608</v>
-      </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="2">
+        <v>29636852</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>609</v>
-      </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="2">
+        <v>23058124</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>610</v>
-      </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="2">
+        <v>20444577</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>611</v>
-      </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="2">
+        <v>23498367</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>612</v>
-      </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
+      <c r="A132" s="2">
+        <v>23638504</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>613</v>
-      </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="2">
+        <v>24234660</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>614</v>
-      </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="2">
+        <v>42356698</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>615</v>
-      </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="2">
+        <v>21357987</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>616</v>
-      </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="2">
+        <v>32354486</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>617</v>
-      </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="2">
+        <v>22958612</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>618</v>
-      </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="2">
+        <v>24724157</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>619</v>
-      </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
+      <c r="A139" s="2">
+        <v>22227448</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>620</v>
-      </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="2">
+        <v>23634505</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>621</v>
-      </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="2">
+        <v>21609851</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>622</v>
-      </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="2">
+        <v>35857151</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>623</v>
-      </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="2">
+        <v>39651378</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>624</v>
-      </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="2">
+        <v>22815124</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>625</v>
-      </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="2">
+        <v>21625757</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>626</v>
-      </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="2">
+        <v>24480169</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>627</v>
-      </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="2">
+        <v>29690710</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>628</v>
-      </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="2">
+        <v>24658216</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>629</v>
-      </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="2">
+        <v>35209877</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>630</v>
-      </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="2">
+        <v>34698237</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>631</v>
-      </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="2">
+        <v>38219512</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>632</v>
-      </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="2">
+        <v>31185857</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>633</v>
-      </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="2">
+        <v>24689513</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>634</v>
-      </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="2">
+        <v>23381514</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>635</v>
-      </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="2">
+        <v>24972023</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>636</v>
-      </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="2">
+        <v>20303267</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>637</v>
-      </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="2">
+        <v>32352838</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>638</v>
-      </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
+      <c r="A158" s="2">
+        <v>21742130</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>639</v>
-      </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
+      <c r="A159" s="2">
+        <v>28005299</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>640</v>
-      </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
+      <c r="A160" s="2">
+        <v>25549517</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>641</v>
-      </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="2">
+        <v>24362216</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>642</v>
-      </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
+      <c r="A162" s="2">
+        <v>39424964</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>643</v>
-      </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
+      <c r="A163" s="2">
+        <v>20303279</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>644</v>
-      </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
+      <c r="A164" s="2">
+        <v>31642578</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>645</v>
-      </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="2">
+        <v>34918289</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>646</v>
-      </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
+      <c r="A166" s="2">
+        <v>43763381</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>647</v>
-      </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
+      <c r="A167" s="2">
+        <v>30152625</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>648</v>
-      </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
+      <c r="A168" s="2">
+        <v>29351681</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>649</v>
-      </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
+      <c r="A169" s="2">
+        <v>22227237</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>650</v>
-      </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
+      <c r="A170" s="2">
+        <v>21181901</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>651</v>
-      </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
+      <c r="A171" s="2">
+        <v>36864641</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>652</v>
-      </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
+      <c r="A172" s="2">
+        <v>36864870</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
+      <c r="A173" s="2">
+        <v>30483503</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>654</v>
-      </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
+      <c r="A174" s="2">
+        <v>33336188</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>655</v>
-      </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
+      <c r="A175" s="2">
+        <v>20942624</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>656</v>
-      </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
+      <c r="A176" s="2">
+        <v>20802105</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>657</v>
-      </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
+      <c r="A177" s="2">
+        <v>34245270</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>658</v>
-      </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
+      <c r="A178" s="2">
+        <v>23977606</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>659</v>
-      </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
+      <c r="A179" s="2">
+        <v>22291718</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>660</v>
-      </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
+      <c r="A180" s="2">
+        <v>36031750</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>661</v>
-      </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
+      <c r="A181" s="2">
+        <v>29889291</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>662</v>
-      </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
+      <c r="A182" s="2">
+        <v>14961536</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>663</v>
-      </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
+      <c r="A183" s="2">
+        <v>31510739</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>664</v>
-      </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="2">
+        <v>22659477</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>665</v>
-      </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
+      <c r="A185" s="2">
+        <v>35510657</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>666</v>
-      </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
+      <c r="A186" s="2">
+        <v>21362663</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>667</v>
-      </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
+      <c r="A187" s="2">
+        <v>31621878</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>668</v>
-      </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
+      <c r="A188" s="2">
+        <v>22788303</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>669</v>
-      </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
+      <c r="A189" s="2">
+        <v>37742935</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>670</v>
-      </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
+      <c r="A190" s="2">
+        <v>22788270</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>671</v>
-      </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
+      <c r="A191" s="2">
+        <v>24972336</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>672</v>
-      </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
+      <c r="A192" s="2">
+        <v>32095401</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>673</v>
-      </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="2">
+        <v>22168783</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>674</v>
-      </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" s="1" t="s">
+      <c r="A194" s="2">
+        <v>30071374</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>675</v>
-      </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="1" t="s">
+      <c r="A195" s="2">
+        <v>38593260</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>676</v>
-      </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
+      <c r="A196" s="2">
+        <v>26527791</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>677</v>
-      </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="1" t="s">
+      <c r="A197" s="2">
+        <v>22157191</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>678</v>
-      </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="1" t="s">
+      <c r="A198" s="2">
+        <v>34920278</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>679</v>
-      </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
+      <c r="A199" s="2">
+        <v>22358400</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>680</v>
-      </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
+      <c r="A200" s="2">
+        <v>26880974</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>681</v>
-      </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
+      <c r="A201" s="2">
+        <v>25412637</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>682</v>
-      </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
+      <c r="A202" s="2">
+        <v>25405703</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>683</v>
-      </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
+      <c r="A203" s="2">
+        <v>25321998</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>684</v>
-      </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
+      <c r="A204" s="2">
+        <v>28595959</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>685</v>
-      </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="1" t="s">
+      <c r="A205" s="2">
+        <v>24234594</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>686</v>
-      </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
+      <c r="A206" s="2">
+        <v>17592148</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>687</v>
-      </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
+      <c r="A207" s="2">
+        <v>26611055</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>688</v>
-      </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
+      <c r="A208" s="2">
+        <v>30819377</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>689</v>
-      </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
+      <c r="A209" s="2">
+        <v>35852581</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>690</v>
-      </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
+      <c r="A210" s="2">
+        <v>24362575</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>691</v>
-      </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
+      <c r="A211" s="2">
+        <v>24362494</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>692</v>
-      </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
+      <c r="A212" s="2">
+        <v>21361349</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>693</v>
-      </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
+      <c r="A213" s="2">
+        <v>27276036</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>694</v>
-      </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
+      <c r="A214" s="2">
+        <v>25252170</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>695</v>
-      </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
+      <c r="A215" s="2">
+        <v>27047787</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>696</v>
-      </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
+      <c r="A216" s="2">
+        <v>35735583</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>697</v>
-      </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
+      <c r="A217" s="2">
+        <v>34059920</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>698</v>
-      </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="2">
+        <v>26287080</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>699</v>
-      </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
+      <c r="A219" s="2">
+        <v>32748561</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>700</v>
-      </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
+      <c r="A220" s="2">
+        <v>34100810</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>701</v>
-      </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
+      <c r="A221" s="2">
+        <v>26175061</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>702</v>
-      </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
+      <c r="A222" s="2">
+        <v>32808204</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>703</v>
-      </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
+      <c r="A223" s="2">
+        <v>26288259</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>704</v>
-      </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
+      <c r="A224" s="2">
+        <v>33836577</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>705</v>
-      </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
+      <c r="A225" s="2">
+        <v>36254114</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>706</v>
-      </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
+      <c r="A226" s="2">
+        <v>37627564</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>707</v>
-      </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
+      <c r="A227" s="2">
+        <v>34918277</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>708</v>
-      </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
+      <c r="A228" s="2">
+        <v>23027912</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>709</v>
-      </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
+      <c r="A229" s="2">
+        <v>31870932</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>710</v>
-      </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
+      <c r="A230" s="2">
+        <v>22958944</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>711</v>
-      </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
+      <c r="A231" s="2">
+        <v>37741946</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>712</v>
-      </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
+      <c r="A232" s="2">
+        <v>41321909</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>713</v>
-      </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="2">
+        <v>23016360</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>714</v>
-      </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>98</v>
+      <c r="A234" s="2">
+        <v>23545310</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>578</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>99</v>
+      <c r="A235" s="2">
+        <v>22358149</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>579</v>
+        <v>101</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>100</v>
+      <c r="A236" s="2">
+        <v>36253033</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>580</v>
+        <v>102</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>101</v>
+      <c r="A237" s="2">
+        <v>33018441</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>581</v>
+        <v>103</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>102</v>
+      <c r="A238" s="2">
+        <v>36424177</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>582</v>
+        <v>104</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>103</v>
+      <c r="A239" s="2">
+        <v>32627275</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>583</v>
+        <v>105</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
-        <v>104</v>
+      <c r="A240" s="2">
+        <v>31510692</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>584</v>
+        <v>106</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
-        <v>105</v>
+      <c r="A241" s="2">
+        <v>39954847</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>585</v>
+        <v>107</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>106</v>
+      <c r="A242" s="2">
+        <v>21361920</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>586</v>
+        <v>108</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>107</v>
+      <c r="A243" s="2">
+        <v>40995577</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>108</v>
+      <c r="A244" s="2">
+        <v>29507880</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>587</v>
+        <v>109</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
-        <v>109</v>
+      <c r="A245" s="2">
+        <v>17505151</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>588</v>
+        <v>110</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
-        <v>110</v>
+      <c r="A246" s="2">
+        <v>22358123</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>589</v>
+        <v>111</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
-        <v>111</v>
+      <c r="A247" s="2">
+        <v>24168512</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>590</v>
+        <v>112</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>112</v>
+      <c r="A248" s="2">
+        <v>24793449</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>591</v>
+        <v>113</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>113</v>
+      <c r="A249" s="2">
+        <v>20303185</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>592</v>
+        <v>114</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>114</v>
+      <c r="A250" s="2">
+        <v>26878138</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>593</v>
+        <v>115</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>115</v>
+      <c r="A251" s="2">
+        <v>32399820</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>594</v>
+        <v>116</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>116</v>
+      <c r="A252" s="2">
+        <v>27548540</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>595</v>
+        <v>117</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>117</v>
+      <c r="A253" s="2">
+        <v>28487592</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>596</v>
+        <v>118</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
-        <v>118</v>
+      <c r="A254" s="2">
+        <v>23840920</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>597</v>
+        <v>119</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
-        <v>119</v>
+      <c r="A255" s="2">
+        <v>34194266</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>715</v>
+        <v>237</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" s="1" t="s">
-        <v>237</v>
+      <c r="A256" s="2">
+        <v>24283743</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>716</v>
+        <v>238</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" s="1" t="s">
-        <v>238</v>
+      <c r="A257" s="2">
+        <v>36252044</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>717</v>
+        <v>239</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258" s="1" t="s">
-        <v>239</v>
+      <c r="A258" s="2">
+        <v>44665690</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>718</v>
+        <v>240</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259" s="1" t="s">
-        <v>240</v>
+      <c r="A259" s="2">
+        <v>22063346</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>719</v>
+        <v>241</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260" s="1" t="s">
-        <v>241</v>
+      <c r="A260" s="2">
+        <v>33058571</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>720</v>
+        <v>242</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261" s="1" t="s">
-        <v>242</v>
+      <c r="A261" s="2">
+        <v>18357372</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>721</v>
+        <v>243</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262" s="1" t="s">
-        <v>243</v>
+      <c r="A262" s="2">
+        <v>42917666</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>722</v>
+        <v>244</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263" s="1" t="s">
-        <v>244</v>
+      <c r="A263" s="2">
+        <v>27685008</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>723</v>
+        <v>245</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
-        <v>245</v>
+      <c r="A264" s="2">
+        <v>38764011</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>724</v>
+        <v>246</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
-        <v>246</v>
+      <c r="A265" s="2">
+        <v>25412179</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>725</v>
+        <v>247</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="1" t="s">
-        <v>247</v>
+      <c r="A266" s="2">
+        <v>28262734</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>726</v>
+        <v>248</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="1" t="s">
-        <v>248</v>
+      <c r="A267" s="2">
+        <v>22289822</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>727</v>
+        <v>249</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="1" t="s">
+      <c r="A268" s="2">
+        <v>32808204</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>703</v>
-      </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="1" t="s">
-        <v>249</v>
+      <c r="A269" s="2">
+        <v>38461651</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>728</v>
+        <v>250</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="1" t="s">
-        <v>250</v>
+      <c r="A270" s="2">
+        <v>30839346</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>729</v>
+        <v>251</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="1" t="s">
-        <v>251</v>
+      <c r="A271" s="2">
+        <v>22011661</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>730</v>
+        <v>252</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="1" t="s">
-        <v>252</v>
+      <c r="A272" s="2">
+        <v>23982667</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>731</v>
+        <v>253</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="1" t="s">
-        <v>253</v>
+      <c r="A273" s="2">
+        <v>21358069</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>732</v>
+        <v>254</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="1" t="s">
-        <v>254</v>
+      <c r="A274" s="2">
+        <v>35505636</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>733</v>
+        <v>255</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="1" t="s">
-        <v>255</v>
+      <c r="A275" s="2">
+        <v>94120990</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>734</v>
+        <v>256</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="1" t="s">
-        <v>256</v>
+      <c r="A276" s="2">
+        <v>36423198</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>735</v>
+        <v>257</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="1" t="s">
-        <v>257</v>
+      <c r="A277" s="2">
+        <v>24168538</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>736</v>
+        <v>258</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="1" t="s">
-        <v>258</v>
+      <c r="A278" s="2">
+        <v>28720656</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>737</v>
+        <v>259</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="1" t="s">
-        <v>259</v>
+      <c r="A279" s="2">
+        <v>35923623</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>738</v>
+        <v>260</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="1" t="s">
-        <v>260</v>
+      <c r="A280" s="2">
+        <v>32454491</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>739</v>
+        <v>261</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="1" t="s">
-        <v>261</v>
+      <c r="A281" s="2">
+        <v>22003244</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>740</v>
+        <v>262</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282" s="1" t="s">
-        <v>262</v>
+      <c r="A282" s="2">
+        <v>24426178</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>741</v>
+        <v>263</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283" s="1" t="s">
-        <v>263</v>
+      <c r="A283" s="2">
+        <v>24691206</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>742</v>
+        <v>264</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284" s="1" t="s">
-        <v>264</v>
+      <c r="A284" s="2">
+        <v>28538570</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>743</v>
+        <v>265</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285" s="1" t="s">
-        <v>265</v>
+      <c r="A285" s="2">
+        <v>40470047</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>744</v>
+        <v>266</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286" s="1" t="s">
-        <v>266</v>
+      <c r="A286" s="2">
+        <v>23027976</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>745</v>
+        <v>267</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287" s="1" t="s">
-        <v>267</v>
+      <c r="A287" s="2">
+        <v>31324264</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>746</v>
+        <v>268</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288" s="1" t="s">
-        <v>268</v>
+      <c r="A288" s="2">
+        <v>20943378</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>747</v>
+        <v>269</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
-        <v>269</v>
+      <c r="A289" s="2">
+        <v>36034749</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>748</v>
+        <v>270</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290" s="1" t="s">
-        <v>270</v>
+      <c r="A290" s="2">
+        <v>30246776</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>749</v>
+        <v>271</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" s="1" t="s">
-        <v>271</v>
+      <c r="A291" s="2">
+        <v>39183400</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>750</v>
+        <v>272</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" s="1" t="s">
-        <v>272</v>
+      <c r="A292" s="2">
+        <v>42516938</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>751</v>
+        <v>273</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" s="1" t="s">
-        <v>273</v>
+      <c r="A293" s="2">
+        <v>22957809</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>752</v>
+        <v>274</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" s="1" t="s">
-        <v>274</v>
+      <c r="A294" s="2">
+        <v>38592131</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>753</v>
+        <v>275</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" s="1" t="s">
-        <v>275</v>
+      <c r="A295" s="2">
+        <v>22359886</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>754</v>
+        <v>276</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" s="1" t="s">
-        <v>276</v>
+      <c r="A296" s="2">
+        <v>24689413</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>755</v>
+        <v>277</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" s="1" t="s">
-        <v>277</v>
+      <c r="A297" s="2">
+        <v>40592734</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>756</v>
+        <v>278</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" s="1" t="s">
-        <v>278</v>
+      <c r="A298" s="2">
+        <v>29098020</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>757</v>
+        <v>279</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" s="1" t="s">
-        <v>279</v>
+      <c r="A299" s="2">
+        <v>22014027</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>758</v>
+        <v>280</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" s="1" t="s">
-        <v>280</v>
+      <c r="A300" s="2">
+        <v>25321963</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>759</v>
+        <v>281</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>281</v>
+      <c r="A301" s="2">
+        <v>25823793</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>760</v>
+        <v>282</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>282</v>
+      <c r="A302" s="2">
+        <v>25939441</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>761</v>
+        <v>283</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>283</v>
+      <c r="A303" s="2">
+        <v>37924320</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>762</v>
+        <v>284</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" s="1" t="s">
-        <v>284</v>
+      <c r="A304" s="2">
+        <v>23791715</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>763</v>
+        <v>285</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" s="1" t="s">
-        <v>285</v>
+      <c r="A305" s="2">
+        <v>25991951</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>764</v>
+        <v>286</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" s="1" t="s">
-        <v>286</v>
+      <c r="A306" s="2">
+        <v>33960311</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>765</v>
+        <v>287</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" s="1" t="s">
-        <v>287</v>
+      <c r="A307" s="2">
+        <v>24266713</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>766</v>
+        <v>288</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" s="1" t="s">
-        <v>288</v>
+      <c r="A308" s="2">
+        <v>24464114</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>767</v>
+        <v>289</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" s="1" t="s">
-        <v>289</v>
+      <c r="A309" s="2">
+        <v>22159387</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>768</v>
+        <v>290</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" s="1" t="s">
-        <v>290</v>
+      <c r="A310" s="2">
+        <v>17078888</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>769</v>
+        <v>291</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" s="1" t="s">
-        <v>291</v>
+      <c r="A311" s="2">
+        <v>23545633</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>770</v>
+        <v>292</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" s="1" t="s">
-        <v>292</v>
+      <c r="A312" s="2">
+        <v>26511903</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>771</v>
+        <v>293</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" s="1" t="s">
-        <v>293</v>
+      <c r="A313" s="2">
+        <v>20655436</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>772</v>
+        <v>294</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" s="1" t="s">
-        <v>294</v>
+      <c r="A314" s="2">
+        <v>38460901</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>773</v>
+        <v>295</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" s="1" t="s">
-        <v>295</v>
+      <c r="A315" s="2">
+        <v>24972537</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>774</v>
+        <v>296</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" s="1" t="s">
-        <v>296</v>
+      <c r="A316" s="2">
+        <v>36034208</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>775</v>
+        <v>297</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
-        <v>297</v>
+      <c r="A317" s="2">
+        <v>24091818</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>776</v>
+        <v>298</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
-        <v>298</v>
+      <c r="A318" s="2">
+        <v>23735583</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>777</v>
+        <v>299</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" s="1" t="s">
-        <v>299</v>
+      <c r="A319" s="2">
+        <v>27350486</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>778</v>
+        <v>300</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" s="1" t="s">
-        <v>300</v>
+      <c r="A320" s="2">
+        <v>29358159</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>779</v>
+        <v>301</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" s="1" t="s">
-        <v>301</v>
+      <c r="A321" s="2">
+        <v>40368952</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>780</v>
+        <v>302</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" s="1" t="s">
-        <v>302</v>
+      <c r="A322" s="2">
+        <v>28967371</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>781</v>
+        <v>303</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
-        <v>303</v>
+      <c r="A323" s="2">
+        <v>23545559</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>782</v>
+        <v>304</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" s="1" t="s">
-        <v>304</v>
+      <c r="A324" s="2">
+        <v>21362237</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>783</v>
+        <v>305</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
-        <v>305</v>
+      <c r="A325" s="2">
+        <v>21926671</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>784</v>
+        <v>306</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" s="1" t="s">
-        <v>306</v>
+      <c r="A326" s="2">
+        <v>31005272</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>785</v>
+        <v>307</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
-        <v>307</v>
+      <c r="A327" s="2">
+        <v>24689541</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>786</v>
+        <v>308</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
-        <v>308</v>
+      <c r="A328" s="2">
+        <v>24948406</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>787</v>
+        <v>309</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" s="1" t="s">
-        <v>309</v>
+      <c r="A329" s="2">
+        <v>34697514</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>788</v>
+        <v>310</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" s="1" t="s">
-        <v>310</v>
+      <c r="A330" s="2">
+        <v>28040884</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>789</v>
+        <v>311</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" s="1" t="s">
-        <v>311</v>
+      <c r="A331" s="2">
+        <v>22714928</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>790</v>
+        <v>312</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
-        <v>312</v>
+      <c r="A332" s="2">
+        <v>22063563</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>791</v>
+        <v>313</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>313</v>
+      <c r="A333" s="2">
+        <v>32353281</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>792</v>
+        <v>314</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>314</v>
+      <c r="A334" s="2">
+        <v>21895303</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>793</v>
+        <v>315</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
-        <v>315</v>
+      <c r="A335" s="2">
+        <v>23380945</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>794</v>
+        <v>316</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
-        <v>316</v>
+      <c r="A336" s="2">
+        <v>34915707</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>795</v>
+        <v>317</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
-        <v>317</v>
+      <c r="A337" s="2">
+        <v>29165845</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>796</v>
+        <v>318</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
-        <v>318</v>
+      <c r="A338" s="2">
+        <v>37506972</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>797</v>
+        <v>319</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="1" t="s">
-        <v>319</v>
+      <c r="A339" s="2">
+        <v>30725182</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>798</v>
+        <v>320</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
-        <v>320</v>
+      <c r="A340" s="2">
+        <v>29302709</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>799</v>
+        <v>321</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="1" t="s">
-        <v>321</v>
+      <c r="A341" s="2">
+        <v>32083544</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>800</v>
+        <v>322</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" s="1" t="s">
-        <v>322</v>
+      <c r="A342" s="2">
+        <v>21181864</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>801</v>
+        <v>323</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" s="1" t="s">
-        <v>323</v>
+      <c r="A343" s="2">
+        <v>32860358</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>802</v>
+        <v>324</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" s="1" t="s">
-        <v>324</v>
+      <c r="A344" s="2">
+        <v>23634590</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>803</v>
+        <v>325</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="1" t="s">
-        <v>325</v>
+      <c r="A345" s="2">
+        <v>32693363</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>804</v>
+        <v>326</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" s="1" t="s">
-        <v>326</v>
+      <c r="A346" s="2">
+        <v>37647939</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>805</v>
+        <v>327</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="1" t="s">
-        <v>327</v>
+      <c r="A347" s="2">
+        <v>42188332</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>806</v>
+        <v>328</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" s="1" t="s">
-        <v>328</v>
+      <c r="A348" s="2">
+        <v>29621457</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>807</v>
+        <v>329</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" s="1" t="s">
-        <v>329</v>
+      <c r="A349" s="2">
+        <v>35209926</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>808</v>
+        <v>330</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="1" t="s">
-        <v>330</v>
+      <c r="A350" s="2">
+        <v>23735777</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>809</v>
+        <v>331</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351" s="1" t="s">
-        <v>331</v>
+      <c r="A351" s="2">
+        <v>35852888</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>810</v>
+        <v>332</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352" s="1" t="s">
-        <v>332</v>
+      <c r="A352" s="2">
+        <v>22705601</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>811</v>
+        <v>333</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353" s="1" t="s">
-        <v>333</v>
+      <c r="A353" s="2">
+        <v>40779566</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>812</v>
+        <v>334</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>334</v>
+      <c r="A354" s="2">
+        <v>38462345</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>813</v>
+        <v>335</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355" s="1" t="s">
-        <v>335</v>
+      <c r="A355" s="2">
+        <v>35209826</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>814</v>
+        <v>336</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356" s="1" t="s">
-        <v>336</v>
+      <c r="A356" s="2">
+        <v>23378799</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>815</v>
+        <v>337</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357" s="1" t="s">
-        <v>337</v>
+      <c r="A357" s="2">
+        <v>21591896</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>816</v>
+        <v>338</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358" s="1" t="s">
-        <v>338</v>
+      <c r="A358" s="2">
+        <v>23381001</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>817</v>
+        <v>339</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359" s="1" t="s">
-        <v>339</v>
+      <c r="A359" s="2">
+        <v>25135290</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>818</v>
+        <v>340</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360" s="1" t="s">
-        <v>340</v>
+      <c r="A360" s="2">
+        <v>30157764</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>819</v>
+        <v>341</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361" s="1" t="s">
-        <v>341</v>
+      <c r="A361" s="2">
+        <v>20386732</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>820</v>
+        <v>342</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362" s="1" t="s">
-        <v>342</v>
+      <c r="A362" s="2">
+        <v>29774845</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>821</v>
+        <v>343</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363" s="1" t="s">
-        <v>343</v>
+      <c r="A363" s="2">
+        <v>29176116</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>822</v>
+        <v>344</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364" s="1" t="s">
-        <v>344</v>
+      <c r="A364" s="2">
+        <v>25462802</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>823</v>
+        <v>345</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365" s="1" t="s">
-        <v>345</v>
+      <c r="A365" s="2">
+        <v>38460584</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>824</v>
+        <v>346</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366" s="1" t="s">
-        <v>346</v>
+      <c r="A366" s="2">
+        <v>21113917</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>825</v>
+        <v>347</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367" s="1" t="s">
-        <v>347</v>
+      <c r="A367" s="2">
+        <v>21331530</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>826</v>
+        <v>348</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368" s="1" t="s">
-        <v>348</v>
+      <c r="A368" s="2">
+        <v>21359584</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>827</v>
+        <v>349</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369" s="1" t="s">
-        <v>349</v>
+      <c r="A369" s="2">
+        <v>24426718</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>828</v>
+        <v>350</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370" s="1" t="s">
-        <v>350</v>
+      <c r="A370" s="2">
+        <v>29740911</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>829</v>
+        <v>351</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371" s="1" t="s">
-        <v>351</v>
+      <c r="A371" s="2">
+        <v>40592351</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>830</v>
+        <v>352</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372" s="1" t="s">
-        <v>352</v>
+      <c r="A372" s="2">
+        <v>27350707</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>831</v>
+        <v>353</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373" s="1" t="s">
-        <v>353</v>
+      <c r="A373" s="2">
+        <v>38217860</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>832</v>
+        <v>354</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374" s="1" t="s">
-        <v>354</v>
+      <c r="A374" s="2">
+        <v>35736626</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>833</v>
+        <v>355</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375" s="1" t="s">
-        <v>355</v>
+      <c r="A375" s="2">
+        <v>41157267</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>834</v>
+        <v>356</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376" s="1" t="s">
-        <v>356</v>
+      <c r="A376" s="2">
+        <v>28263027</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>835</v>
+        <v>357</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377" s="1" t="s">
-        <v>357</v>
+      <c r="A377" s="2">
+        <v>20943015</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>836</v>
+        <v>358</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378" s="1" t="s">
-        <v>358</v>
+      <c r="A378" s="2">
+        <v>22227467</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>837</v>
+        <v>359</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379" s="1" t="s">
-        <v>359</v>
+      <c r="A379" s="2">
+        <v>17470975</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>838</v>
+        <v>360</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380" s="1" t="s">
-        <v>360</v>
+      <c r="A380" s="2">
+        <v>36250663</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>839</v>
+        <v>361</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381" s="1" t="s">
-        <v>361</v>
+      <c r="A381" s="2">
+        <v>23638433</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>840</v>
+        <v>362</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382" s="1" t="s">
-        <v>362</v>
+      <c r="A382" s="2">
+        <v>27685079</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>841</v>
+        <v>363</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383" s="1" t="s">
-        <v>363</v>
+      <c r="A383" s="2">
+        <v>22107249</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>842</v>
+        <v>364</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384" s="1" t="s">
-        <v>364</v>
+      <c r="A384" s="2">
+        <v>23721828</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>843</v>
+        <v>365</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385" s="1" t="s">
-        <v>365</v>
+      <c r="A385" s="2">
+        <v>25167554</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>844</v>
+        <v>366</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386" s="1" t="s">
-        <v>366</v>
+      <c r="A386" s="2">
+        <v>23977750</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>845</v>
+        <v>367</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387" s="1" t="s">
-        <v>367</v>
+      <c r="A387" s="2">
+        <v>26590440</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>846</v>
+        <v>368</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388" s="1" t="s">
-        <v>368</v>
+      <c r="A388" s="2">
+        <v>22658377</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>847</v>
+        <v>369</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389" s="1" t="s">
-        <v>369</v>
+      <c r="A389" s="2">
+        <v>22998098</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>848</v>
+        <v>370</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390" s="1" t="s">
-        <v>370</v>
+      <c r="A390" s="2">
+        <v>34754541</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>849</v>
+        <v>371</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391" s="1" t="s">
-        <v>371</v>
+      <c r="A391" s="2">
+        <v>33022964</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>850</v>
+        <v>372</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392" s="1" t="s">
-        <v>372</v>
+      <c r="A392" s="2">
+        <v>27682747</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>851</v>
+        <v>373</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393" s="1" t="s">
-        <v>373</v>
+      <c r="A393" s="2">
+        <v>18582264</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>852</v>
+        <v>374</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394" s="1" t="s">
-        <v>374</v>
+      <c r="A394" s="2">
+        <v>23634716</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>853</v>
+        <v>375</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395" s="1" t="s">
-        <v>375</v>
+      <c r="A395" s="2">
+        <v>30542371</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>854</v>
+        <v>376</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396" s="1" t="s">
-        <v>376</v>
+      <c r="A396" s="2">
+        <v>32353264</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>855</v>
+        <v>377</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397" s="1" t="s">
-        <v>377</v>
+      <c r="A397" s="2">
+        <v>26678986</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>856</v>
+        <v>378</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398" s="1" t="s">
-        <v>378</v>
+      <c r="A398" s="2">
+        <v>27043160</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>857</v>
+        <v>379</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399" s="1" t="s">
-        <v>379</v>
+      <c r="A399" s="2">
+        <v>20132367</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>858</v>
+        <v>380</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400" s="1" t="s">
-        <v>380</v>
+      <c r="A400" s="2">
+        <v>26643306</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>859</v>
+        <v>381</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401" s="1" t="s">
-        <v>381</v>
+      <c r="A401" s="2">
+        <v>16210504</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>860</v>
+        <v>382</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402" s="1" t="s">
-        <v>382</v>
+      <c r="A402" s="2">
+        <v>24693692</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>861</v>
+        <v>383</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403" s="1" t="s">
-        <v>383</v>
+      <c r="A403" s="2">
+        <v>21592155</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>862</v>
+        <v>384</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404" s="1" t="s">
-        <v>384</v>
+      <c r="A404" s="2">
+        <v>28487749</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>863</v>
+        <v>385</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405" s="1" t="s">
-        <v>385</v>
+      <c r="A405" s="2">
+        <v>22754849</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>864</v>
+        <v>386</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406" s="1" t="s">
-        <v>386</v>
+      <c r="A406" s="2">
+        <v>30839554</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>865</v>
+        <v>387</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407" s="1" t="s">
-        <v>387</v>
+      <c r="A407" s="2">
+        <v>20275867</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>866</v>
+        <v>388</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408" s="1" t="s">
-        <v>388</v>
+      <c r="A408" s="2">
+        <v>20935981</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>867</v>
+        <v>389</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409" s="1" t="s">
-        <v>389</v>
+      <c r="A409" s="2">
+        <v>29149188</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>868</v>
+        <v>390</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410" s="1" t="s">
-        <v>390</v>
+      <c r="A410" s="2">
+        <v>28005762</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>869</v>
+        <v>391</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411" s="1" t="s">
-        <v>391</v>
+      <c r="A411" s="2">
+        <v>35381994</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>870</v>
+        <v>392</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412" s="1" t="s">
-        <v>392</v>
+      <c r="A412" s="2">
+        <v>23134190</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>871</v>
+        <v>393</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413" s="1" t="s">
-        <v>393</v>
+      <c r="A413" s="2">
+        <v>35192507</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>872</v>
+        <v>394</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" s="1" t="s">
-        <v>394</v>
+      <c r="A414" s="2">
+        <v>25195096</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>873</v>
+        <v>395</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" s="1" t="s">
-        <v>395</v>
+      <c r="A415" s="2">
+        <v>23297764</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>874</v>
+        <v>396</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416" s="1" t="s">
-        <v>396</v>
+      <c r="A416" s="2">
+        <v>29345396</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>875</v>
+        <v>397</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417" s="1" t="s">
-        <v>397</v>
+      <c r="A417" s="2">
+        <v>33836286</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>876</v>
+        <v>398</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418" s="1" t="s">
-        <v>398</v>
+      <c r="A418" s="2">
+        <v>21609794</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>877</v>
+        <v>399</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419" s="1" t="s">
-        <v>399</v>
+      <c r="A419" s="2">
+        <v>34915882</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>878</v>
+        <v>400</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420" s="1" t="s">
-        <v>400</v>
+      <c r="A420" s="2">
+        <v>41321591</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>879</v>
+        <v>401</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421" s="1" t="s">
-        <v>401</v>
+      <c r="A421" s="2">
+        <v>38460036</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>880</v>
+        <v>402</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" s="1" t="s">
-        <v>402</v>
+      <c r="A422" s="2">
+        <v>28691607</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>881</v>
+        <v>403</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423" s="1" t="s">
-        <v>403</v>
+      <c r="A423" s="2">
+        <v>22659558</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>882</v>
+        <v>404</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424" s="1" t="s">
-        <v>404</v>
+      <c r="A424" s="2">
+        <v>28525815</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>883</v>
+        <v>405</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A425" s="1" t="s">
-        <v>405</v>
+      <c r="A425" s="2">
+        <v>22754977</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>884</v>
+        <v>406</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A426" s="1" t="s">
-        <v>406</v>
+      <c r="A426" s="2">
+        <v>25695492</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>885</v>
+        <v>407</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A427" s="1" t="s">
-        <v>407</v>
+      <c r="A427" s="2">
+        <v>26908791</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>886</v>
+        <v>408</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A428" s="1" t="s">
-        <v>408</v>
+      <c r="A428" s="2">
+        <v>22159245</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>887</v>
+        <v>409</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A429" s="1" t="s">
-        <v>409</v>
+      <c r="A429" s="2">
+        <v>23943704</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>888</v>
+        <v>410</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A430" s="1" t="s">
-        <v>410</v>
+      <c r="A430" s="2">
+        <v>33630294</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>889</v>
+        <v>411</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A431" s="1" t="s">
-        <v>411</v>
+      <c r="A431" s="2">
+        <v>26510270</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>890</v>
+        <v>412</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A432" s="1" t="s">
-        <v>412</v>
+      <c r="A432" s="2">
+        <v>22058632</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>891</v>
+        <v>413</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A433" s="1" t="s">
-        <v>413</v>
+      <c r="A433" s="2">
+        <v>23364568</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>892</v>
+        <v>414</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A434" s="1" t="s">
-        <v>414</v>
+      <c r="A434" s="2">
+        <v>26872125</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>893</v>
+        <v>415</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A435" s="1" t="s">
-        <v>415</v>
+      <c r="A435" s="2">
+        <v>39651061</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>894</v>
+        <v>416</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A436" s="1" t="s">
-        <v>416</v>
+      <c r="A436" s="2">
+        <v>18769981</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>895</v>
+        <v>417</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A437" s="1" t="s">
-        <v>417</v>
+      <c r="A437" s="2">
+        <v>35734655</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>896</v>
+        <v>418</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A438" s="1" t="s">
-        <v>418</v>
+      <c r="A438" s="2">
+        <v>36544343</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>897</v>
+        <v>419</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A439" s="1" t="s">
-        <v>419</v>
+      <c r="A439" s="2">
+        <v>32632990</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>898</v>
+        <v>420</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A440" s="1" t="s">
-        <v>420</v>
+      <c r="A440" s="2">
+        <v>24561015</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>899</v>
+        <v>421</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A441" s="1" t="s">
-        <v>421</v>
+      <c r="A441" s="2">
+        <v>26791183</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>900</v>
+        <v>422</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A442" s="1" t="s">
-        <v>422</v>
+      <c r="A442" s="2">
+        <v>30145582</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>901</v>
+        <v>423</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A443" s="1" t="s">
-        <v>423</v>
+      <c r="A443" s="2">
+        <v>25549159</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>902</v>
+        <v>424</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A444" s="1" t="s">
-        <v>424</v>
+      <c r="A444" s="2">
+        <v>29540715</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A445" s="1" t="s">
+      <c r="A445" s="2">
+        <v>29812570</v>
+      </c>
+      <c r="B445" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>903</v>
-      </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A446" s="1" t="s">
+      <c r="A446" s="2">
+        <v>35735457</v>
+      </c>
+      <c r="B446" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B446" s="1" t="s">
-        <v>904</v>
-      </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A447" s="1" t="s">
+      <c r="A447" s="2">
+        <v>24343147</v>
+      </c>
+      <c r="B447" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B447" s="1" t="s">
-        <v>905</v>
-      </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A448" s="1" t="s">
+      <c r="A448" s="2">
+        <v>22788401</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B448" s="1" t="s">
-        <v>906</v>
-      </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A449" s="1" t="s">
+      <c r="A449" s="2">
+        <v>31979348</v>
+      </c>
+      <c r="B449" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B449" s="1" t="s">
-        <v>907</v>
-      </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A450" s="1" t="s">
+      <c r="A450" s="2">
+        <v>21610323</v>
+      </c>
+      <c r="B450" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B450" s="1" t="s">
-        <v>908</v>
-      </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A451" s="1" t="s">
+      <c r="A451" s="2">
+        <v>35850413</v>
+      </c>
+      <c r="B451" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B451" s="1" t="s">
-        <v>909</v>
-      </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A452" s="1" t="s">
+      <c r="A452" s="2">
+        <v>28040622</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>910</v>
-      </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A453" s="1" t="s">
+      <c r="A453" s="2">
+        <v>31612043</v>
+      </c>
+      <c r="B453" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B453" s="1" t="s">
-        <v>911</v>
-      </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A454" s="1" t="s">
+      <c r="A454" s="2">
+        <v>28904948</v>
+      </c>
+      <c r="B454" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B454" s="1" t="s">
-        <v>912</v>
-      </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A455" s="1" t="s">
+      <c r="A455" s="2">
+        <v>32690087</v>
+      </c>
+      <c r="B455" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B455" s="1" t="s">
-        <v>913</v>
-      </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A456" s="1" t="s">
-        <v>436</v>
+      <c r="A456" s="2">
+        <v>39524184</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A457" s="1" t="s">
-        <v>437</v>
+      <c r="A457" s="2">
+        <v>26231472</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>914</v>
+        <v>436</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" s="2">
+        <v>28416683</v>
+      </c>
+      <c r="B459" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A459" s="1" t="s">
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" s="2">
+        <v>36254561</v>
+      </c>
+      <c r="B460" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B459" s="1" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A460" s="1" t="s">
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" s="2">
+        <v>20989790</v>
+      </c>
+      <c r="B461" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A461" s="1" t="s">
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" s="2">
+        <v>25001083</v>
+      </c>
+      <c r="B462" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B461" s="1" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A462" s="1" t="s">
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" s="2">
+        <v>35506028</v>
+      </c>
+      <c r="B463" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B462" s="1" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A463" s="1" t="s">
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" s="2">
+        <v>25939866</v>
+      </c>
+      <c r="B464" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B463" s="1" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A464" s="1" t="s">
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" s="2">
+        <v>38463986</v>
+      </c>
+      <c r="B465" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B464" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A465" s="1" t="s">
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" s="2">
+        <v>25462001</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A466" s="1" t="s">
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" s="2">
+        <v>20462239</v>
+      </c>
+      <c r="B467" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A467" s="1" t="s">
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" s="2">
+        <v>35736736</v>
+      </c>
+      <c r="B468" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B467" s="1" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A468" s="1" t="s">
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" s="2">
+        <v>37742216</v>
+      </c>
+      <c r="B469" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B468" s="1" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A469" s="1" t="s">
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" s="2">
+        <v>22358058</v>
+      </c>
+      <c r="B470" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B469" s="1" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A470" s="1" t="s">
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" s="2">
+        <v>24660435</v>
+      </c>
+      <c r="B471" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A471" s="1" t="s">
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" s="2">
+        <v>32351220</v>
+      </c>
+      <c r="B472" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A472" s="1" t="s">
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" s="2">
+        <v>32033627</v>
+      </c>
+      <c r="B473" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B472" s="1" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A473" s="1" t="s">
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" s="2">
+        <v>35734525</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A474" s="1" t="s">
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" s="2">
+        <v>33236890</v>
+      </c>
+      <c r="B475" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A475" s="1" t="s">
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" s="2">
+        <v>39954725</v>
+      </c>
+      <c r="B476" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A476" s="1" t="s">
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" s="2">
+        <v>40592181</v>
+      </c>
+      <c r="B477" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A477" s="1" t="s">
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" s="2">
+        <v>31044246</v>
+      </c>
+      <c r="B478" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A478" s="1" t="s">
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" s="2">
+        <v>38593247</v>
+      </c>
+      <c r="B479" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B478" s="1" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A479" s="1" t="s">
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" s="2">
+        <v>20133097</v>
+      </c>
+      <c r="B480" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B479" s="1" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A480" s="1" t="s">
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481" s="2">
+        <v>24480361</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B480" s="1" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A481" s="1" t="s">
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482" s="2">
+        <v>32750544</v>
+      </c>
+      <c r="B482" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B481" s="1" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A482" s="1" t="s">
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483" s="2">
+        <v>35189008</v>
+      </c>
+      <c r="B483" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B482" s="1" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A483" s="1" t="s">
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484" s="2">
+        <v>21742241</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A484" s="1" t="s">
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485" s="2">
+        <v>24879167</v>
+      </c>
+      <c r="B485" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B484" s="1" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A485" s="1" t="s">
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486" s="2">
+        <v>37297387</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B485" s="1" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A486" s="1" t="s">
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487" s="2">
+        <v>25118471</v>
+      </c>
+      <c r="B487" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A487" s="1" t="s">
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488" s="2">
+        <v>36251995</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B487" s="1" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A488" s="1" t="s">
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" s="2">
+        <v>30631277</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B488" s="1" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A489" s="1" t="s">
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490" s="2">
+        <v>18011287</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A490" s="1" t="s">
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491" s="2">
+        <v>27276160</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B490" s="1" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A491" s="1" t="s">
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492" s="2">
+        <v>25649193</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B491" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A492" s="1" t="s">
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493" s="2">
+        <v>37462200</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B492" s="1" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A493" s="1" t="s">
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494" s="2">
+        <v>34657161</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B493" s="1" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A494" s="1" t="s">
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495" s="2">
+        <v>35857624</v>
+      </c>
+      <c r="B495" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B494" s="1" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A495" s="1" t="s">
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496" s="2">
+        <v>35506984</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B495" s="1" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A496" s="1" t="s">
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497" s="2">
+        <v>24795163</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B496" s="1" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A497" s="1" t="s">
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498" s="2">
+        <v>31633471</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B497" s="1" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A498" s="1" t="s">
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499" s="2">
+        <v>31871375</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A499" s="1" t="s">
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500" s="2">
+        <v>28904783</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B499" s="1" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A500" s="1" t="s">
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501" s="2">
+        <v>37298151</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B500" s="1" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A501" s="1" t="s">
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502" s="2">
+        <v>24793376</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B501" s="1" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A502" s="1" t="s">
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503" s="2">
+        <v>23634370</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B502" s="1" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A503" s="1" t="s">
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504" s="2">
+        <v>23381812</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B503" s="1" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A504" s="1" t="s">
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505" s="2">
+        <v>23488413</v>
+      </c>
+      <c r="B505" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A505" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
@@ -7286,7 +5853,7 @@
         <v>26287740</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>963</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Educacion\Desktop\constancia 22 junio impulso educativo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6880FF98-DEAE-4598-852A-9B927F5E7A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D638C-5725-47BA-B4B2-5655CD3AA9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="825" windowWidth="16020" windowHeight="10095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="225" windowWidth="12765" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="497">
   <si>
     <t>Nombre</t>
   </si>
@@ -1483,6 +1483,39 @@
   </si>
   <si>
     <t>DOMINGUEZ MARIA TERESA</t>
+  </si>
+  <si>
+    <t>39182456</t>
+  </si>
+  <si>
+    <t>PEREZ HERNANDEZ PAULA VALERIA</t>
+  </si>
+  <si>
+    <t>21358069</t>
+  </si>
+  <si>
+    <t>PEREIRA MARCELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>22107249</t>
+  </si>
+  <si>
+    <t>26510108</t>
+  </si>
+  <si>
+    <t>LUNA LOPEZ MARIA CELESTE</t>
+  </si>
+  <si>
+    <t>29174845</t>
+  </si>
+  <si>
+    <t>VARGAS YANINA SABRINA</t>
+  </si>
+  <si>
+    <t>36911521</t>
+  </si>
+  <si>
+    <t>OLMEDO ANDRADA PABLO AGUSTIN</t>
   </si>
 </sst>
 </file>
@@ -1518,10 +1551,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1802,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -1817,7 +1849,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>30631696</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1825,7 +1857,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>27196572</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1833,7 +1865,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4">
         <v>20465404</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1841,7 +1873,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5">
         <v>23071321</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1849,7 +1881,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6">
         <v>36864805</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1857,7 +1889,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7">
         <v>33438505</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1865,7 +1897,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8">
         <v>23058073</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1873,7 +1905,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9">
         <v>25252365</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1881,7 +1913,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10">
         <v>22958332</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1889,7 +1921,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11">
         <v>21955804</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1897,7 +1929,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12">
         <v>33629423</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1905,7 +1937,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13">
         <v>39009689</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1913,7 +1945,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14">
         <v>20634242</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1921,7 +1953,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15">
         <v>20448237</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1929,7 +1961,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16">
         <v>22159296</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1937,7 +1969,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17">
         <v>24879536</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1945,7 +1977,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18">
         <v>30091185</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1953,7 +1985,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19">
         <v>35848352</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1961,7 +1993,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20">
         <v>38463632</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1969,7 +2001,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21">
         <v>22997121</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1977,7 +2009,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22">
         <v>24948758</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1985,7 +2017,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23">
         <v>20969813</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1993,7 +2025,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24">
         <v>33047056</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -2001,7 +2033,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25">
         <v>22754820</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2009,7 +2041,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26">
         <v>20801301</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2017,7 +2049,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27">
         <v>38459487</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2025,7 +2057,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28">
         <v>25830677</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2033,7 +2065,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29">
         <v>40779269</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2041,7 +2073,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30">
         <v>20131102</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2049,7 +2081,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31">
         <v>27196571</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2057,7 +2089,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32">
         <v>25859978</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2065,7 +2097,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33">
         <v>28720645</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2073,7 +2105,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34">
         <v>39376818</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2081,7 +2113,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35">
         <v>28478006</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2089,7 +2121,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36">
         <v>25649151</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2097,7 +2129,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37">
         <v>39182272</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2105,7 +2137,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38">
         <v>33848770</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2113,7 +2145,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39">
         <v>35849088</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2121,7 +2153,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40">
         <v>24689578</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2129,7 +2161,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41">
         <v>24343120</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2137,7 +2169,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42">
         <v>31227295</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2145,7 +2177,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43">
         <v>28836394</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -2153,7 +2185,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44">
         <v>22014234</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -2161,7 +2193,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45">
         <v>22959661</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2169,7 +2201,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46">
         <v>34696809</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2177,7 +2209,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47">
         <v>29835342</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -2185,7 +2217,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48">
         <v>26287329</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -2193,7 +2225,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49">
         <v>20942703</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -2201,7 +2233,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50">
         <v>20279612</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -2209,7 +2241,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="A51">
         <v>39376371</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -2217,7 +2249,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52">
         <v>21361485</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -2225,7 +2257,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="A53">
         <v>21955849</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -2233,7 +2265,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="A54">
         <v>24091572</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -2241,7 +2273,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55">
         <v>23380244</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -2249,7 +2281,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56">
         <v>30690077</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -2257,7 +2289,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57">
         <v>38015504</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -2265,7 +2297,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="A58">
         <v>22159164</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -2273,7 +2305,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="A59">
         <v>38079089</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -2281,7 +2313,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="A60">
         <v>23381615</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -2289,7 +2321,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="A61">
         <v>37833876</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -2297,7 +2329,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="A62">
         <v>25823517</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -2305,7 +2337,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63">
         <v>31065160</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -2313,7 +2345,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64">
         <v>26629513</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -2321,7 +2353,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65">
         <v>35507732</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -2329,7 +2361,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66">
         <v>27379145</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -2337,7 +2369,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67">
         <v>23545081</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -2345,7 +2377,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68">
         <v>26287544</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -2353,7 +2385,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69">
         <v>21361842</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -2361,7 +2393,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70">
         <v>23977864</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -2369,7 +2401,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="A71">
         <v>22218270</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -2377,7 +2409,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72">
         <v>30805061</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -2385,7 +2417,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="A73">
         <v>21994008</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -2393,7 +2425,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74">
         <v>25939077</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -2401,7 +2433,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75">
         <v>27350993</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -2409,7 +2441,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76">
         <v>28786182</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -2417,7 +2449,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="A77">
         <v>23735654</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -2425,7 +2457,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78">
         <v>24266803</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -2433,7 +2465,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79">
         <v>17120081</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -2441,7 +2473,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80">
         <v>29351642</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -2449,7 +2481,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="A81">
         <v>30157608</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -2457,7 +2489,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="A82">
         <v>41272329</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -2465,7 +2497,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="A83">
         <v>29911944</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -2473,7 +2505,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="A84">
         <v>21357726</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -2481,7 +2513,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="A85">
         <v>29149294</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -2489,7 +2521,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="A86">
         <v>24362061</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -2497,7 +2529,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="A87">
         <v>43763679</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -2505,7 +2537,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="A88">
         <v>20943569</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -2513,7 +2545,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="A89">
         <v>26678946</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -2521,7 +2553,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="A90">
         <v>33319111</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -2529,7 +2561,7 @@
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="A91">
         <v>32723512</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -2537,7 +2569,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="A92">
         <v>24244922</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -2545,7 +2577,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="A93">
         <v>24234998</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -2561,7 +2593,7 @@
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="A95">
         <v>23545310</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -2569,7 +2601,7 @@
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="A96">
         <v>22358149</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -2577,7 +2609,7 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97">
         <v>36253033</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -2585,7 +2617,7 @@
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="A98">
         <v>33018441</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -2593,7 +2625,7 @@
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="A99">
         <v>36424177</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -2601,7 +2633,7 @@
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="A100">
         <v>32627275</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -2609,7 +2641,7 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="A101">
         <v>31510692</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -2617,7 +2649,7 @@
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="A102">
         <v>39954847</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -2625,7 +2657,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="A103">
         <v>21361920</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -2633,7 +2665,7 @@
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="A104">
         <v>40995577</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -2641,7 +2673,7 @@
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="A105">
         <v>29507880</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -2649,7 +2681,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="A106">
         <v>17505151</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -2657,7 +2689,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="A107">
         <v>22358123</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -2665,7 +2697,7 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="A108">
         <v>24168512</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -2673,7 +2705,7 @@
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="A109">
         <v>24793449</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -2681,7 +2713,7 @@
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="A110">
         <v>20303185</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -2689,7 +2721,7 @@
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="A111">
         <v>26878138</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -2697,7 +2729,7 @@
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="A112">
         <v>32399820</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -2705,7 +2737,7 @@
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="A113">
         <v>27548540</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -2713,7 +2745,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="A114">
         <v>28487592</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -2721,7 +2753,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="A115">
         <v>23840920</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -2729,7 +2761,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="A116">
         <v>34194266</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -2737,7 +2769,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="A117">
         <v>31510814</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -2745,7 +2777,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="A118">
         <v>42081919</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -2753,7 +2785,7 @@
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="A119">
         <v>24948199</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -2761,7 +2793,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="A120">
         <v>22227351</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -2769,7 +2801,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="A121">
         <v>23752125</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -2777,7 +2809,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="A122">
         <v>32083615</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -2785,7 +2817,7 @@
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="A123">
         <v>37531313</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -2793,7 +2825,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="A124">
         <v>38075082</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -2801,7 +2833,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="A125">
         <v>39376722</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -2809,7 +2841,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="A126">
         <v>28888597</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -2817,7 +2849,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="A127">
         <v>23380997</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -2825,7 +2857,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="A128">
         <v>29636852</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -2833,7 +2865,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="A129">
         <v>23058124</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -2841,7 +2873,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="A130">
         <v>20444577</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -2849,7 +2881,7 @@
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="A131">
         <v>23498367</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -2857,7 +2889,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="A132">
         <v>23638504</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -2865,7 +2897,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="A133">
         <v>24234660</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -2873,7 +2905,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="A134">
         <v>42356698</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -2881,7 +2913,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="A135">
         <v>21357987</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -2889,7 +2921,7 @@
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="A136">
         <v>32354486</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -2897,7 +2929,7 @@
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="A137">
         <v>22958612</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -2905,7 +2937,7 @@
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="A138">
         <v>24724157</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -2913,7 +2945,7 @@
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="A139">
         <v>22227448</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -2921,7 +2953,7 @@
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="A140">
         <v>23634505</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -2929,7 +2961,7 @@
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="A141">
         <v>21609851</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -2937,7 +2969,7 @@
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="A142">
         <v>35857151</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -2945,7 +2977,7 @@
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="A143">
         <v>39651378</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -2953,7 +2985,7 @@
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="A144">
         <v>22815124</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -2961,7 +2993,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="A145">
         <v>21625757</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -2969,7 +3001,7 @@
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="A146">
         <v>24480169</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -2977,7 +3009,7 @@
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="A147">
         <v>29690710</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -2985,7 +3017,7 @@
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="A148">
         <v>24658216</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -2993,7 +3025,7 @@
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="A149">
         <v>35209877</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -3001,7 +3033,7 @@
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="A150">
         <v>34698237</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -3009,7 +3041,7 @@
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="A151">
         <v>38219512</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -3017,7 +3049,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="A152">
         <v>31185857</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -3025,7 +3057,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="A153">
         <v>24689513</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -3033,7 +3065,7 @@
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="A154">
         <v>23381514</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -3041,7 +3073,7 @@
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="A155">
         <v>24972023</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -3049,7 +3081,7 @@
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="A156">
         <v>20303267</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -3057,7 +3089,7 @@
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="A157">
         <v>32352838</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -3065,7 +3097,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="A158">
         <v>21742130</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -3073,7 +3105,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="A159">
         <v>28005299</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -3081,7 +3113,7 @@
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="A160">
         <v>25549517</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -3089,7 +3121,7 @@
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="A161">
         <v>24362216</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -3097,7 +3129,7 @@
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="A162">
         <v>39424964</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -3105,7 +3137,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="A163">
         <v>20303279</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -3113,7 +3145,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="A164">
         <v>31642578</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -3121,7 +3153,7 @@
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="A165">
         <v>34918289</v>
       </c>
       <c r="B165" s="1" t="s">
@@ -3129,7 +3161,7 @@
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="A166">
         <v>43763381</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -3137,7 +3169,7 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="A167">
         <v>30152625</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -3145,7 +3177,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="A168">
         <v>29351681</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -3153,7 +3185,7 @@
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="A169">
         <v>22227237</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -3161,7 +3193,7 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="A170">
         <v>21181901</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -3169,7 +3201,7 @@
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="A171">
         <v>36864641</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -3177,7 +3209,7 @@
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="A172">
         <v>36864870</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -3185,7 +3217,7 @@
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
+      <c r="A173">
         <v>30483503</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -3193,7 +3225,7 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="A174">
         <v>33336188</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -3201,7 +3233,7 @@
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="A175">
         <v>20942624</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -3209,7 +3241,7 @@
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="A176">
         <v>20802105</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -3217,7 +3249,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="A177">
         <v>34245270</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -3225,7 +3257,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="A178">
         <v>23977606</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -3233,7 +3265,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="A179">
         <v>22291718</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -3241,7 +3273,7 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="A180">
         <v>36031750</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -3249,7 +3281,7 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="A181">
         <v>29889291</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -3257,7 +3289,7 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+      <c r="A182">
         <v>14961536</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -3265,7 +3297,7 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="A183">
         <v>31510739</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -3273,7 +3305,7 @@
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+      <c r="A184">
         <v>22659477</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -3281,7 +3313,7 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="A185">
         <v>35510657</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -3289,7 +3321,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+      <c r="A186">
         <v>21362663</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -3297,7 +3329,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+      <c r="A187">
         <v>31621878</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -3305,7 +3337,7 @@
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
+      <c r="A188">
         <v>22788303</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -3313,7 +3345,7 @@
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
+      <c r="A189">
         <v>37742935</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -3321,7 +3353,7 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
+      <c r="A190">
         <v>22788270</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -3329,7 +3361,7 @@
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
+      <c r="A191">
         <v>24972336</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -3337,7 +3369,7 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
+      <c r="A192">
         <v>32095401</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -3345,7 +3377,7 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
+      <c r="A193">
         <v>22168783</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -3353,7 +3385,7 @@
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
+      <c r="A194">
         <v>30071374</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -3361,7 +3393,7 @@
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
+      <c r="A195">
         <v>38593260</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -3369,7 +3401,7 @@
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
+      <c r="A196">
         <v>26527791</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -3377,7 +3409,7 @@
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
+      <c r="A197">
         <v>22157191</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -3385,7 +3417,7 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
+      <c r="A198">
         <v>34920278</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -3393,7 +3425,7 @@
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
+      <c r="A199">
         <v>22358400</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -3401,7 +3433,7 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
+      <c r="A200">
         <v>26880974</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -3409,7 +3441,7 @@
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
+      <c r="A201">
         <v>25412637</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -3417,7 +3449,7 @@
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
+      <c r="A202">
         <v>25405703</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -3425,7 +3457,7 @@
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
+      <c r="A203">
         <v>25321998</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -3433,7 +3465,7 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
+      <c r="A204">
         <v>28595959</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -3441,7 +3473,7 @@
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
+      <c r="A205">
         <v>24234594</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -3449,7 +3481,7 @@
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
+      <c r="A206">
         <v>17592148</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -3457,7 +3489,7 @@
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
+      <c r="A207">
         <v>26611055</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -3465,7 +3497,7 @@
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
+      <c r="A208">
         <v>30819377</v>
       </c>
       <c r="B208" s="1" t="s">
@@ -3473,7 +3505,7 @@
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
+      <c r="A209">
         <v>35852581</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -3481,7 +3513,7 @@
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" s="2">
+      <c r="A210">
         <v>24362575</v>
       </c>
       <c r="B210" s="1" t="s">
@@ -3489,7 +3521,7 @@
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
+      <c r="A211">
         <v>24362494</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -3497,7 +3529,7 @@
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
+      <c r="A212">
         <v>21361349</v>
       </c>
       <c r="B212" s="1" t="s">
@@ -3505,7 +3537,7 @@
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="2">
+      <c r="A213">
         <v>27276036</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -3513,7 +3545,7 @@
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="2">
+      <c r="A214">
         <v>25252170</v>
       </c>
       <c r="B214" s="1" t="s">
@@ -3521,7 +3553,7 @@
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
+      <c r="A215">
         <v>27047787</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -3529,7 +3561,7 @@
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="2">
+      <c r="A216">
         <v>35735583</v>
       </c>
       <c r="B216" s="1" t="s">
@@ -3537,7 +3569,7 @@
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
+      <c r="A217">
         <v>34059920</v>
       </c>
       <c r="B217" s="1" t="s">
@@ -3545,7 +3577,7 @@
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
+      <c r="A218">
         <v>26287080</v>
       </c>
       <c r="B218" s="1" t="s">
@@ -3553,7 +3585,7 @@
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" s="2">
+      <c r="A219">
         <v>32748561</v>
       </c>
       <c r="B219" s="1" t="s">
@@ -3561,7 +3593,7 @@
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
+      <c r="A220">
         <v>34100810</v>
       </c>
       <c r="B220" s="1" t="s">
@@ -3569,7 +3601,7 @@
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
+      <c r="A221">
         <v>26175061</v>
       </c>
       <c r="B221" s="1" t="s">
@@ -3577,7 +3609,7 @@
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
+      <c r="A222">
         <v>32808204</v>
       </c>
       <c r="B222" s="1" t="s">
@@ -3585,7 +3617,7 @@
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
+      <c r="A223">
         <v>26288259</v>
       </c>
       <c r="B223" s="1" t="s">
@@ -3593,7 +3625,7 @@
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
+      <c r="A224">
         <v>33836577</v>
       </c>
       <c r="B224" s="1" t="s">
@@ -3601,7 +3633,7 @@
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
+      <c r="A225">
         <v>36254114</v>
       </c>
       <c r="B225" s="1" t="s">
@@ -3609,7 +3641,7 @@
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
+      <c r="A226">
         <v>37627564</v>
       </c>
       <c r="B226" s="1" t="s">
@@ -3617,7 +3649,7 @@
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
+      <c r="A227">
         <v>34918277</v>
       </c>
       <c r="B227" s="1" t="s">
@@ -3625,7 +3657,7 @@
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
+      <c r="A228">
         <v>23027912</v>
       </c>
       <c r="B228" s="1" t="s">
@@ -3633,7 +3665,7 @@
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
+      <c r="A229">
         <v>31870932</v>
       </c>
       <c r="B229" s="1" t="s">
@@ -3641,7 +3673,7 @@
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
+      <c r="A230">
         <v>22958944</v>
       </c>
       <c r="B230" s="1" t="s">
@@ -3649,7 +3681,7 @@
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
+      <c r="A231">
         <v>37741946</v>
       </c>
       <c r="B231" s="1" t="s">
@@ -3657,7 +3689,7 @@
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
+      <c r="A232">
         <v>41321909</v>
       </c>
       <c r="B232" s="1" t="s">
@@ -3665,7 +3697,7 @@
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
+      <c r="A233">
         <v>23016360</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -3673,7 +3705,7 @@
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
+      <c r="A234">
         <v>23545310</v>
       </c>
       <c r="B234" s="1" t="s">
@@ -3681,7 +3713,7 @@
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
+      <c r="A235">
         <v>22358149</v>
       </c>
       <c r="B235" s="1" t="s">
@@ -3689,7 +3721,7 @@
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
+      <c r="A236">
         <v>36253033</v>
       </c>
       <c r="B236" s="1" t="s">
@@ -3697,7 +3729,7 @@
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
+      <c r="A237">
         <v>33018441</v>
       </c>
       <c r="B237" s="1" t="s">
@@ -3705,7 +3737,7 @@
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
+      <c r="A238">
         <v>36424177</v>
       </c>
       <c r="B238" s="1" t="s">
@@ -3713,7 +3745,7 @@
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
+      <c r="A239">
         <v>32627275</v>
       </c>
       <c r="B239" s="1" t="s">
@@ -3721,7 +3753,7 @@
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
+      <c r="A240">
         <v>31510692</v>
       </c>
       <c r="B240" s="1" t="s">
@@ -3729,7 +3761,7 @@
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
+      <c r="A241">
         <v>39954847</v>
       </c>
       <c r="B241" s="1" t="s">
@@ -3737,7 +3769,7 @@
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
+      <c r="A242">
         <v>21361920</v>
       </c>
       <c r="B242" s="1" t="s">
@@ -3745,7 +3777,7 @@
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" s="2">
+      <c r="A243">
         <v>40995577</v>
       </c>
       <c r="B243" s="1" t="s">
@@ -3753,7 +3785,7 @@
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
+      <c r="A244">
         <v>29507880</v>
       </c>
       <c r="B244" s="1" t="s">
@@ -3761,7 +3793,7 @@
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="2">
+      <c r="A245">
         <v>17505151</v>
       </c>
       <c r="B245" s="1" t="s">
@@ -3769,7 +3801,7 @@
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
+      <c r="A246">
         <v>22358123</v>
       </c>
       <c r="B246" s="1" t="s">
@@ -3777,7 +3809,7 @@
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" s="2">
+      <c r="A247">
         <v>24168512</v>
       </c>
       <c r="B247" s="1" t="s">
@@ -3785,7 +3817,7 @@
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
+      <c r="A248">
         <v>24793449</v>
       </c>
       <c r="B248" s="1" t="s">
@@ -3793,7 +3825,7 @@
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
+      <c r="A249">
         <v>20303185</v>
       </c>
       <c r="B249" s="1" t="s">
@@ -3801,7 +3833,7 @@
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
+      <c r="A250">
         <v>26878138</v>
       </c>
       <c r="B250" s="1" t="s">
@@ -3809,7 +3841,7 @@
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
+      <c r="A251">
         <v>32399820</v>
       </c>
       <c r="B251" s="1" t="s">
@@ -3817,7 +3849,7 @@
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
+      <c r="A252">
         <v>27548540</v>
       </c>
       <c r="B252" s="1" t="s">
@@ -3825,7 +3857,7 @@
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="2">
+      <c r="A253">
         <v>28487592</v>
       </c>
       <c r="B253" s="1" t="s">
@@ -3833,7 +3865,7 @@
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" s="2">
+      <c r="A254">
         <v>23840920</v>
       </c>
       <c r="B254" s="1" t="s">
@@ -3841,7 +3873,7 @@
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" s="2">
+      <c r="A255">
         <v>34194266</v>
       </c>
       <c r="B255" s="1" t="s">
@@ -3849,7 +3881,7 @@
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256" s="2">
+      <c r="A256">
         <v>24283743</v>
       </c>
       <c r="B256" s="1" t="s">
@@ -3857,7 +3889,7 @@
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257" s="2">
+      <c r="A257">
         <v>36252044</v>
       </c>
       <c r="B257" s="1" t="s">
@@ -3865,7 +3897,7 @@
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258" s="2">
+      <c r="A258">
         <v>44665690</v>
       </c>
       <c r="B258" s="1" t="s">
@@ -3873,7 +3905,7 @@
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259" s="2">
+      <c r="A259">
         <v>22063346</v>
       </c>
       <c r="B259" s="1" t="s">
@@ -3881,7 +3913,7 @@
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260" s="2">
+      <c r="A260">
         <v>33058571</v>
       </c>
       <c r="B260" s="1" t="s">
@@ -3889,7 +3921,7 @@
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261" s="2">
+      <c r="A261">
         <v>18357372</v>
       </c>
       <c r="B261" s="1" t="s">
@@ -3897,7 +3929,7 @@
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262" s="2">
+      <c r="A262">
         <v>42917666</v>
       </c>
       <c r="B262" s="1" t="s">
@@ -3905,7 +3937,7 @@
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263" s="2">
+      <c r="A263">
         <v>27685008</v>
       </c>
       <c r="B263" s="1" t="s">
@@ -3913,7 +3945,7 @@
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="2">
+      <c r="A264">
         <v>38764011</v>
       </c>
       <c r="B264" s="1" t="s">
@@ -3921,7 +3953,7 @@
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="2">
+      <c r="A265">
         <v>25412179</v>
       </c>
       <c r="B265" s="1" t="s">
@@ -3929,7 +3961,7 @@
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="2">
+      <c r="A266">
         <v>28262734</v>
       </c>
       <c r="B266" s="1" t="s">
@@ -3937,7 +3969,7 @@
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="2">
+      <c r="A267">
         <v>22289822</v>
       </c>
       <c r="B267" s="1" t="s">
@@ -3945,7 +3977,7 @@
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="2">
+      <c r="A268">
         <v>32808204</v>
       </c>
       <c r="B268" s="1" t="s">
@@ -3953,7 +3985,7 @@
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="2">
+      <c r="A269">
         <v>38461651</v>
       </c>
       <c r="B269" s="1" t="s">
@@ -3961,7 +3993,7 @@
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="2">
+      <c r="A270">
         <v>30839346</v>
       </c>
       <c r="B270" s="1" t="s">
@@ -3969,7 +4001,7 @@
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="2">
+      <c r="A271">
         <v>22011661</v>
       </c>
       <c r="B271" s="1" t="s">
@@ -3977,7 +4009,7 @@
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="2">
+      <c r="A272">
         <v>23982667</v>
       </c>
       <c r="B272" s="1" t="s">
@@ -3985,7 +4017,7 @@
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="2">
+      <c r="A273">
         <v>21358069</v>
       </c>
       <c r="B273" s="1" t="s">
@@ -3993,7 +4025,7 @@
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="2">
+      <c r="A274">
         <v>35505636</v>
       </c>
       <c r="B274" s="1" t="s">
@@ -4001,7 +4033,7 @@
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="2">
+      <c r="A275">
         <v>94120990</v>
       </c>
       <c r="B275" s="1" t="s">
@@ -4009,7 +4041,7 @@
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="2">
+      <c r="A276">
         <v>36423198</v>
       </c>
       <c r="B276" s="1" t="s">
@@ -4017,7 +4049,7 @@
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="2">
+      <c r="A277">
         <v>24168538</v>
       </c>
       <c r="B277" s="1" t="s">
@@ -4025,7 +4057,7 @@
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="2">
+      <c r="A278">
         <v>28720656</v>
       </c>
       <c r="B278" s="1" t="s">
@@ -4033,7 +4065,7 @@
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="2">
+      <c r="A279">
         <v>35923623</v>
       </c>
       <c r="B279" s="1" t="s">
@@ -4041,7 +4073,7 @@
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="2">
+      <c r="A280">
         <v>32454491</v>
       </c>
       <c r="B280" s="1" t="s">
@@ -4049,7 +4081,7 @@
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="2">
+      <c r="A281">
         <v>22003244</v>
       </c>
       <c r="B281" s="1" t="s">
@@ -4057,7 +4089,7 @@
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282" s="2">
+      <c r="A282">
         <v>24426178</v>
       </c>
       <c r="B282" s="1" t="s">
@@ -4065,7 +4097,7 @@
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283" s="2">
+      <c r="A283">
         <v>24691206</v>
       </c>
       <c r="B283" s="1" t="s">
@@ -4073,7 +4105,7 @@
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284" s="2">
+      <c r="A284">
         <v>28538570</v>
       </c>
       <c r="B284" s="1" t="s">
@@ -4081,7 +4113,7 @@
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285" s="2">
+      <c r="A285">
         <v>40470047</v>
       </c>
       <c r="B285" s="1" t="s">
@@ -4089,7 +4121,7 @@
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286" s="2">
+      <c r="A286">
         <v>23027976</v>
       </c>
       <c r="B286" s="1" t="s">
@@ -4097,7 +4129,7 @@
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287" s="2">
+      <c r="A287">
         <v>31324264</v>
       </c>
       <c r="B287" s="1" t="s">
@@ -4105,7 +4137,7 @@
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288" s="2">
+      <c r="A288">
         <v>20943378</v>
       </c>
       <c r="B288" s="1" t="s">
@@ -4113,7 +4145,7 @@
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289" s="2">
+      <c r="A289">
         <v>36034749</v>
       </c>
       <c r="B289" s="1" t="s">
@@ -4121,7 +4153,7 @@
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290" s="2">
+      <c r="A290">
         <v>30246776</v>
       </c>
       <c r="B290" s="1" t="s">
@@ -4129,7 +4161,7 @@
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" s="2">
+      <c r="A291">
         <v>39183400</v>
       </c>
       <c r="B291" s="1" t="s">
@@ -4137,7 +4169,7 @@
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" s="2">
+      <c r="A292">
         <v>42516938</v>
       </c>
       <c r="B292" s="1" t="s">
@@ -4145,7 +4177,7 @@
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" s="2">
+      <c r="A293">
         <v>22957809</v>
       </c>
       <c r="B293" s="1" t="s">
@@ -4153,7 +4185,7 @@
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" s="2">
+      <c r="A294">
         <v>38592131</v>
       </c>
       <c r="B294" s="1" t="s">
@@ -4161,7 +4193,7 @@
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" s="2">
+      <c r="A295">
         <v>22359886</v>
       </c>
       <c r="B295" s="1" t="s">
@@ -4169,7 +4201,7 @@
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" s="2">
+      <c r="A296">
         <v>24689413</v>
       </c>
       <c r="B296" s="1" t="s">
@@ -4177,7 +4209,7 @@
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" s="2">
+      <c r="A297">
         <v>40592734</v>
       </c>
       <c r="B297" s="1" t="s">
@@ -4185,7 +4217,7 @@
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" s="2">
+      <c r="A298">
         <v>29098020</v>
       </c>
       <c r="B298" s="1" t="s">
@@ -4193,7 +4225,7 @@
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" s="2">
+      <c r="A299">
         <v>22014027</v>
       </c>
       <c r="B299" s="1" t="s">
@@ -4201,7 +4233,7 @@
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" s="2">
+      <c r="A300">
         <v>25321963</v>
       </c>
       <c r="B300" s="1" t="s">
@@ -4209,7 +4241,7 @@
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" s="2">
+      <c r="A301">
         <v>25823793</v>
       </c>
       <c r="B301" s="1" t="s">
@@ -4217,7 +4249,7 @@
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" s="2">
+      <c r="A302">
         <v>25939441</v>
       </c>
       <c r="B302" s="1" t="s">
@@ -4225,7 +4257,7 @@
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" s="2">
+      <c r="A303">
         <v>37924320</v>
       </c>
       <c r="B303" s="1" t="s">
@@ -4233,7 +4265,7 @@
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" s="2">
+      <c r="A304">
         <v>23791715</v>
       </c>
       <c r="B304" s="1" t="s">
@@ -4241,7 +4273,7 @@
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" s="2">
+      <c r="A305">
         <v>25991951</v>
       </c>
       <c r="B305" s="1" t="s">
@@ -4249,7 +4281,7 @@
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" s="2">
+      <c r="A306">
         <v>33960311</v>
       </c>
       <c r="B306" s="1" t="s">
@@ -4257,7 +4289,7 @@
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" s="2">
+      <c r="A307">
         <v>24266713</v>
       </c>
       <c r="B307" s="1" t="s">
@@ -4265,7 +4297,7 @@
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" s="2">
+      <c r="A308">
         <v>24464114</v>
       </c>
       <c r="B308" s="1" t="s">
@@ -4273,7 +4305,7 @@
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" s="2">
+      <c r="A309">
         <v>22159387</v>
       </c>
       <c r="B309" s="1" t="s">
@@ -4281,7 +4313,7 @@
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" s="2">
+      <c r="A310">
         <v>17078888</v>
       </c>
       <c r="B310" s="1" t="s">
@@ -4289,7 +4321,7 @@
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" s="2">
+      <c r="A311">
         <v>23545633</v>
       </c>
       <c r="B311" s="1" t="s">
@@ -4297,7 +4329,7 @@
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" s="2">
+      <c r="A312">
         <v>26511903</v>
       </c>
       <c r="B312" s="1" t="s">
@@ -4305,7 +4337,7 @@
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" s="2">
+      <c r="A313">
         <v>20655436</v>
       </c>
       <c r="B313" s="1" t="s">
@@ -4313,7 +4345,7 @@
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" s="2">
+      <c r="A314">
         <v>38460901</v>
       </c>
       <c r="B314" s="1" t="s">
@@ -4321,7 +4353,7 @@
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" s="2">
+      <c r="A315">
         <v>24972537</v>
       </c>
       <c r="B315" s="1" t="s">
@@ -4329,7 +4361,7 @@
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" s="2">
+      <c r="A316">
         <v>36034208</v>
       </c>
       <c r="B316" s="1" t="s">
@@ -4337,7 +4369,7 @@
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" s="2">
+      <c r="A317">
         <v>24091818</v>
       </c>
       <c r="B317" s="1" t="s">
@@ -4345,7 +4377,7 @@
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" s="2">
+      <c r="A318">
         <v>23735583</v>
       </c>
       <c r="B318" s="1" t="s">
@@ -4353,7 +4385,7 @@
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" s="2">
+      <c r="A319">
         <v>27350486</v>
       </c>
       <c r="B319" s="1" t="s">
@@ -4361,7 +4393,7 @@
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" s="2">
+      <c r="A320">
         <v>29358159</v>
       </c>
       <c r="B320" s="1" t="s">
@@ -4369,7 +4401,7 @@
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" s="2">
+      <c r="A321">
         <v>40368952</v>
       </c>
       <c r="B321" s="1" t="s">
@@ -4377,7 +4409,7 @@
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" s="2">
+      <c r="A322">
         <v>28967371</v>
       </c>
       <c r="B322" s="1" t="s">
@@ -4385,7 +4417,7 @@
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" s="2">
+      <c r="A323">
         <v>23545559</v>
       </c>
       <c r="B323" s="1" t="s">
@@ -4393,7 +4425,7 @@
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" s="2">
+      <c r="A324">
         <v>21362237</v>
       </c>
       <c r="B324" s="1" t="s">
@@ -4401,7 +4433,7 @@
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" s="2">
+      <c r="A325">
         <v>21926671</v>
       </c>
       <c r="B325" s="1" t="s">
@@ -4409,7 +4441,7 @@
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" s="2">
+      <c r="A326">
         <v>31005272</v>
       </c>
       <c r="B326" s="1" t="s">
@@ -4417,7 +4449,7 @@
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" s="2">
+      <c r="A327">
         <v>24689541</v>
       </c>
       <c r="B327" s="1" t="s">
@@ -4425,7 +4457,7 @@
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" s="2">
+      <c r="A328">
         <v>24948406</v>
       </c>
       <c r="B328" s="1" t="s">
@@ -4433,7 +4465,7 @@
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" s="2">
+      <c r="A329">
         <v>34697514</v>
       </c>
       <c r="B329" s="1" t="s">
@@ -4441,7 +4473,7 @@
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" s="2">
+      <c r="A330">
         <v>28040884</v>
       </c>
       <c r="B330" s="1" t="s">
@@ -4449,7 +4481,7 @@
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" s="2">
+      <c r="A331">
         <v>22714928</v>
       </c>
       <c r="B331" s="1" t="s">
@@ -4457,7 +4489,7 @@
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" s="2">
+      <c r="A332">
         <v>22063563</v>
       </c>
       <c r="B332" s="1" t="s">
@@ -4465,7 +4497,7 @@
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333" s="2">
+      <c r="A333">
         <v>32353281</v>
       </c>
       <c r="B333" s="1" t="s">
@@ -4473,7 +4505,7 @@
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334" s="2">
+      <c r="A334">
         <v>21895303</v>
       </c>
       <c r="B334" s="1" t="s">
@@ -4481,7 +4513,7 @@
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="2">
+      <c r="A335">
         <v>23380945</v>
       </c>
       <c r="B335" s="1" t="s">
@@ -4489,7 +4521,7 @@
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="2">
+      <c r="A336">
         <v>34915707</v>
       </c>
       <c r="B336" s="1" t="s">
@@ -4497,7 +4529,7 @@
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="2">
+      <c r="A337">
         <v>29165845</v>
       </c>
       <c r="B337" s="1" t="s">
@@ -4505,7 +4537,7 @@
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="2">
+      <c r="A338">
         <v>37506972</v>
       </c>
       <c r="B338" s="1" t="s">
@@ -4513,7 +4545,7 @@
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="2">
+      <c r="A339">
         <v>30725182</v>
       </c>
       <c r="B339" s="1" t="s">
@@ -4521,7 +4553,7 @@
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="2">
+      <c r="A340">
         <v>29302709</v>
       </c>
       <c r="B340" s="1" t="s">
@@ -4529,7 +4561,7 @@
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="2">
+      <c r="A341">
         <v>32083544</v>
       </c>
       <c r="B341" s="1" t="s">
@@ -4537,7 +4569,7 @@
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" s="2">
+      <c r="A342">
         <v>21181864</v>
       </c>
       <c r="B342" s="1" t="s">
@@ -4545,7 +4577,7 @@
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" s="2">
+      <c r="A343">
         <v>32860358</v>
       </c>
       <c r="B343" s="1" t="s">
@@ -4553,7 +4585,7 @@
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" s="2">
+      <c r="A344">
         <v>23634590</v>
       </c>
       <c r="B344" s="1" t="s">
@@ -4561,7 +4593,7 @@
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="2">
+      <c r="A345">
         <v>32693363</v>
       </c>
       <c r="B345" s="1" t="s">
@@ -4569,7 +4601,7 @@
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" s="2">
+      <c r="A346">
         <v>37647939</v>
       </c>
       <c r="B346" s="1" t="s">
@@ -4577,7 +4609,7 @@
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="2">
+      <c r="A347">
         <v>42188332</v>
       </c>
       <c r="B347" s="1" t="s">
@@ -4585,7 +4617,7 @@
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" s="2">
+      <c r="A348">
         <v>29621457</v>
       </c>
       <c r="B348" s="1" t="s">
@@ -4593,7 +4625,7 @@
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" s="2">
+      <c r="A349">
         <v>35209926</v>
       </c>
       <c r="B349" s="1" t="s">
@@ -4601,7 +4633,7 @@
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="2">
+      <c r="A350">
         <v>23735777</v>
       </c>
       <c r="B350" s="1" t="s">
@@ -4609,7 +4641,7 @@
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351" s="2">
+      <c r="A351">
         <v>35852888</v>
       </c>
       <c r="B351" s="1" t="s">
@@ -4617,7 +4649,7 @@
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352" s="2">
+      <c r="A352">
         <v>22705601</v>
       </c>
       <c r="B352" s="1" t="s">
@@ -4625,7 +4657,7 @@
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353" s="2">
+      <c r="A353">
         <v>40779566</v>
       </c>
       <c r="B353" s="1" t="s">
@@ -4633,7 +4665,7 @@
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354" s="2">
+      <c r="A354">
         <v>38462345</v>
       </c>
       <c r="B354" s="1" t="s">
@@ -4641,7 +4673,7 @@
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355" s="2">
+      <c r="A355">
         <v>35209826</v>
       </c>
       <c r="B355" s="1" t="s">
@@ -4649,7 +4681,7 @@
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356" s="2">
+      <c r="A356">
         <v>23378799</v>
       </c>
       <c r="B356" s="1" t="s">
@@ -4657,7 +4689,7 @@
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357" s="2">
+      <c r="A357">
         <v>21591896</v>
       </c>
       <c r="B357" s="1" t="s">
@@ -4665,7 +4697,7 @@
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358" s="2">
+      <c r="A358">
         <v>23381001</v>
       </c>
       <c r="B358" s="1" t="s">
@@ -4673,7 +4705,7 @@
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359" s="2">
+      <c r="A359">
         <v>25135290</v>
       </c>
       <c r="B359" s="1" t="s">
@@ -4681,7 +4713,7 @@
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360" s="2">
+      <c r="A360">
         <v>30157764</v>
       </c>
       <c r="B360" s="1" t="s">
@@ -4689,7 +4721,7 @@
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361" s="2">
+      <c r="A361">
         <v>20386732</v>
       </c>
       <c r="B361" s="1" t="s">
@@ -4697,7 +4729,7 @@
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362" s="2">
+      <c r="A362">
         <v>29774845</v>
       </c>
       <c r="B362" s="1" t="s">
@@ -4705,7 +4737,7 @@
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363" s="2">
+      <c r="A363">
         <v>29176116</v>
       </c>
       <c r="B363" s="1" t="s">
@@ -4713,7 +4745,7 @@
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364" s="2">
+      <c r="A364">
         <v>25462802</v>
       </c>
       <c r="B364" s="1" t="s">
@@ -4721,7 +4753,7 @@
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365" s="2">
+      <c r="A365">
         <v>38460584</v>
       </c>
       <c r="B365" s="1" t="s">
@@ -4729,7 +4761,7 @@
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366" s="2">
+      <c r="A366">
         <v>21113917</v>
       </c>
       <c r="B366" s="1" t="s">
@@ -4737,7 +4769,7 @@
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367" s="2">
+      <c r="A367">
         <v>21331530</v>
       </c>
       <c r="B367" s="1" t="s">
@@ -4745,7 +4777,7 @@
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368" s="2">
+      <c r="A368">
         <v>21359584</v>
       </c>
       <c r="B368" s="1" t="s">
@@ -4753,7 +4785,7 @@
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369" s="2">
+      <c r="A369">
         <v>24426718</v>
       </c>
       <c r="B369" s="1" t="s">
@@ -4761,7 +4793,7 @@
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370" s="2">
+      <c r="A370">
         <v>29740911</v>
       </c>
       <c r="B370" s="1" t="s">
@@ -4769,7 +4801,7 @@
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371" s="2">
+      <c r="A371">
         <v>40592351</v>
       </c>
       <c r="B371" s="1" t="s">
@@ -4777,7 +4809,7 @@
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372" s="2">
+      <c r="A372">
         <v>27350707</v>
       </c>
       <c r="B372" s="1" t="s">
@@ -4785,7 +4817,7 @@
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373" s="2">
+      <c r="A373">
         <v>38217860</v>
       </c>
       <c r="B373" s="1" t="s">
@@ -4793,7 +4825,7 @@
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374" s="2">
+      <c r="A374">
         <v>35736626</v>
       </c>
       <c r="B374" s="1" t="s">
@@ -4801,7 +4833,7 @@
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375" s="2">
+      <c r="A375">
         <v>41157267</v>
       </c>
       <c r="B375" s="1" t="s">
@@ -4809,7 +4841,7 @@
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376" s="2">
+      <c r="A376">
         <v>28263027</v>
       </c>
       <c r="B376" s="1" t="s">
@@ -4817,7 +4849,7 @@
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377" s="2">
+      <c r="A377">
         <v>20943015</v>
       </c>
       <c r="B377" s="1" t="s">
@@ -4825,7 +4857,7 @@
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378" s="2">
+      <c r="A378">
         <v>22227467</v>
       </c>
       <c r="B378" s="1" t="s">
@@ -4833,7 +4865,7 @@
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379" s="2">
+      <c r="A379">
         <v>17470975</v>
       </c>
       <c r="B379" s="1" t="s">
@@ -4841,7 +4873,7 @@
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380" s="2">
+      <c r="A380">
         <v>36250663</v>
       </c>
       <c r="B380" s="1" t="s">
@@ -4849,7 +4881,7 @@
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381" s="2">
+      <c r="A381">
         <v>23638433</v>
       </c>
       <c r="B381" s="1" t="s">
@@ -4857,7 +4889,7 @@
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382" s="2">
+      <c r="A382">
         <v>27685079</v>
       </c>
       <c r="B382" s="1" t="s">
@@ -4865,7 +4897,7 @@
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383" s="2">
+      <c r="A383">
         <v>22107249</v>
       </c>
       <c r="B383" s="1" t="s">
@@ -4873,7 +4905,7 @@
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384" s="2">
+      <c r="A384">
         <v>23721828</v>
       </c>
       <c r="B384" s="1" t="s">
@@ -4881,7 +4913,7 @@
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385" s="2">
+      <c r="A385">
         <v>25167554</v>
       </c>
       <c r="B385" s="1" t="s">
@@ -4889,7 +4921,7 @@
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386" s="2">
+      <c r="A386">
         <v>23977750</v>
       </c>
       <c r="B386" s="1" t="s">
@@ -4897,7 +4929,7 @@
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387" s="2">
+      <c r="A387">
         <v>26590440</v>
       </c>
       <c r="B387" s="1" t="s">
@@ -4905,7 +4937,7 @@
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388" s="2">
+      <c r="A388">
         <v>22658377</v>
       </c>
       <c r="B388" s="1" t="s">
@@ -4913,7 +4945,7 @@
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389" s="2">
+      <c r="A389">
         <v>22998098</v>
       </c>
       <c r="B389" s="1" t="s">
@@ -4921,7 +4953,7 @@
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390" s="2">
+      <c r="A390">
         <v>34754541</v>
       </c>
       <c r="B390" s="1" t="s">
@@ -4929,7 +4961,7 @@
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391" s="2">
+      <c r="A391">
         <v>33022964</v>
       </c>
       <c r="B391" s="1" t="s">
@@ -4937,7 +4969,7 @@
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392" s="2">
+      <c r="A392">
         <v>27682747</v>
       </c>
       <c r="B392" s="1" t="s">
@@ -4945,7 +4977,7 @@
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393" s="2">
+      <c r="A393">
         <v>18582264</v>
       </c>
       <c r="B393" s="1" t="s">
@@ -4953,7 +4985,7 @@
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394" s="2">
+      <c r="A394">
         <v>23634716</v>
       </c>
       <c r="B394" s="1" t="s">
@@ -4961,7 +4993,7 @@
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395" s="2">
+      <c r="A395">
         <v>30542371</v>
       </c>
       <c r="B395" s="1" t="s">
@@ -4969,7 +5001,7 @@
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396" s="2">
+      <c r="A396">
         <v>32353264</v>
       </c>
       <c r="B396" s="1" t="s">
@@ -4977,7 +5009,7 @@
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397" s="2">
+      <c r="A397">
         <v>26678986</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -4985,7 +5017,7 @@
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398" s="2">
+      <c r="A398">
         <v>27043160</v>
       </c>
       <c r="B398" s="1" t="s">
@@ -4993,7 +5025,7 @@
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399" s="2">
+      <c r="A399">
         <v>20132367</v>
       </c>
       <c r="B399" s="1" t="s">
@@ -5001,7 +5033,7 @@
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400" s="2">
+      <c r="A400">
         <v>26643306</v>
       </c>
       <c r="B400" s="1" t="s">
@@ -5009,7 +5041,7 @@
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401" s="2">
+      <c r="A401">
         <v>16210504</v>
       </c>
       <c r="B401" s="1" t="s">
@@ -5017,7 +5049,7 @@
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402" s="2">
+      <c r="A402">
         <v>24693692</v>
       </c>
       <c r="B402" s="1" t="s">
@@ -5025,7 +5057,7 @@
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403" s="2">
+      <c r="A403">
         <v>21592155</v>
       </c>
       <c r="B403" s="1" t="s">
@@ -5033,7 +5065,7 @@
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404" s="2">
+      <c r="A404">
         <v>28487749</v>
       </c>
       <c r="B404" s="1" t="s">
@@ -5041,7 +5073,7 @@
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405" s="2">
+      <c r="A405">
         <v>22754849</v>
       </c>
       <c r="B405" s="1" t="s">
@@ -5049,7 +5081,7 @@
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406" s="2">
+      <c r="A406">
         <v>30839554</v>
       </c>
       <c r="B406" s="1" t="s">
@@ -5057,7 +5089,7 @@
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407" s="2">
+      <c r="A407">
         <v>20275867</v>
       </c>
       <c r="B407" s="1" t="s">
@@ -5065,7 +5097,7 @@
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408" s="2">
+      <c r="A408">
         <v>20935981</v>
       </c>
       <c r="B408" s="1" t="s">
@@ -5073,7 +5105,7 @@
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409" s="2">
+      <c r="A409">
         <v>29149188</v>
       </c>
       <c r="B409" s="1" t="s">
@@ -5081,7 +5113,7 @@
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410" s="2">
+      <c r="A410">
         <v>28005762</v>
       </c>
       <c r="B410" s="1" t="s">
@@ -5089,7 +5121,7 @@
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411" s="2">
+      <c r="A411">
         <v>35381994</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -5097,7 +5129,7 @@
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412" s="2">
+      <c r="A412">
         <v>23134190</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -5105,7 +5137,7 @@
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413" s="2">
+      <c r="A413">
         <v>35192507</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -5113,7 +5145,7 @@
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" s="2">
+      <c r="A414">
         <v>25195096</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -5121,7 +5153,7 @@
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" s="2">
+      <c r="A415">
         <v>23297764</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -5129,7 +5161,7 @@
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416" s="2">
+      <c r="A416">
         <v>29345396</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -5137,7 +5169,7 @@
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417" s="2">
+      <c r="A417">
         <v>33836286</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -5145,7 +5177,7 @@
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418" s="2">
+      <c r="A418">
         <v>21609794</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -5153,7 +5185,7 @@
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419" s="2">
+      <c r="A419">
         <v>34915882</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -5161,7 +5193,7 @@
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420" s="2">
+      <c r="A420">
         <v>41321591</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -5169,7 +5201,7 @@
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421" s="2">
+      <c r="A421">
         <v>38460036</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -5177,7 +5209,7 @@
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" s="2">
+      <c r="A422">
         <v>28691607</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -5185,7 +5217,7 @@
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423" s="2">
+      <c r="A423">
         <v>22659558</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -5193,7 +5225,7 @@
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424" s="2">
+      <c r="A424">
         <v>28525815</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -5201,7 +5233,7 @@
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A425" s="2">
+      <c r="A425">
         <v>22754977</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -5209,7 +5241,7 @@
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A426" s="2">
+      <c r="A426">
         <v>25695492</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -5217,7 +5249,7 @@
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A427" s="2">
+      <c r="A427">
         <v>26908791</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -5225,7 +5257,7 @@
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A428" s="2">
+      <c r="A428">
         <v>22159245</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -5233,7 +5265,7 @@
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A429" s="2">
+      <c r="A429">
         <v>23943704</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -5241,7 +5273,7 @@
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A430" s="2">
+      <c r="A430">
         <v>33630294</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -5249,7 +5281,7 @@
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A431" s="2">
+      <c r="A431">
         <v>26510270</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -5257,7 +5289,7 @@
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A432" s="2">
+      <c r="A432">
         <v>22058632</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -5265,7 +5297,7 @@
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A433" s="2">
+      <c r="A433">
         <v>23364568</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -5273,7 +5305,7 @@
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A434" s="2">
+      <c r="A434">
         <v>26872125</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -5281,7 +5313,7 @@
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A435" s="2">
+      <c r="A435">
         <v>39651061</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -5289,7 +5321,7 @@
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A436" s="2">
+      <c r="A436">
         <v>18769981</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -5297,7 +5329,7 @@
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A437" s="2">
+      <c r="A437">
         <v>35734655</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -5305,7 +5337,7 @@
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A438" s="2">
+      <c r="A438">
         <v>36544343</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -5313,7 +5345,7 @@
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A439" s="2">
+      <c r="A439">
         <v>32632990</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -5321,7 +5353,7 @@
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A440" s="2">
+      <c r="A440">
         <v>24561015</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -5329,7 +5361,7 @@
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A441" s="2">
+      <c r="A441">
         <v>26791183</v>
       </c>
       <c r="B441" s="1" t="s">
@@ -5337,7 +5369,7 @@
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A442" s="2">
+      <c r="A442">
         <v>30145582</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -5345,7 +5377,7 @@
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A443" s="2">
+      <c r="A443">
         <v>25549159</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -5353,7 +5385,7 @@
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A444" s="2">
+      <c r="A444">
         <v>29540715</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -5361,7 +5393,7 @@
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A445" s="2">
+      <c r="A445">
         <v>29812570</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -5369,7 +5401,7 @@
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A446" s="2">
+      <c r="A446">
         <v>35735457</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -5377,7 +5409,7 @@
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A447" s="2">
+      <c r="A447">
         <v>24343147</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -5385,7 +5417,7 @@
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A448" s="2">
+      <c r="A448">
         <v>22788401</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -5393,7 +5425,7 @@
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A449" s="2">
+      <c r="A449">
         <v>31979348</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -5401,7 +5433,7 @@
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A450" s="2">
+      <c r="A450">
         <v>21610323</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -5409,7 +5441,7 @@
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A451" s="2">
+      <c r="A451">
         <v>35850413</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -5417,7 +5449,7 @@
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A452" s="2">
+      <c r="A452">
         <v>28040622</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -5425,7 +5457,7 @@
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A453" s="2">
+      <c r="A453">
         <v>31612043</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -5433,7 +5465,7 @@
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A454" s="2">
+      <c r="A454">
         <v>28904948</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -5441,7 +5473,7 @@
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A455" s="2">
+      <c r="A455">
         <v>32690087</v>
       </c>
       <c r="B455" s="1" t="s">
@@ -5449,7 +5481,7 @@
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A456" s="2">
+      <c r="A456">
         <v>39524184</v>
       </c>
       <c r="B456" s="1" t="s">
@@ -5457,7 +5489,7 @@
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A457" s="2">
+      <c r="A457">
         <v>26231472</v>
       </c>
       <c r="B457" s="1" t="s">
@@ -5473,7 +5505,7 @@
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A459" s="2">
+      <c r="A459">
         <v>28416683</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -5481,7 +5513,7 @@
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A460" s="2">
+      <c r="A460">
         <v>36254561</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -5489,7 +5521,7 @@
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A461" s="2">
+      <c r="A461">
         <v>20989790</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -5497,7 +5529,7 @@
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A462" s="2">
+      <c r="A462">
         <v>25001083</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -5505,7 +5537,7 @@
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A463" s="2">
+      <c r="A463">
         <v>35506028</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -5513,7 +5545,7 @@
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A464" s="2">
+      <c r="A464">
         <v>25939866</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -5521,7 +5553,7 @@
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A465" s="2">
+      <c r="A465">
         <v>38463986</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -5529,7 +5561,7 @@
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A466" s="2">
+      <c r="A466">
         <v>25462001</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -5537,7 +5569,7 @@
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A467" s="2">
+      <c r="A467">
         <v>20462239</v>
       </c>
       <c r="B467" s="1" t="s">
@@ -5545,7 +5577,7 @@
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A468" s="2">
+      <c r="A468">
         <v>35736736</v>
       </c>
       <c r="B468" s="1" t="s">
@@ -5553,7 +5585,7 @@
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A469" s="2">
+      <c r="A469">
         <v>37742216</v>
       </c>
       <c r="B469" s="1" t="s">
@@ -5561,7 +5593,7 @@
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A470" s="2">
+      <c r="A470">
         <v>22358058</v>
       </c>
       <c r="B470" s="1" t="s">
@@ -5569,7 +5601,7 @@
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A471" s="2">
+      <c r="A471">
         <v>24660435</v>
       </c>
       <c r="B471" s="1" t="s">
@@ -5577,7 +5609,7 @@
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A472" s="2">
+      <c r="A472">
         <v>32351220</v>
       </c>
       <c r="B472" s="1" t="s">
@@ -5585,7 +5617,7 @@
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A473" s="2">
+      <c r="A473">
         <v>32033627</v>
       </c>
       <c r="B473" s="1" t="s">
@@ -5593,7 +5625,7 @@
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A474" s="2">
+      <c r="A474">
         <v>35734525</v>
       </c>
       <c r="B474" s="1" t="s">
@@ -5601,7 +5633,7 @@
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A475" s="2">
+      <c r="A475">
         <v>33236890</v>
       </c>
       <c r="B475" s="1" t="s">
@@ -5609,7 +5641,7 @@
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A476" s="2">
+      <c r="A476">
         <v>39954725</v>
       </c>
       <c r="B476" s="1" t="s">
@@ -5617,7 +5649,7 @@
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A477" s="2">
+      <c r="A477">
         <v>40592181</v>
       </c>
       <c r="B477" s="1" t="s">
@@ -5625,7 +5657,7 @@
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A478" s="2">
+      <c r="A478">
         <v>31044246</v>
       </c>
       <c r="B478" s="1" t="s">
@@ -5633,7 +5665,7 @@
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A479" s="2">
+      <c r="A479">
         <v>38593247</v>
       </c>
       <c r="B479" s="1" t="s">
@@ -5641,7 +5673,7 @@
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A480" s="2">
+      <c r="A480">
         <v>20133097</v>
       </c>
       <c r="B480" s="1" t="s">
@@ -5649,7 +5681,7 @@
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A481" s="2">
+      <c r="A481">
         <v>24480361</v>
       </c>
       <c r="B481" s="1" t="s">
@@ -5657,7 +5689,7 @@
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A482" s="2">
+      <c r="A482">
         <v>32750544</v>
       </c>
       <c r="B482" s="1" t="s">
@@ -5665,7 +5697,7 @@
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A483" s="2">
+      <c r="A483">
         <v>35189008</v>
       </c>
       <c r="B483" s="1" t="s">
@@ -5673,7 +5705,7 @@
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A484" s="2">
+      <c r="A484">
         <v>21742241</v>
       </c>
       <c r="B484" s="1" t="s">
@@ -5681,7 +5713,7 @@
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A485" s="2">
+      <c r="A485">
         <v>24879167</v>
       </c>
       <c r="B485" s="1" t="s">
@@ -5689,7 +5721,7 @@
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A486" s="2">
+      <c r="A486">
         <v>37297387</v>
       </c>
       <c r="B486" s="1" t="s">
@@ -5697,7 +5729,7 @@
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A487" s="2">
+      <c r="A487">
         <v>25118471</v>
       </c>
       <c r="B487" s="1" t="s">
@@ -5705,7 +5737,7 @@
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A488" s="2">
+      <c r="A488">
         <v>36251995</v>
       </c>
       <c r="B488" s="1" t="s">
@@ -5713,7 +5745,7 @@
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A489" s="2">
+      <c r="A489">
         <v>30631277</v>
       </c>
       <c r="B489" s="1" t="s">
@@ -5721,7 +5753,7 @@
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A490" s="2">
+      <c r="A490">
         <v>18011287</v>
       </c>
       <c r="B490" s="1" t="s">
@@ -5729,7 +5761,7 @@
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A491" s="2">
+      <c r="A491">
         <v>27276160</v>
       </c>
       <c r="B491" s="1" t="s">
@@ -5737,7 +5769,7 @@
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A492" s="2">
+      <c r="A492">
         <v>25649193</v>
       </c>
       <c r="B492" s="1" t="s">
@@ -5745,7 +5777,7 @@
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A493" s="2">
+      <c r="A493">
         <v>37462200</v>
       </c>
       <c r="B493" s="1" t="s">
@@ -5753,7 +5785,7 @@
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A494" s="2">
+      <c r="A494">
         <v>34657161</v>
       </c>
       <c r="B494" s="1" t="s">
@@ -5761,7 +5793,7 @@
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A495" s="2">
+      <c r="A495">
         <v>35857624</v>
       </c>
       <c r="B495" s="1" t="s">
@@ -5769,7 +5801,7 @@
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A496" s="2">
+      <c r="A496">
         <v>35506984</v>
       </c>
       <c r="B496" s="1" t="s">
@@ -5777,7 +5809,7 @@
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A497" s="2">
+      <c r="A497">
         <v>24795163</v>
       </c>
       <c r="B497" s="1" t="s">
@@ -5785,7 +5817,7 @@
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A498" s="2">
+      <c r="A498">
         <v>31633471</v>
       </c>
       <c r="B498" s="1" t="s">
@@ -5793,7 +5825,7 @@
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A499" s="2">
+      <c r="A499">
         <v>31871375</v>
       </c>
       <c r="B499" s="1" t="s">
@@ -5801,7 +5833,7 @@
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A500" s="2">
+      <c r="A500">
         <v>28904783</v>
       </c>
       <c r="B500" s="1" t="s">
@@ -5809,7 +5841,7 @@
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A501" s="2">
+      <c r="A501">
         <v>37298151</v>
       </c>
       <c r="B501" s="1" t="s">
@@ -5817,7 +5849,7 @@
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A502" s="2">
+      <c r="A502">
         <v>24793376</v>
       </c>
       <c r="B502" s="1" t="s">
@@ -5825,7 +5857,7 @@
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A503" s="2">
+      <c r="A503">
         <v>23634370</v>
       </c>
       <c r="B503" s="1" t="s">
@@ -5833,7 +5865,7 @@
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A504" s="2">
+      <c r="A504">
         <v>23381812</v>
       </c>
       <c r="B504" s="1" t="s">
@@ -5841,7 +5873,7 @@
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A505" s="2">
+      <c r="A505">
         <v>23488413</v>
       </c>
       <c r="B505" s="1" t="s">
@@ -5854,6 +5886,54 @@
       </c>
       <c r="B506" s="1" t="s">
         <v>485</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -2849,10 +2849,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>835</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -2526,7 +2526,7 @@
     <t>FAELLA RODRIGUEZ MARISEL DEL CARMEN</t>
   </si>
   <si>
-    <t>nombre</t>
+    <t>Nombre</t>
   </si>
 </sst>
 </file>
@@ -2849,3391 +2849,3391 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>412</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>413</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>414</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>415</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>416</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>417</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>418</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>419</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>420</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>421</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>422</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>423</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>424</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>425</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
         <v>426</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>427</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>428</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>429</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>430</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>431</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>432</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>433</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>434</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
         <v>435</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>436</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>437</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>438</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>439</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
         <v>440</v>
-      </c>
-      <c r="B30" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>441</v>
-      </c>
-      <c r="B31" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
         <v>442</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>443</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
         <v>444</v>
-      </c>
-      <c r="B34" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>445</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>446</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
         <v>447</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
         <v>448</v>
-      </c>
-      <c r="B38" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
         <v>449</v>
-      </c>
-      <c r="B39" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>450</v>
-      </c>
-      <c r="B40" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
         <v>451</v>
-      </c>
-      <c r="B41" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
         <v>452</v>
-      </c>
-      <c r="B42" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
         <v>453</v>
-      </c>
-      <c r="B43" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
         <v>454</v>
-      </c>
-      <c r="B44" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
         <v>455</v>
-      </c>
-      <c r="B45" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
         <v>456</v>
-      </c>
-      <c r="B46" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
         <v>457</v>
-      </c>
-      <c r="B47" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
         <v>458</v>
-      </c>
-      <c r="B48" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
         <v>459</v>
-      </c>
-      <c r="B49" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
         <v>460</v>
-      </c>
-      <c r="B50" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
         <v>461</v>
-      </c>
-      <c r="B51" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
         <v>462</v>
-      </c>
-      <c r="B52" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
         <v>463</v>
-      </c>
-      <c r="B53" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
         <v>464</v>
-      </c>
-      <c r="B54" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
         <v>465</v>
-      </c>
-      <c r="B55" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
         <v>466</v>
-      </c>
-      <c r="B56" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
         <v>467</v>
-      </c>
-      <c r="B57" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
         <v>468</v>
-      </c>
-      <c r="B58" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
         <v>469</v>
-      </c>
-      <c r="B59" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
         <v>470</v>
-      </c>
-      <c r="B60" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
         <v>471</v>
-      </c>
-      <c r="B61" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
         <v>472</v>
-      </c>
-      <c r="B62" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
         <v>473</v>
-      </c>
-      <c r="B63" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
         <v>474</v>
-      </c>
-      <c r="B64" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
         <v>475</v>
-      </c>
-      <c r="B65" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
         <v>476</v>
-      </c>
-      <c r="B66" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
         <v>477</v>
-      </c>
-      <c r="B67" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
         <v>478</v>
-      </c>
-      <c r="B68" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
         <v>479</v>
-      </c>
-      <c r="B69" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
         <v>480</v>
-      </c>
-      <c r="B70" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
         <v>481</v>
-      </c>
-      <c r="B71" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
         <v>482</v>
-      </c>
-      <c r="B72" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
         <v>483</v>
-      </c>
-      <c r="B73" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
         <v>484</v>
-      </c>
-      <c r="B74" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
         <v>485</v>
-      </c>
-      <c r="B75" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
         <v>486</v>
-      </c>
-      <c r="B76" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
         <v>487</v>
-      </c>
-      <c r="B77" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
         <v>488</v>
-      </c>
-      <c r="B78" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
         <v>489</v>
-      </c>
-      <c r="B79" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
         <v>490</v>
-      </c>
-      <c r="B80" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
         <v>491</v>
-      </c>
-      <c r="B81" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
         <v>492</v>
-      </c>
-      <c r="B82" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
         <v>493</v>
-      </c>
-      <c r="B83" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
         <v>494</v>
-      </c>
-      <c r="B84" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
         <v>495</v>
-      </c>
-      <c r="B85" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
         <v>496</v>
-      </c>
-      <c r="B86" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
         <v>497</v>
-      </c>
-      <c r="B87" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
         <v>498</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
         <v>499</v>
-      </c>
-      <c r="B89" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
         <v>500</v>
-      </c>
-      <c r="B90" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
         <v>501</v>
-      </c>
-      <c r="B91" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
         <v>502</v>
-      </c>
-      <c r="B92" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
         <v>503</v>
-      </c>
-      <c r="B93" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
         <v>504</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
         <v>505</v>
-      </c>
-      <c r="B95" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
         <v>506</v>
-      </c>
-      <c r="B96" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
         <v>507</v>
-      </c>
-      <c r="B97" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
         <v>508</v>
-      </c>
-      <c r="B98" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
         <v>509</v>
-      </c>
-      <c r="B99" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
         <v>510</v>
-      </c>
-      <c r="B100" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
         <v>511</v>
-      </c>
-      <c r="B101" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
         <v>512</v>
-      </c>
-      <c r="B102" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
         <v>513</v>
-      </c>
-      <c r="B103" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
         <v>514</v>
-      </c>
-      <c r="B104" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
         <v>515</v>
-      </c>
-      <c r="B105" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
         <v>516</v>
-      </c>
-      <c r="B106" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
         <v>517</v>
-      </c>
-      <c r="B107" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
         <v>518</v>
-      </c>
-      <c r="B108" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
         <v>519</v>
-      </c>
-      <c r="B109" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
         <v>520</v>
-      </c>
-      <c r="B110" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
         <v>521</v>
-      </c>
-      <c r="B111" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
         <v>522</v>
-      </c>
-      <c r="B112" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
         <v>523</v>
-      </c>
-      <c r="B113" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
         <v>524</v>
-      </c>
-      <c r="B114" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
         <v>525</v>
-      </c>
-      <c r="B115" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
         <v>526</v>
-      </c>
-      <c r="B116" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
         <v>527</v>
-      </c>
-      <c r="B117" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
         <v>528</v>
-      </c>
-      <c r="B118" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
         <v>529</v>
-      </c>
-      <c r="B119" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
         <v>530</v>
-      </c>
-      <c r="B120" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
         <v>531</v>
-      </c>
-      <c r="B121" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
         <v>532</v>
-      </c>
-      <c r="B122" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
         <v>533</v>
-      </c>
-      <c r="B123" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
         <v>534</v>
-      </c>
-      <c r="B124" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
         <v>535</v>
-      </c>
-      <c r="B125" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
         <v>536</v>
-      </c>
-      <c r="B126" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
         <v>537</v>
-      </c>
-      <c r="B127" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
         <v>538</v>
-      </c>
-      <c r="B128" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
         <v>539</v>
-      </c>
-      <c r="B129" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
         <v>540</v>
-      </c>
-      <c r="B130" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
         <v>541</v>
-      </c>
-      <c r="B131" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
         <v>542</v>
-      </c>
-      <c r="B132" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
         <v>543</v>
-      </c>
-      <c r="B133" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
         <v>544</v>
-      </c>
-      <c r="B134" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
         <v>545</v>
-      </c>
-      <c r="B135" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
         <v>546</v>
-      </c>
-      <c r="B136" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
         <v>547</v>
-      </c>
-      <c r="B137" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
         <v>548</v>
-      </c>
-      <c r="B138" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
         <v>549</v>
-      </c>
-      <c r="B139" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
         <v>550</v>
-      </c>
-      <c r="B140" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
         <v>551</v>
-      </c>
-      <c r="B141" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
         <v>552</v>
-      </c>
-      <c r="B142" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
         <v>553</v>
-      </c>
-      <c r="B143" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
         <v>554</v>
-      </c>
-      <c r="B144" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
         <v>555</v>
-      </c>
-      <c r="B145" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
         <v>556</v>
-      </c>
-      <c r="B146" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
         <v>557</v>
-      </c>
-      <c r="B147" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
         <v>558</v>
-      </c>
-      <c r="B148" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
         <v>559</v>
-      </c>
-      <c r="B149" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
         <v>560</v>
-      </c>
-      <c r="B150" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
         <v>561</v>
-      </c>
-      <c r="B151" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
         <v>562</v>
-      </c>
-      <c r="B152" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
         <v>563</v>
-      </c>
-      <c r="B153" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
         <v>564</v>
-      </c>
-      <c r="B154" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
         <v>565</v>
-      </c>
-      <c r="B155" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
         <v>566</v>
-      </c>
-      <c r="B156" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
         <v>567</v>
-      </c>
-      <c r="B157" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
         <v>568</v>
-      </c>
-      <c r="B158" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
         <v>569</v>
-      </c>
-      <c r="B159" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
         <v>570</v>
-      </c>
-      <c r="B160" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
         <v>571</v>
-      </c>
-      <c r="B161" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
         <v>572</v>
-      </c>
-      <c r="B162" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
         <v>573</v>
-      </c>
-      <c r="B163" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
         <v>574</v>
-      </c>
-      <c r="B164" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
         <v>575</v>
-      </c>
-      <c r="B165" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
         <v>576</v>
-      </c>
-      <c r="B166" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
         <v>577</v>
-      </c>
-      <c r="B167" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
         <v>578</v>
-      </c>
-      <c r="B168" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
         <v>579</v>
-      </c>
-      <c r="B169" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
         <v>580</v>
-      </c>
-      <c r="B170" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
         <v>581</v>
-      </c>
-      <c r="B171" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
         <v>582</v>
-      </c>
-      <c r="B172" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
         <v>583</v>
-      </c>
-      <c r="B173" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
         <v>584</v>
-      </c>
-      <c r="B174" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
         <v>585</v>
-      </c>
-      <c r="B175" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
         <v>586</v>
-      </c>
-      <c r="B176" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
         <v>587</v>
-      </c>
-      <c r="B177" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
         <v>588</v>
-      </c>
-      <c r="B178" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
         <v>589</v>
-      </c>
-      <c r="B179" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
         <v>590</v>
-      </c>
-      <c r="B180" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
         <v>591</v>
-      </c>
-      <c r="B181" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
         <v>592</v>
-      </c>
-      <c r="B182" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
         <v>593</v>
-      </c>
-      <c r="B183" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
         <v>594</v>
-      </c>
-      <c r="B184" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
         <v>595</v>
-      </c>
-      <c r="B185" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
         <v>596</v>
-      </c>
-      <c r="B186" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
         <v>597</v>
-      </c>
-      <c r="B187" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
         <v>598</v>
-      </c>
-      <c r="B188" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
         <v>599</v>
-      </c>
-      <c r="B189" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
         <v>600</v>
-      </c>
-      <c r="B190" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
         <v>601</v>
-      </c>
-      <c r="B191" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
         <v>602</v>
-      </c>
-      <c r="B192" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
         <v>603</v>
-      </c>
-      <c r="B193" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
         <v>604</v>
-      </c>
-      <c r="B194" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
         <v>605</v>
-      </c>
-      <c r="B195" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
         <v>606</v>
-      </c>
-      <c r="B196" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
         <v>607</v>
-      </c>
-      <c r="B197" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
         <v>608</v>
-      </c>
-      <c r="B198" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
         <v>609</v>
-      </c>
-      <c r="B199" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
         <v>610</v>
-      </c>
-      <c r="B200" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
         <v>611</v>
-      </c>
-      <c r="B201" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
         <v>612</v>
-      </c>
-      <c r="B202" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
         <v>613</v>
-      </c>
-      <c r="B203" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
         <v>614</v>
-      </c>
-      <c r="B204" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
         <v>615</v>
-      </c>
-      <c r="B205" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
         <v>616</v>
-      </c>
-      <c r="B206" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
         <v>617</v>
-      </c>
-      <c r="B207" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
         <v>618</v>
-      </c>
-      <c r="B208" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
         <v>619</v>
-      </c>
-      <c r="B209" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
         <v>620</v>
-      </c>
-      <c r="B210" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
         <v>621</v>
-      </c>
-      <c r="B211" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
         <v>622</v>
-      </c>
-      <c r="B212" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
         <v>623</v>
-      </c>
-      <c r="B213" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
         <v>624</v>
-      </c>
-      <c r="B214" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
         <v>625</v>
-      </c>
-      <c r="B215" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
         <v>626</v>
-      </c>
-      <c r="B216" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
         <v>627</v>
-      </c>
-      <c r="B217" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
         <v>628</v>
-      </c>
-      <c r="B218" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
         <v>629</v>
-      </c>
-      <c r="B219" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
         <v>630</v>
-      </c>
-      <c r="B220" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
         <v>631</v>
-      </c>
-      <c r="B221" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
         <v>632</v>
-      </c>
-      <c r="B222" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
         <v>633</v>
-      </c>
-      <c r="B223" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
         <v>634</v>
-      </c>
-      <c r="B224" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
         <v>635</v>
-      </c>
-      <c r="B225" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
         <v>636</v>
-      </c>
-      <c r="B226" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
         <v>637</v>
-      </c>
-      <c r="B227" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
         <v>638</v>
-      </c>
-      <c r="B228" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
         <v>639</v>
-      </c>
-      <c r="B229" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
         <v>640</v>
-      </c>
-      <c r="B230" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
         <v>641</v>
-      </c>
-      <c r="B231" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
         <v>642</v>
-      </c>
-      <c r="B232" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
         <v>643</v>
-      </c>
-      <c r="B233" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
         <v>644</v>
-      </c>
-      <c r="B234" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
         <v>645</v>
-      </c>
-      <c r="B235" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
         <v>646</v>
-      </c>
-      <c r="B236" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
         <v>647</v>
-      </c>
-      <c r="B237" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
         <v>648</v>
-      </c>
-      <c r="B238" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
         <v>649</v>
-      </c>
-      <c r="B239" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
         <v>650</v>
-      </c>
-      <c r="B240" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
         <v>651</v>
-      </c>
-      <c r="B241" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
         <v>652</v>
-      </c>
-      <c r="B242" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
         <v>653</v>
-      </c>
-      <c r="B243" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
         <v>654</v>
-      </c>
-      <c r="B244" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
         <v>655</v>
-      </c>
-      <c r="B245" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
         <v>656</v>
-      </c>
-      <c r="B246" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
         <v>657</v>
-      </c>
-      <c r="B247" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
         <v>658</v>
-      </c>
-      <c r="B248" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
         <v>659</v>
-      </c>
-      <c r="B249" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
         <v>660</v>
-      </c>
-      <c r="B250" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
         <v>661</v>
-      </c>
-      <c r="B251" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
         <v>662</v>
-      </c>
-      <c r="B252" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
         <v>663</v>
-      </c>
-      <c r="B253" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
         <v>664</v>
-      </c>
-      <c r="B254" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
         <v>665</v>
-      </c>
-      <c r="B255" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
         <v>666</v>
-      </c>
-      <c r="B256" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
         <v>667</v>
-      </c>
-      <c r="B257" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
         <v>668</v>
-      </c>
-      <c r="B258" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
         <v>669</v>
-      </c>
-      <c r="B259" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
         <v>670</v>
-      </c>
-      <c r="B260" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
         <v>671</v>
-      </c>
-      <c r="B261" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
         <v>672</v>
-      </c>
-      <c r="B262" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
         <v>673</v>
-      </c>
-      <c r="B263" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
         <v>674</v>
-      </c>
-      <c r="B264" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
         <v>675</v>
-      </c>
-      <c r="B265" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
         <v>676</v>
-      </c>
-      <c r="B266" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
         <v>677</v>
-      </c>
-      <c r="B267" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
         <v>678</v>
-      </c>
-      <c r="B268" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
         <v>679</v>
-      </c>
-      <c r="B269" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
         <v>680</v>
-      </c>
-      <c r="B270" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
         <v>681</v>
-      </c>
-      <c r="B271" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
         <v>682</v>
-      </c>
-      <c r="B272" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
         <v>683</v>
-      </c>
-      <c r="B273" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
         <v>684</v>
-      </c>
-      <c r="B274" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
         <v>685</v>
-      </c>
-      <c r="B275" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
         <v>686</v>
-      </c>
-      <c r="B276" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
         <v>687</v>
-      </c>
-      <c r="B277" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
         <v>688</v>
-      </c>
-      <c r="B278" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
         <v>689</v>
-      </c>
-      <c r="B279" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
         <v>690</v>
-      </c>
-      <c r="B280" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
         <v>691</v>
-      </c>
-      <c r="B281" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
         <v>692</v>
-      </c>
-      <c r="B282" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
         <v>693</v>
-      </c>
-      <c r="B283" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
         <v>694</v>
-      </c>
-      <c r="B284" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
         <v>695</v>
-      </c>
-      <c r="B285" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
         <v>696</v>
-      </c>
-      <c r="B286" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
         <v>697</v>
-      </c>
-      <c r="B287" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
         <v>698</v>
-      </c>
-      <c r="B288" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
         <v>699</v>
-      </c>
-      <c r="B289" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
         <v>700</v>
-      </c>
-      <c r="B290" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
         <v>701</v>
-      </c>
-      <c r="B291" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
         <v>702</v>
-      </c>
-      <c r="B292" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
         <v>703</v>
-      </c>
-      <c r="B293" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
         <v>704</v>
-      </c>
-      <c r="B294" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
         <v>705</v>
-      </c>
-      <c r="B295" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
         <v>706</v>
-      </c>
-      <c r="B296" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
         <v>707</v>
-      </c>
-      <c r="B297" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
         <v>708</v>
-      </c>
-      <c r="B298" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
         <v>709</v>
-      </c>
-      <c r="B299" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
         <v>710</v>
-      </c>
-      <c r="B300" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
         <v>711</v>
-      </c>
-      <c r="B301" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
         <v>712</v>
-      </c>
-      <c r="B302" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
         <v>713</v>
-      </c>
-      <c r="B303" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
         <v>714</v>
-      </c>
-      <c r="B304" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
         <v>715</v>
-      </c>
-      <c r="B305" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
         <v>716</v>
-      </c>
-      <c r="B306" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
         <v>717</v>
-      </c>
-      <c r="B307" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
         <v>718</v>
-      </c>
-      <c r="B308" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
         <v>719</v>
-      </c>
-      <c r="B309" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
         <v>720</v>
-      </c>
-      <c r="B310" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
         <v>721</v>
-      </c>
-      <c r="B311" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
         <v>722</v>
-      </c>
-      <c r="B312" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
         <v>723</v>
-      </c>
-      <c r="B313" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
         <v>724</v>
-      </c>
-      <c r="B314" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
         <v>725</v>
-      </c>
-      <c r="B315" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
         <v>726</v>
-      </c>
-      <c r="B316" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>316</v>
+      </c>
+      <c r="B317" t="s">
         <v>727</v>
-      </c>
-      <c r="B317" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>317</v>
+      </c>
+      <c r="B318" t="s">
         <v>728</v>
-      </c>
-      <c r="B318" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>318</v>
+      </c>
+      <c r="B319" t="s">
         <v>729</v>
-      </c>
-      <c r="B319" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>319</v>
+      </c>
+      <c r="B320" t="s">
         <v>730</v>
-      </c>
-      <c r="B320" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>320</v>
+      </c>
+      <c r="B321" t="s">
         <v>731</v>
-      </c>
-      <c r="B321" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>321</v>
+      </c>
+      <c r="B322" t="s">
         <v>732</v>
-      </c>
-      <c r="B322" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>322</v>
+      </c>
+      <c r="B323" t="s">
         <v>733</v>
-      </c>
-      <c r="B323" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
         <v>734</v>
-      </c>
-      <c r="B324" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
         <v>735</v>
-      </c>
-      <c r="B325" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
         <v>736</v>
-      </c>
-      <c r="B326" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
         <v>737</v>
-      </c>
-      <c r="B327" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
         <v>738</v>
-      </c>
-      <c r="B328" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
         <v>739</v>
-      </c>
-      <c r="B329" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
         <v>740</v>
-      </c>
-      <c r="B330" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
         <v>741</v>
-      </c>
-      <c r="B331" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
         <v>742</v>
-      </c>
-      <c r="B332" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
         <v>743</v>
-      </c>
-      <c r="B333" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
         <v>744</v>
-      </c>
-      <c r="B334" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
         <v>745</v>
-      </c>
-      <c r="B335" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>335</v>
+      </c>
+      <c r="B336" t="s">
         <v>746</v>
-      </c>
-      <c r="B336" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>336</v>
+      </c>
+      <c r="B337" t="s">
         <v>747</v>
-      </c>
-      <c r="B337" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
+        <v>337</v>
+      </c>
+      <c r="B338" t="s">
         <v>748</v>
-      </c>
-      <c r="B338" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
+        <v>338</v>
+      </c>
+      <c r="B339" t="s">
         <v>749</v>
-      </c>
-      <c r="B339" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s">
         <v>750</v>
-      </c>
-      <c r="B340" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
         <v>751</v>
-      </c>
-      <c r="B341" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>341</v>
+      </c>
+      <c r="B342" t="s">
         <v>752</v>
-      </c>
-      <c r="B342" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>342</v>
+      </c>
+      <c r="B343" t="s">
         <v>753</v>
-      </c>
-      <c r="B343" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>343</v>
+      </c>
+      <c r="B344" t="s">
         <v>754</v>
-      </c>
-      <c r="B344" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
         <v>755</v>
-      </c>
-      <c r="B345" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>345</v>
+      </c>
+      <c r="B346" t="s">
         <v>756</v>
-      </c>
-      <c r="B346" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>346</v>
+      </c>
+      <c r="B347" t="s">
         <v>757</v>
-      </c>
-      <c r="B347" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>347</v>
+      </c>
+      <c r="B348" t="s">
         <v>758</v>
-      </c>
-      <c r="B348" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>348</v>
+      </c>
+      <c r="B349" t="s">
         <v>759</v>
-      </c>
-      <c r="B349" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>349</v>
+      </c>
+      <c r="B350" t="s">
         <v>760</v>
-      </c>
-      <c r="B350" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>350</v>
+      </c>
+      <c r="B351" t="s">
         <v>761</v>
-      </c>
-      <c r="B351" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
+        <v>351</v>
+      </c>
+      <c r="B352" t="s">
         <v>762</v>
-      </c>
-      <c r="B352" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>352</v>
+      </c>
+      <c r="B353" t="s">
         <v>763</v>
-      </c>
-      <c r="B353" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>353</v>
+      </c>
+      <c r="B354" t="s">
         <v>764</v>
-      </c>
-      <c r="B354" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>354</v>
+      </c>
+      <c r="B355" t="s">
         <v>765</v>
-      </c>
-      <c r="B355" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>355</v>
+      </c>
+      <c r="B356" t="s">
         <v>766</v>
-      </c>
-      <c r="B356" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>356</v>
+      </c>
+      <c r="B357" t="s">
         <v>767</v>
-      </c>
-      <c r="B357" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>357</v>
+      </c>
+      <c r="B358" t="s">
         <v>768</v>
-      </c>
-      <c r="B358" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
+        <v>358</v>
+      </c>
+      <c r="B359" t="s">
         <v>769</v>
-      </c>
-      <c r="B359" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
         <v>770</v>
-      </c>
-      <c r="B360" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
         <v>771</v>
-      </c>
-      <c r="B361" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
         <v>772</v>
-      </c>
-      <c r="B362" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
         <v>773</v>
-      </c>
-      <c r="B363" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
         <v>774</v>
-      </c>
-      <c r="B364" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
         <v>775</v>
-      </c>
-      <c r="B365" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
         <v>776</v>
-      </c>
-      <c r="B366" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
         <v>777</v>
-      </c>
-      <c r="B367" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
         <v>778</v>
-      </c>
-      <c r="B368" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
         <v>779</v>
-      </c>
-      <c r="B369" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
         <v>780</v>
-      </c>
-      <c r="B370" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
         <v>781</v>
-      </c>
-      <c r="B371" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
         <v>782</v>
-      </c>
-      <c r="B372" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>372</v>
+      </c>
+      <c r="B373" t="s">
         <v>783</v>
-      </c>
-      <c r="B373" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>373</v>
+      </c>
+      <c r="B374" t="s">
         <v>784</v>
-      </c>
-      <c r="B374" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>374</v>
+      </c>
+      <c r="B375" t="s">
         <v>785</v>
-      </c>
-      <c r="B375" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
+        <v>375</v>
+      </c>
+      <c r="B376" t="s">
         <v>786</v>
       </c>
-      <c r="B376" t="s">
-        <v>375</v>
-      </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
+      <c r="B377" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>376</v>
+      </c>
+      <c r="B378" t="s">
         <v>788</v>
-      </c>
-      <c r="B378" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
+        <v>377</v>
+      </c>
+      <c r="B379" t="s">
         <v>789</v>
-      </c>
-      <c r="B379" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>378</v>
+      </c>
+      <c r="B380" t="s">
         <v>790</v>
-      </c>
-      <c r="B380" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>379</v>
+      </c>
+      <c r="B381" t="s">
         <v>791</v>
-      </c>
-      <c r="B381" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>380</v>
+      </c>
+      <c r="B382" t="s">
         <v>792</v>
-      </c>
-      <c r="B382" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
+        <v>381</v>
+      </c>
+      <c r="B383" t="s">
         <v>793</v>
-      </c>
-      <c r="B383" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>382</v>
+      </c>
+      <c r="B384" t="s">
         <v>794</v>
-      </c>
-      <c r="B384" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
+        <v>383</v>
+      </c>
+      <c r="B385" t="s">
         <v>795</v>
-      </c>
-      <c r="B385" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>384</v>
+      </c>
+      <c r="B386" t="s">
         <v>796</v>
-      </c>
-      <c r="B386" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>385</v>
+      </c>
+      <c r="B387" t="s">
         <v>797</v>
-      </c>
-      <c r="B387" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>386</v>
+      </c>
+      <c r="B388" t="s">
         <v>798</v>
-      </c>
-      <c r="B388" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
+        <v>387</v>
+      </c>
+      <c r="B389" t="s">
         <v>799</v>
-      </c>
-      <c r="B389" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>388</v>
+      </c>
+      <c r="B390" t="s">
         <v>800</v>
-      </c>
-      <c r="B390" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
+        <v>389</v>
+      </c>
+      <c r="B391" t="s">
         <v>801</v>
-      </c>
-      <c r="B391" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>390</v>
+      </c>
+      <c r="B392" t="s">
         <v>802</v>
-      </c>
-      <c r="B392" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
+        <v>391</v>
+      </c>
+      <c r="B393" t="s">
         <v>803</v>
-      </c>
-      <c r="B393" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
+        <v>392</v>
+      </c>
+      <c r="B394" t="s">
         <v>804</v>
-      </c>
-      <c r="B394" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
+        <v>393</v>
+      </c>
+      <c r="B395" t="s">
         <v>805</v>
-      </c>
-      <c r="B395" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>394</v>
+      </c>
+      <c r="B396" t="s">
         <v>806</v>
-      </c>
-      <c r="B396" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
+        <v>395</v>
+      </c>
+      <c r="B397" t="s">
         <v>807</v>
-      </c>
-      <c r="B397" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
+        <v>396</v>
+      </c>
+      <c r="B398" t="s">
         <v>808</v>
-      </c>
-      <c r="B398" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>397</v>
+      </c>
+      <c r="B399" t="s">
         <v>809</v>
-      </c>
-      <c r="B399" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>398</v>
+      </c>
+      <c r="B400" t="s">
         <v>810</v>
-      </c>
-      <c r="B400" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>399</v>
+      </c>
+      <c r="B401" t="s">
         <v>811</v>
-      </c>
-      <c r="B401" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>400</v>
+      </c>
+      <c r="B402" t="s">
         <v>812</v>
-      </c>
-      <c r="B402" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
+        <v>401</v>
+      </c>
+      <c r="B403" t="s">
         <v>813</v>
-      </c>
-      <c r="B403" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
+        <v>402</v>
+      </c>
+      <c r="B404" t="s">
         <v>814</v>
-      </c>
-      <c r="B404" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
+        <v>403</v>
+      </c>
+      <c r="B405" t="s">
         <v>815</v>
-      </c>
-      <c r="B405" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
+        <v>404</v>
+      </c>
+      <c r="B406" t="s">
         <v>816</v>
-      </c>
-      <c r="B406" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
+        <v>405</v>
+      </c>
+      <c r="B407" t="s">
         <v>817</v>
-      </c>
-      <c r="B407" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
+        <v>406</v>
+      </c>
+      <c r="B408" t="s">
         <v>818</v>
-      </c>
-      <c r="B408" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>407</v>
+      </c>
+      <c r="B409" t="s">
         <v>819</v>
-      </c>
-      <c r="B409" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
+        <v>408</v>
+      </c>
+      <c r="B410" t="s">
         <v>820</v>
-      </c>
-      <c r="B410" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>409</v>
+      </c>
+      <c r="B411" t="s">
         <v>821</v>
-      </c>
-      <c r="B411" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>410</v>
+      </c>
+      <c r="B412" t="s">
         <v>822</v>
-      </c>
-      <c r="B412" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
+        <v>411</v>
+      </c>
+      <c r="B413" t="s">
         <v>823</v>
       </c>
-      <c r="B413" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
+      <c r="A414">
+        <v>23029081</v>
+      </c>
+      <c r="B414" t="s">
         <v>824</v>
       </c>
-      <c r="B414">
-        <v>23029081</v>
-      </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
+      <c r="A415">
+        <v>24362028</v>
+      </c>
+      <c r="B415" t="s">
         <v>825</v>
       </c>
-      <c r="B415">
-        <v>24362028</v>
-      </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
+      <c r="A416">
+        <v>20943353</v>
+      </c>
+      <c r="B416" t="s">
         <v>826</v>
       </c>
-      <c r="B416">
-        <v>20943353</v>
-      </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
+      <c r="A417">
+        <v>24948498</v>
+      </c>
+      <c r="B417" t="s">
         <v>827</v>
       </c>
-      <c r="B417">
-        <v>24948498</v>
-      </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
+      <c r="A418">
+        <v>32878036</v>
+      </c>
+      <c r="B418" t="s">
         <v>828</v>
       </c>
-      <c r="B418">
-        <v>32878036</v>
-      </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
+      <c r="A419">
+        <v>21362137</v>
+      </c>
+      <c r="B419" t="s">
         <v>829</v>
       </c>
-      <c r="B419">
-        <v>21362137</v>
-      </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
+      <c r="A420">
+        <v>21610071</v>
+      </c>
+      <c r="B420" t="s">
         <v>830</v>
       </c>
-      <c r="B420">
-        <v>21610071</v>
-      </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
+      <c r="A421">
+        <v>33630200</v>
+      </c>
+      <c r="B421" t="s">
         <v>831</v>
       </c>
-      <c r="B421">
-        <v>33630200</v>
-      </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
+      <c r="A422">
+        <v>20303267</v>
+      </c>
+      <c r="B422" t="s">
         <v>832</v>
       </c>
-      <c r="B422">
-        <v>20303267</v>
-      </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
+      <c r="A423">
+        <v>25167554</v>
+      </c>
+      <c r="B423" t="s">
         <v>833</v>
       </c>
-      <c r="B423">
-        <v>25167554</v>
-      </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
+      <c r="A424">
+        <v>35734655</v>
+      </c>
+      <c r="B424" t="s">
         <v>834</v>
-      </c>
-      <c r="B424">
-        <v>35734655</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="838">
   <si>
     <t>DNI</t>
   </si>
@@ -2527,6 +2527,12 @@
   </si>
   <si>
     <t>Nombre</t>
+  </si>
+  <si>
+    <t>PANTUSO</t>
+  </si>
+  <si>
+    <t>ANDREA DEL VALLE</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:C425"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6172,7 +6178,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>24948498</v>
       </c>
@@ -6180,7 +6186,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>32878036</v>
       </c>
@@ -6188,7 +6194,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>21362137</v>
       </c>
@@ -6196,7 +6202,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>21610071</v>
       </c>
@@ -6204,7 +6210,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>33630200</v>
       </c>
@@ -6212,7 +6218,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>20303267</v>
       </c>
@@ -6220,7 +6226,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>25167554</v>
       </c>
@@ -6228,12 +6234,23 @@
         <v>833</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>35734655</v>
       </c>
       <c r="B424" t="s">
         <v>834</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>22663859</v>
+      </c>
+      <c r="B425" t="s">
+        <v>836</v>
+      </c>
+      <c r="C425" t="s">
+        <v>837</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\trabajos 2026\IMPULSO EDUCATIVO\30 JUNIO TM CENTRO CONVENCIONES\30 junio tm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B707F4FE-870A-417F-AEA4-C4DB9A9379CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A117F02-A8C3-4DDF-849C-41260B8D3FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="repetidos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">a!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">a!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,9 +40,6 @@
     <t>22107249</t>
   </si>
   <si>
-    <t>nombre</t>
-  </si>
-  <si>
     <t>22359285</t>
   </si>
   <si>
@@ -1415,6 +1412,9 @@
   </si>
   <si>
     <t>RODRIGUEZ QUIROGA KATERINNE EMILCE</t>
+  </si>
+  <si>
+    <t>Nombre</t>
   </si>
 </sst>
 </file>
@@ -1757,21 +1757,21 @@
   <dimension ref="A1:B488"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="57.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
         <v>44</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
         <v>50</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
         <v>52</v>
@@ -1971,7 +1971,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
         <v>54</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
         <v>56</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
         <v>58</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
         <v>60</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
         <v>64</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
         <v>66</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
         <v>68</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
         <v>70</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
         <v>72</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
         <v>74</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
         <v>76</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
         <v>78</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
         <v>80</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
         <v>82</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
         <v>84</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
         <v>86</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
         <v>88</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
         <v>90</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
         <v>92</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
         <v>94</v>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
         <v>96</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
         <v>98</v>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
         <v>100</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
         <v>102</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
         <v>104</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
         <v>106</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
         <v>108</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
         <v>110</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
         <v>112</v>
@@ -2211,7 +2211,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
         <v>114</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
         <v>116</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
         <v>118</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
         <v>120</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
         <v>122</v>
@@ -2251,7 +2251,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
         <v>124</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
         <v>126</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
         <v>128</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
         <v>130</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
         <v>132</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
         <v>134</v>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
         <v>136</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
         <v>140</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
         <v>142</v>
@@ -2331,7 +2331,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
         <v>144</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
         <v>146</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
         <v>148</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
         <v>150</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
         <v>152</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
         <v>154</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
         <v>156</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
         <v>158</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
         <v>160</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
         <v>162</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
         <v>164</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
         <v>166</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B84" t="s">
         <v>168</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
         <v>170</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B86" t="s">
         <v>172</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
         <v>174</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
         <v>176</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B89" t="s">
         <v>178</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
         <v>180</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
         <v>182</v>
@@ -2491,7 +2491,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
         <v>184</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
         <v>186</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
         <v>188</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
         <v>190</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
         <v>192</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
         <v>194</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
         <v>196</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
         <v>198</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
         <v>200</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
         <v>202</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B102" t="s">
         <v>204</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B103" t="s">
         <v>206</v>
@@ -2587,7 +2587,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B104" t="s">
         <v>208</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B105" t="s">
         <v>210</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B106" t="s">
         <v>212</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
         <v>214</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B108" t="s">
         <v>216</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B109" t="s">
         <v>218</v>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B110" t="s">
         <v>220</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s">
         <v>222</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B112" t="s">
         <v>224</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B113" t="s">
         <v>226</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B114" t="s">
         <v>228</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B115" t="s">
         <v>230</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B116" t="s">
         <v>232</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B117" t="s">
         <v>234</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B118" t="s">
         <v>236</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B119" t="s">
         <v>238</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B120" t="s">
         <v>240</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B121" t="s">
         <v>242</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B122" t="s">
         <v>244</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B123" t="s">
         <v>246</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B124" t="s">
         <v>248</v>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B125" t="s">
         <v>250</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B126" t="s">
         <v>252</v>
@@ -2771,7 +2771,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B127" t="s">
         <v>254</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B128" t="s">
         <v>256</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B129" t="s">
         <v>258</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B130" t="s">
         <v>260</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B131" t="s">
         <v>262</v>
@@ -2811,7 +2811,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B132" t="s">
         <v>264</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B133" t="s">
         <v>266</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B134" t="s">
         <v>268</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B135" t="s">
         <v>270</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B136" t="s">
         <v>272</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B137" t="s">
         <v>274</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B138" t="s">
         <v>276</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B139" t="s">
         <v>278</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B140" t="s">
         <v>280</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B141" t="s">
         <v>282</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B142" t="s">
         <v>284</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B143" t="s">
         <v>286</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B144" t="s">
         <v>288</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B145" t="s">
         <v>290</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B146" t="s">
         <v>292</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B147" t="s">
         <v>294</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B148" t="s">
         <v>296</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B149" t="s">
         <v>298</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B150" t="s">
         <v>300</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B151" t="s">
         <v>302</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B152" t="s">
         <v>304</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B153" t="s">
         <v>70</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B154" t="s">
         <v>306</v>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B155" t="s">
         <v>308</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B156" t="s">
         <v>310</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B157" t="s">
         <v>312</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B158" t="s">
         <v>314</v>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B159" t="s">
         <v>316</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B160" t="s">
         <v>318</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B161" t="s">
         <v>320</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B162" t="s">
         <v>322</v>
@@ -3059,7 +3059,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B163" t="s">
         <v>324</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B164" t="s">
         <v>326</v>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B165" t="s">
         <v>328</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B166" t="s">
         <v>330</v>
@@ -3091,7 +3091,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B167" t="s">
         <v>332</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B168" t="s">
         <v>334</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B169" t="s">
         <v>336</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B170" t="s">
         <v>338</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B171" t="s">
         <v>340</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B172" t="s">
         <v>342</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B173" t="s">
         <v>344</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B174" t="s">
         <v>346</v>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
         <v>348</v>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B176" t="s">
         <v>350</v>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B177" t="s">
         <v>352</v>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B178" t="s">
         <v>354</v>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B179" t="s">
         <v>356</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B180" t="s">
         <v>358</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B181" t="s">
         <v>360</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B182" t="s">
         <v>362</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B183" t="s">
         <v>364</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B184" t="s">
         <v>366</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B185" t="s">
         <v>368</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B186" t="s">
         <v>370</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B187" t="s">
         <v>372</v>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B188" t="s">
         <v>374</v>
@@ -3267,7 +3267,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B189" t="s">
         <v>376</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B190" t="s">
         <v>378</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B191" t="s">
         <v>380</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B192" t="s">
         <v>382</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B193" t="s">
         <v>384</v>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B194" t="s">
         <v>386</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B195" t="s">
         <v>388</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B196" t="s">
         <v>390</v>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B197" t="s">
         <v>392</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B198" t="s">
         <v>394</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B199" t="s">
         <v>396</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B200" t="s">
         <v>398</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B201" t="s">
         <v>400</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B202" t="s">
         <v>402</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B203" t="s">
         <v>404</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B204" t="s">
         <v>406</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B205" t="s">
         <v>408</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B206" t="s">
         <v>410</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B207" t="s">
         <v>412</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B208" t="s">
         <v>414</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B209" t="s">
         <v>416</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B210" t="s">
         <v>418</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B211" t="s">
         <v>420</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B212" t="s">
         <v>422</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B213" t="s">
         <v>424</v>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B214" t="s">
         <v>426</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B215" t="s">
         <v>428</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B216" t="s">
         <v>430</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B217" t="s">
         <v>432</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B218" t="s">
         <v>434</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B219" t="s">
         <v>436</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B220" t="s">
         <v>438</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B221" t="s">
         <v>440</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B222" t="s">
         <v>442</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B223" t="s">
         <v>444</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B224" t="s">
         <v>446</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B225" t="s">
         <v>448</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B226" t="s">
         <v>450</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B227" t="s">
         <v>452</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B228" t="s">
         <v>454</v>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B229" t="s">
         <v>456</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B230" t="s">
         <v>458</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B231" t="s">
         <v>460</v>
@@ -4638,7 +4638,7 @@
       <c r="B488"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A489:A1048576 A1">
+  <conditionalFormatting sqref="B489:B1048576 B1">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -2,23 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\trabajos 2026\IMPULSO EDUCATIVO\30 JUNIO TM CENTRO CONVENCIONES\30 junio tm\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A117F02-A8C3-4DDF-849C-41260B8D3FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A49E33-F059-441C-BFDB-1C142EC1B9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="a" sheetId="1" r:id="rId1"/>
-    <sheet name="repetidos" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">a!$A$1:$A$1</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="460">
   <si>
     <t>DNI</t>
   </si>
   <si>
-    <t>21358069</t>
-  </si>
-  <si>
-    <t>22107249</t>
+    <t>Nombre</t>
   </si>
   <si>
     <t>22359285</t>
@@ -1412,9 +1400,6 @@
   </si>
   <si>
     <t>RODRIGUEZ QUIROGA KATERINNE EMILCE</t>
-  </si>
-  <si>
-    <t>Nombre</t>
   </si>
 </sst>
 </file>
@@ -1450,35 +1435,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1492,7 +1455,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1537,7 +1500,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -1572,7 +1535,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -1754,3161 +1717,1858 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B488"/>
+  <dimension ref="A1:B231"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="57.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>461</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
         <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
         <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
         <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
         <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
         <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
         <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
         <v>59</v>
-      </c>
-      <c r="B30" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
         <v>63</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
         <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
         <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
         <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
         <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
         <v>75</v>
-      </c>
-      <c r="B38" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
         <v>77</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
         <v>79</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
         <v>81</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
         <v>83</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
         <v>85</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
         <v>87</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
         <v>89</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
         <v>91</v>
-      </c>
-      <c r="B46" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
         <v>93</v>
-      </c>
-      <c r="B47" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
         <v>95</v>
-      </c>
-      <c r="B48" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
         <v>97</v>
-      </c>
-      <c r="B49" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
         <v>99</v>
-      </c>
-      <c r="B50" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
         <v>101</v>
-      </c>
-      <c r="B51" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
         <v>103</v>
-      </c>
-      <c r="B52" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
         <v>105</v>
-      </c>
-      <c r="B53" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
         <v>107</v>
-      </c>
-      <c r="B54" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
         <v>109</v>
-      </c>
-      <c r="B55" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
         <v>111</v>
-      </c>
-      <c r="B56" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
         <v>113</v>
-      </c>
-      <c r="B57" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
         <v>115</v>
-      </c>
-      <c r="B58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
         <v>117</v>
-      </c>
-      <c r="B59" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" t="s">
         <v>119</v>
-      </c>
-      <c r="B60" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
         <v>121</v>
-      </c>
-      <c r="B61" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" t="s">
         <v>123</v>
-      </c>
-      <c r="B62" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" t="s">
         <v>125</v>
-      </c>
-      <c r="B63" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" t="s">
         <v>127</v>
-      </c>
-      <c r="B64" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
         <v>129</v>
-      </c>
-      <c r="B65" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" t="s">
         <v>131</v>
-      </c>
-      <c r="B66" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" t="s">
         <v>133</v>
-      </c>
-      <c r="B67" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
         <v>135</v>
-      </c>
-      <c r="B68" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s">
         <v>137</v>
-      </c>
-      <c r="B69" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" t="s">
         <v>139</v>
-      </c>
-      <c r="B70" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" t="s">
         <v>141</v>
-      </c>
-      <c r="B71" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" t="s">
         <v>143</v>
-      </c>
-      <c r="B72" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" t="s">
         <v>145</v>
-      </c>
-      <c r="B73" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" t="s">
         <v>147</v>
-      </c>
-      <c r="B74" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" t="s">
         <v>149</v>
-      </c>
-      <c r="B75" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" t="s">
         <v>151</v>
-      </c>
-      <c r="B76" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" t="s">
         <v>153</v>
-      </c>
-      <c r="B77" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" t="s">
         <v>155</v>
-      </c>
-      <c r="B78" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" t="s">
         <v>157</v>
-      </c>
-      <c r="B79" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" t="s">
         <v>159</v>
-      </c>
-      <c r="B80" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" t="s">
         <v>161</v>
-      </c>
-      <c r="B81" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s">
         <v>163</v>
-      </c>
-      <c r="B82" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
         <v>165</v>
-      </c>
-      <c r="B83" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" t="s">
         <v>167</v>
-      </c>
-      <c r="B84" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
         <v>169</v>
-      </c>
-      <c r="B85" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" t="s">
         <v>171</v>
-      </c>
-      <c r="B86" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" t="s">
         <v>173</v>
-      </c>
-      <c r="B87" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" t="s">
         <v>175</v>
-      </c>
-      <c r="B88" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" t="s">
         <v>177</v>
-      </c>
-      <c r="B89" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" t="s">
         <v>179</v>
-      </c>
-      <c r="B90" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
         <v>181</v>
-      </c>
-      <c r="B91" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
         <v>183</v>
-      </c>
-      <c r="B92" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
         <v>185</v>
-      </c>
-      <c r="B93" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
         <v>187</v>
-      </c>
-      <c r="B94" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
         <v>189</v>
-      </c>
-      <c r="B95" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
         <v>191</v>
-      </c>
-      <c r="B96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
         <v>193</v>
-      </c>
-      <c r="B97" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
         <v>195</v>
-      </c>
-      <c r="B98" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" t="s">
         <v>197</v>
-      </c>
-      <c r="B99" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
         <v>199</v>
-      </c>
-      <c r="B100" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
         <v>201</v>
-      </c>
-      <c r="B101" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
         <v>203</v>
-      </c>
-      <c r="B102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
         <v>205</v>
-      </c>
-      <c r="B103" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
         <v>207</v>
-      </c>
-      <c r="B104" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
         <v>209</v>
-      </c>
-      <c r="B105" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
         <v>211</v>
-      </c>
-      <c r="B106" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
         <v>213</v>
-      </c>
-      <c r="B107" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
         <v>215</v>
-      </c>
-      <c r="B108" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
         <v>217</v>
-      </c>
-      <c r="B109" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
         <v>219</v>
-      </c>
-      <c r="B110" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
         <v>221</v>
-      </c>
-      <c r="B111" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" t="s">
         <v>223</v>
-      </c>
-      <c r="B112" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" t="s">
         <v>225</v>
-      </c>
-      <c r="B113" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" t="s">
         <v>227</v>
-      </c>
-      <c r="B114" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" t="s">
         <v>229</v>
-      </c>
-      <c r="B115" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" t="s">
         <v>231</v>
-      </c>
-      <c r="B116" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" t="s">
         <v>233</v>
-      </c>
-      <c r="B117" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" t="s">
         <v>235</v>
-      </c>
-      <c r="B118" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
         <v>237</v>
-      </c>
-      <c r="B119" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" t="s">
         <v>239</v>
-      </c>
-      <c r="B120" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" t="s">
         <v>241</v>
-      </c>
-      <c r="B121" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
         <v>243</v>
-      </c>
-      <c r="B122" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
         <v>245</v>
-      </c>
-      <c r="B123" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
         <v>247</v>
-      </c>
-      <c r="B124" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" t="s">
         <v>249</v>
-      </c>
-      <c r="B125" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" t="s">
         <v>251</v>
-      </c>
-      <c r="B126" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" t="s">
         <v>253</v>
-      </c>
-      <c r="B127" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
         <v>255</v>
-      </c>
-      <c r="B128" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" t="s">
         <v>257</v>
-      </c>
-      <c r="B129" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" t="s">
         <v>259</v>
-      </c>
-      <c r="B130" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" t="s">
         <v>261</v>
-      </c>
-      <c r="B131" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
         <v>263</v>
-      </c>
-      <c r="B132" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" t="s">
         <v>265</v>
-      </c>
-      <c r="B133" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" t="s">
         <v>267</v>
-      </c>
-      <c r="B134" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" t="s">
         <v>269</v>
-      </c>
-      <c r="B135" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" t="s">
         <v>271</v>
-      </c>
-      <c r="B136" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" t="s">
         <v>273</v>
-      </c>
-      <c r="B137" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" t="s">
         <v>275</v>
-      </c>
-      <c r="B138" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>276</v>
+      </c>
+      <c r="B139" t="s">
         <v>277</v>
-      </c>
-      <c r="B139" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" t="s">
         <v>279</v>
-      </c>
-      <c r="B140" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>280</v>
+      </c>
+      <c r="B141" t="s">
         <v>281</v>
-      </c>
-      <c r="B141" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>282</v>
+      </c>
+      <c r="B142" t="s">
         <v>283</v>
-      </c>
-      <c r="B142" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" t="s">
         <v>285</v>
-      </c>
-      <c r="B143" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" t="s">
         <v>287</v>
-      </c>
-      <c r="B144" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" t="s">
         <v>289</v>
-      </c>
-      <c r="B145" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" t="s">
         <v>291</v>
-      </c>
-      <c r="B146" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" t="s">
         <v>293</v>
-      </c>
-      <c r="B147" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" t="s">
         <v>295</v>
-      </c>
-      <c r="B148" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" t="s">
         <v>297</v>
-      </c>
-      <c r="B149" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" t="s">
         <v>299</v>
-      </c>
-      <c r="B150" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" t="s">
         <v>301</v>
-      </c>
-      <c r="B151" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" t="s">
         <v>303</v>
-      </c>
-      <c r="B152" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>68</v>
+      </c>
+      <c r="B153" t="s">
         <v>69</v>
-      </c>
-      <c r="B153" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>304</v>
+      </c>
+      <c r="B154" t="s">
         <v>305</v>
-      </c>
-      <c r="B154" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>306</v>
+      </c>
+      <c r="B155" t="s">
         <v>307</v>
-      </c>
-      <c r="B155" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>308</v>
+      </c>
+      <c r="B156" t="s">
         <v>309</v>
-      </c>
-      <c r="B156" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>310</v>
+      </c>
+      <c r="B157" t="s">
         <v>311</v>
-      </c>
-      <c r="B157" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>312</v>
+      </c>
+      <c r="B158" t="s">
         <v>313</v>
-      </c>
-      <c r="B158" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>314</v>
+      </c>
+      <c r="B159" t="s">
         <v>315</v>
-      </c>
-      <c r="B159" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>316</v>
+      </c>
+      <c r="B160" t="s">
         <v>317</v>
-      </c>
-      <c r="B160" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" t="s">
         <v>319</v>
-      </c>
-      <c r="B161" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>320</v>
+      </c>
+      <c r="B162" t="s">
         <v>321</v>
-      </c>
-      <c r="B162" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>322</v>
+      </c>
+      <c r="B163" t="s">
         <v>323</v>
-      </c>
-      <c r="B163" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>324</v>
+      </c>
+      <c r="B164" t="s">
         <v>325</v>
-      </c>
-      <c r="B164" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>326</v>
+      </c>
+      <c r="B165" t="s">
         <v>327</v>
-      </c>
-      <c r="B165" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>328</v>
+      </c>
+      <c r="B166" t="s">
         <v>329</v>
-      </c>
-      <c r="B166" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>330</v>
+      </c>
+      <c r="B167" t="s">
         <v>331</v>
-      </c>
-      <c r="B167" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>332</v>
+      </c>
+      <c r="B168" t="s">
         <v>333</v>
-      </c>
-      <c r="B168" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>334</v>
+      </c>
+      <c r="B169" t="s">
         <v>335</v>
-      </c>
-      <c r="B169" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>336</v>
+      </c>
+      <c r="B170" t="s">
         <v>337</v>
-      </c>
-      <c r="B170" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>338</v>
+      </c>
+      <c r="B171" t="s">
         <v>339</v>
-      </c>
-      <c r="B171" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>340</v>
+      </c>
+      <c r="B172" t="s">
         <v>341</v>
-      </c>
-      <c r="B172" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>342</v>
+      </c>
+      <c r="B173" t="s">
         <v>343</v>
-      </c>
-      <c r="B173" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>344</v>
+      </c>
+      <c r="B174" t="s">
         <v>345</v>
-      </c>
-      <c r="B174" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>346</v>
+      </c>
+      <c r="B175" t="s">
         <v>347</v>
-      </c>
-      <c r="B175" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>348</v>
+      </c>
+      <c r="B176" t="s">
         <v>349</v>
-      </c>
-      <c r="B176" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>350</v>
+      </c>
+      <c r="B177" t="s">
         <v>351</v>
-      </c>
-      <c r="B177" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>352</v>
+      </c>
+      <c r="B178" t="s">
         <v>353</v>
-      </c>
-      <c r="B178" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>354</v>
+      </c>
+      <c r="B179" t="s">
         <v>355</v>
-      </c>
-      <c r="B179" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>356</v>
+      </c>
+      <c r="B180" t="s">
         <v>357</v>
-      </c>
-      <c r="B180" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>358</v>
+      </c>
+      <c r="B181" t="s">
         <v>359</v>
-      </c>
-      <c r="B181" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>360</v>
+      </c>
+      <c r="B182" t="s">
         <v>361</v>
-      </c>
-      <c r="B182" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>362</v>
+      </c>
+      <c r="B183" t="s">
         <v>363</v>
-      </c>
-      <c r="B183" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>364</v>
+      </c>
+      <c r="B184" t="s">
         <v>365</v>
-      </c>
-      <c r="B184" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>366</v>
+      </c>
+      <c r="B185" t="s">
         <v>367</v>
-      </c>
-      <c r="B185" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>368</v>
+      </c>
+      <c r="B186" t="s">
         <v>369</v>
-      </c>
-      <c r="B186" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>370</v>
+      </c>
+      <c r="B187" t="s">
         <v>371</v>
-      </c>
-      <c r="B187" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>372</v>
+      </c>
+      <c r="B188" t="s">
         <v>373</v>
-      </c>
-      <c r="B188" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>374</v>
+      </c>
+      <c r="B189" t="s">
         <v>375</v>
-      </c>
-      <c r="B189" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>376</v>
+      </c>
+      <c r="B190" t="s">
         <v>377</v>
-      </c>
-      <c r="B190" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>378</v>
+      </c>
+      <c r="B191" t="s">
         <v>379</v>
-      </c>
-      <c r="B191" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>380</v>
+      </c>
+      <c r="B192" t="s">
         <v>381</v>
-      </c>
-      <c r="B192" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>382</v>
+      </c>
+      <c r="B193" t="s">
         <v>383</v>
-      </c>
-      <c r="B193" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>384</v>
+      </c>
+      <c r="B194" t="s">
         <v>385</v>
-      </c>
-      <c r="B194" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>386</v>
+      </c>
+      <c r="B195" t="s">
         <v>387</v>
-      </c>
-      <c r="B195" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>388</v>
+      </c>
+      <c r="B196" t="s">
         <v>389</v>
-      </c>
-      <c r="B196" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>390</v>
+      </c>
+      <c r="B197" t="s">
         <v>391</v>
-      </c>
-      <c r="B197" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>392</v>
+      </c>
+      <c r="B198" t="s">
         <v>393</v>
-      </c>
-      <c r="B198" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>394</v>
+      </c>
+      <c r="B199" t="s">
         <v>395</v>
-      </c>
-      <c r="B199" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>396</v>
+      </c>
+      <c r="B200" t="s">
         <v>397</v>
-      </c>
-      <c r="B200" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>398</v>
+      </c>
+      <c r="B201" t="s">
         <v>399</v>
-      </c>
-      <c r="B201" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>400</v>
+      </c>
+      <c r="B202" t="s">
         <v>401</v>
-      </c>
-      <c r="B202" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>402</v>
+      </c>
+      <c r="B203" t="s">
         <v>403</v>
-      </c>
-      <c r="B203" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>404</v>
+      </c>
+      <c r="B204" t="s">
         <v>405</v>
-      </c>
-      <c r="B204" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>406</v>
+      </c>
+      <c r="B205" t="s">
         <v>407</v>
-      </c>
-      <c r="B205" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>408</v>
+      </c>
+      <c r="B206" t="s">
         <v>409</v>
-      </c>
-      <c r="B206" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>410</v>
+      </c>
+      <c r="B207" t="s">
         <v>411</v>
-      </c>
-      <c r="B207" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>412</v>
+      </c>
+      <c r="B208" t="s">
         <v>413</v>
-      </c>
-      <c r="B208" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>414</v>
+      </c>
+      <c r="B209" t="s">
         <v>415</v>
-      </c>
-      <c r="B209" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>416</v>
+      </c>
+      <c r="B210" t="s">
         <v>417</v>
-      </c>
-      <c r="B210" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>418</v>
+      </c>
+      <c r="B211" t="s">
         <v>419</v>
-      </c>
-      <c r="B211" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>420</v>
+      </c>
+      <c r="B212" t="s">
         <v>421</v>
-      </c>
-      <c r="B212" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>422</v>
+      </c>
+      <c r="B213" t="s">
         <v>423</v>
-      </c>
-      <c r="B213" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>424</v>
+      </c>
+      <c r="B214" t="s">
         <v>425</v>
-      </c>
-      <c r="B214" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>426</v>
+      </c>
+      <c r="B215" t="s">
         <v>427</v>
-      </c>
-      <c r="B215" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>428</v>
+      </c>
+      <c r="B216" t="s">
         <v>429</v>
-      </c>
-      <c r="B216" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>430</v>
+      </c>
+      <c r="B217" t="s">
         <v>431</v>
-      </c>
-      <c r="B217" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>432</v>
+      </c>
+      <c r="B218" t="s">
         <v>433</v>
-      </c>
-      <c r="B218" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>434</v>
+      </c>
+      <c r="B219" t="s">
         <v>435</v>
-      </c>
-      <c r="B219" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>436</v>
+      </c>
+      <c r="B220" t="s">
         <v>437</v>
-      </c>
-      <c r="B220" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>438</v>
+      </c>
+      <c r="B221" t="s">
         <v>439</v>
-      </c>
-      <c r="B221" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>440</v>
+      </c>
+      <c r="B222" t="s">
         <v>441</v>
-      </c>
-      <c r="B222" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>442</v>
+      </c>
+      <c r="B223" t="s">
         <v>443</v>
-      </c>
-      <c r="B223" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>444</v>
+      </c>
+      <c r="B224" t="s">
         <v>445</v>
-      </c>
-      <c r="B224" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>446</v>
+      </c>
+      <c r="B225" t="s">
         <v>447</v>
-      </c>
-      <c r="B225" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>448</v>
+      </c>
+      <c r="B226" t="s">
         <v>449</v>
-      </c>
-      <c r="B226" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>450</v>
+      </c>
+      <c r="B227" t="s">
         <v>451</v>
-      </c>
-      <c r="B227" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>452</v>
+      </c>
+      <c r="B228" t="s">
         <v>453</v>
-      </c>
-      <c r="B228" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>454</v>
+      </c>
+      <c r="B229" t="s">
         <v>455</v>
-      </c>
-      <c r="B229" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>456</v>
+      </c>
+      <c r="B230" t="s">
         <v>457</v>
-      </c>
-      <c r="B230" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>458</v>
+      </c>
+      <c r="B231" t="s">
         <v>459</v>
       </c>
-      <c r="B231" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232"/>
-      <c r="B232"/>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233"/>
-      <c r="B233"/>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234"/>
-      <c r="B234"/>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235"/>
-      <c r="B235"/>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236"/>
-      <c r="B236"/>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237"/>
-      <c r="B237"/>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238"/>
-      <c r="B238"/>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239"/>
-      <c r="B239"/>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240"/>
-      <c r="B240"/>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241"/>
-      <c r="B241"/>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242"/>
-      <c r="B242"/>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243"/>
-      <c r="B243"/>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244"/>
-      <c r="B244"/>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245"/>
-      <c r="B245"/>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246"/>
-      <c r="B246"/>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247"/>
-      <c r="B247"/>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248"/>
-      <c r="B248"/>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249"/>
-      <c r="B249"/>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250"/>
-      <c r="B250"/>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251"/>
-      <c r="B251"/>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252"/>
-      <c r="B252"/>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253"/>
-      <c r="B253"/>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254"/>
-      <c r="B254"/>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255"/>
-      <c r="B255"/>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A256"/>
-      <c r="B256"/>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A257"/>
-      <c r="B257"/>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A258"/>
-      <c r="B258"/>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A259"/>
-      <c r="B259"/>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A260"/>
-      <c r="B260"/>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A261"/>
-      <c r="B261"/>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A262"/>
-      <c r="B262"/>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A263"/>
-      <c r="B263"/>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264"/>
-      <c r="B264"/>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265"/>
-      <c r="B265"/>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266"/>
-      <c r="B266"/>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267"/>
-      <c r="B267"/>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268"/>
-      <c r="B268"/>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269"/>
-      <c r="B269"/>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270"/>
-      <c r="B270"/>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271"/>
-      <c r="B271"/>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272"/>
-      <c r="B272"/>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273"/>
-      <c r="B273"/>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274"/>
-      <c r="B274"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275"/>
-      <c r="B275"/>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276"/>
-      <c r="B276"/>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277"/>
-      <c r="B277"/>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278"/>
-      <c r="B278"/>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279"/>
-      <c r="B279"/>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280"/>
-      <c r="B280"/>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281"/>
-      <c r="B281"/>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282"/>
-      <c r="B282"/>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283"/>
-      <c r="B283"/>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284"/>
-      <c r="B284"/>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285"/>
-      <c r="B285"/>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286"/>
-      <c r="B286"/>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287"/>
-      <c r="B287"/>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288"/>
-      <c r="B288"/>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A289"/>
-      <c r="B289"/>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A290"/>
-      <c r="B290"/>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291"/>
-      <c r="B291"/>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292"/>
-      <c r="B292"/>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293"/>
-      <c r="B293"/>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294"/>
-      <c r="B294"/>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295"/>
-      <c r="B295"/>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296"/>
-      <c r="B296"/>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297"/>
-      <c r="B297"/>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298"/>
-      <c r="B298"/>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299"/>
-      <c r="B299"/>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300"/>
-      <c r="B300"/>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301"/>
-      <c r="B301"/>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302"/>
-      <c r="B302"/>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303"/>
-      <c r="B303"/>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304"/>
-      <c r="B304"/>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305"/>
-      <c r="B305"/>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306"/>
-      <c r="B306"/>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307"/>
-      <c r="B307"/>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308"/>
-      <c r="B308"/>
-    </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309"/>
-      <c r="B309"/>
-    </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310"/>
-      <c r="B310"/>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311"/>
-      <c r="B311"/>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312"/>
-      <c r="B312"/>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313"/>
-      <c r="B313"/>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314"/>
-      <c r="B314"/>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315"/>
-      <c r="B315"/>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316"/>
-      <c r="B316"/>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317"/>
-      <c r="B317"/>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318"/>
-      <c r="B318"/>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319"/>
-      <c r="B319"/>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320"/>
-      <c r="B320"/>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321"/>
-      <c r="B321"/>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322"/>
-      <c r="B322"/>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323"/>
-      <c r="B323"/>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324"/>
-      <c r="B324"/>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325"/>
-      <c r="B325"/>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326"/>
-      <c r="B326"/>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327"/>
-      <c r="B327"/>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328"/>
-      <c r="B328"/>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329"/>
-      <c r="B329"/>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330"/>
-      <c r="B330"/>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331"/>
-      <c r="B331"/>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332"/>
-      <c r="B332"/>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333"/>
-      <c r="B333"/>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334"/>
-      <c r="B334"/>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335"/>
-      <c r="B335"/>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336"/>
-      <c r="B336"/>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337"/>
-      <c r="B337"/>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338"/>
-      <c r="B338"/>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339"/>
-      <c r="B339"/>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340"/>
-      <c r="B340"/>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341"/>
-      <c r="B341"/>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342"/>
-      <c r="B342"/>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343"/>
-      <c r="B343"/>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344"/>
-      <c r="B344"/>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345"/>
-      <c r="B345"/>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346"/>
-      <c r="B346"/>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347"/>
-      <c r="B347"/>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348"/>
-      <c r="B348"/>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349"/>
-      <c r="B349"/>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350"/>
-      <c r="B350"/>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351"/>
-      <c r="B351"/>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352"/>
-      <c r="B352"/>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353"/>
-      <c r="B353"/>
-    </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354"/>
-      <c r="B354"/>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355"/>
-      <c r="B355"/>
-    </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356"/>
-      <c r="B356"/>
-    </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357"/>
-      <c r="B357"/>
-    </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358"/>
-      <c r="B358"/>
-    </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359"/>
-      <c r="B359"/>
-    </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360"/>
-      <c r="B360"/>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361"/>
-      <c r="B361"/>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362"/>
-      <c r="B362"/>
-    </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A363"/>
-      <c r="B363"/>
-    </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A364"/>
-      <c r="B364"/>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A365"/>
-      <c r="B365"/>
-    </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A366"/>
-      <c r="B366"/>
-    </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A367"/>
-      <c r="B367"/>
-    </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A368"/>
-      <c r="B368"/>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A369"/>
-      <c r="B369"/>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A370"/>
-      <c r="B370"/>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A371"/>
-      <c r="B371"/>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A372"/>
-      <c r="B372"/>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A373"/>
-      <c r="B373"/>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A374"/>
-      <c r="B374"/>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A375"/>
-      <c r="B375"/>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A376"/>
-      <c r="B376"/>
-    </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A377"/>
-      <c r="B377"/>
-    </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A378"/>
-      <c r="B378"/>
-    </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A379"/>
-      <c r="B379"/>
-    </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A380"/>
-      <c r="B380"/>
-    </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A381"/>
-      <c r="B381"/>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A382"/>
-      <c r="B382"/>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A383"/>
-      <c r="B383"/>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A384"/>
-      <c r="B384"/>
-    </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A385"/>
-      <c r="B385"/>
-    </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A386"/>
-      <c r="B386"/>
-    </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A387"/>
-      <c r="B387"/>
-    </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A388"/>
-      <c r="B388"/>
-    </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A389"/>
-      <c r="B389"/>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A390"/>
-      <c r="B390"/>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A391"/>
-      <c r="B391"/>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A392"/>
-      <c r="B392"/>
-    </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A393"/>
-      <c r="B393"/>
-    </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A394"/>
-      <c r="B394"/>
-    </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A395"/>
-      <c r="B395"/>
-    </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396"/>
-      <c r="B396"/>
-    </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A397"/>
-      <c r="B397"/>
-    </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A398"/>
-      <c r="B398"/>
-    </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A399"/>
-      <c r="B399"/>
-    </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A400"/>
-      <c r="B400"/>
-    </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A401"/>
-      <c r="B401"/>
-    </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A402"/>
-      <c r="B402"/>
-    </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A403"/>
-      <c r="B403"/>
-    </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A404"/>
-      <c r="B404"/>
-    </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A405"/>
-      <c r="B405"/>
-    </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A406"/>
-      <c r="B406"/>
-    </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A407"/>
-      <c r="B407"/>
-    </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408"/>
-      <c r="B408"/>
-    </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A409"/>
-      <c r="B409"/>
-    </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A410"/>
-      <c r="B410"/>
-    </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A411"/>
-      <c r="B411"/>
-    </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A412"/>
-      <c r="B412"/>
-    </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413"/>
-      <c r="B413"/>
-    </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414"/>
-      <c r="B414"/>
-    </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415"/>
-      <c r="B415"/>
-    </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A416"/>
-      <c r="B416"/>
-    </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A417"/>
-      <c r="B417"/>
-    </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A418"/>
-      <c r="B418"/>
-    </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A419"/>
-      <c r="B419"/>
-    </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A420"/>
-      <c r="B420"/>
-    </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A421"/>
-      <c r="B421"/>
-    </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422"/>
-      <c r="B422"/>
-    </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A423"/>
-      <c r="B423"/>
-    </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A424"/>
-      <c r="B424"/>
-    </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A425"/>
-      <c r="B425"/>
-    </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A426"/>
-      <c r="B426"/>
-    </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A427"/>
-      <c r="B427"/>
-    </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A428"/>
-      <c r="B428"/>
-    </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A429"/>
-      <c r="B429"/>
-    </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A430"/>
-      <c r="B430"/>
-    </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A431"/>
-      <c r="B431"/>
-    </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A432"/>
-      <c r="B432"/>
-    </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A433"/>
-      <c r="B433"/>
-    </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A434"/>
-      <c r="B434"/>
-    </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A435"/>
-      <c r="B435"/>
-    </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A436"/>
-      <c r="B436"/>
-    </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A437"/>
-      <c r="B437"/>
-    </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A438"/>
-      <c r="B438"/>
-    </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A439"/>
-      <c r="B439"/>
-    </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A440"/>
-      <c r="B440"/>
-    </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A441"/>
-      <c r="B441"/>
-    </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A442"/>
-      <c r="B442"/>
-    </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A443"/>
-      <c r="B443"/>
-    </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A444"/>
-      <c r="B444"/>
-    </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A445"/>
-      <c r="B445"/>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A446"/>
-      <c r="B446"/>
-    </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A447"/>
-      <c r="B447"/>
-    </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A448"/>
-      <c r="B448"/>
-    </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A449"/>
-      <c r="B449"/>
-    </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A450"/>
-      <c r="B450"/>
-    </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A451"/>
-      <c r="B451"/>
-    </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A452"/>
-      <c r="B452"/>
-    </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A453"/>
-      <c r="B453"/>
-    </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A454"/>
-      <c r="B454"/>
-    </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A455"/>
-      <c r="B455"/>
-    </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A456"/>
-      <c r="B456"/>
-    </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A457"/>
-      <c r="B457"/>
-    </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A458"/>
-      <c r="B458"/>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A459"/>
-      <c r="B459"/>
-    </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A460"/>
-      <c r="B460"/>
-    </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A461"/>
-      <c r="B461"/>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A462"/>
-      <c r="B462"/>
-    </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A463"/>
-      <c r="B463"/>
-    </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A464"/>
-      <c r="B464"/>
-    </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A465"/>
-      <c r="B465"/>
-    </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A466"/>
-      <c r="B466"/>
-    </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A467"/>
-      <c r="B467"/>
-    </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A468"/>
-      <c r="B468"/>
-    </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A469"/>
-      <c r="B469"/>
-    </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A470"/>
-      <c r="B470"/>
-    </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A471"/>
-      <c r="B471"/>
-    </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A472"/>
-      <c r="B472"/>
-    </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A473"/>
-      <c r="B473"/>
-    </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A474"/>
-      <c r="B474"/>
-    </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A475"/>
-      <c r="B475"/>
-    </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A476"/>
-      <c r="B476"/>
-    </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A477"/>
-      <c r="B477"/>
-    </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A478"/>
-      <c r="B478"/>
-    </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A479"/>
-      <c r="B479"/>
-    </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A480"/>
-      <c r="B480"/>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A481"/>
-      <c r="B481"/>
-    </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A482"/>
-      <c r="B482"/>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A483"/>
-      <c r="B483"/>
-    </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A484"/>
-      <c r="B484"/>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A485"/>
-      <c r="B485"/>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A486"/>
-      <c r="B486"/>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A487"/>
-      <c r="B487"/>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A488"/>
-      <c r="B488"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B489:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01454E28-C0A7-4BA7-98DF-496A332C1C4A}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>17505151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>17505151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>20303185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>20303185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>21358069</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>21361920</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>21361920</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>22107249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>22358123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>22358123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>22358149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>22358149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>23545310</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>23545310</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>23840920</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>23840920</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>24168512</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>24168512</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>24793449</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>24793449</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>26878138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>26878138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>27548540</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>27548540</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>28487592</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>28487592</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>29507880</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29507880</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>31510692</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31510692</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32399820</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>32399820</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>32627275</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>32627275</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>32808204</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>32808204</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>33018441</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>33018441</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>34194266</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>34194266</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>36253033</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>36253033</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>36424177</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>36424177</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>39954847</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>39954847</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>40995577</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>40995577</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A1:A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="93" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7350"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9756"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="910">
   <si>
     <t>DNI</t>
   </si>
@@ -2746,6 +2746,9 @@
   </si>
   <si>
     <t>SANSONE SANCHEZ LOURDES MARTINA</t>
+  </si>
+  <si>
+    <t>LUCERO BRIZUELA ENRIQUE ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -3063,14 +3066,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B530"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B531"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="52.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="52.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3086,7 +3089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3094,7 +3097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3118,7 +3121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3126,7 +3129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3134,7 +3137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3142,7 +3145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3158,7 +3161,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3166,7 +3169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3174,7 +3177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3182,7 +3185,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3190,7 +3193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3198,7 +3201,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3214,7 +3217,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3222,7 +3225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3230,7 +3233,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3238,7 +3241,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3246,7 +3249,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -3262,7 +3265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -3270,7 +3273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -3278,7 +3281,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -3294,7 +3297,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -3302,7 +3305,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -3310,7 +3313,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -3326,7 +3329,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -3334,7 +3337,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -3350,7 +3353,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -3358,7 +3361,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -3366,7 +3369,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -3390,7 +3393,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -3398,7 +3401,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -3406,7 +3409,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3425,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -3446,7 +3449,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -3462,7 +3465,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -3478,7 +3481,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -3486,7 +3489,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -3510,7 +3513,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -3518,7 +3521,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -3526,7 +3529,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -3534,7 +3537,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -3566,7 +3569,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -3574,7 +3577,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -3582,7 +3585,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>132</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -3614,7 +3617,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -3622,7 +3625,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -3630,7 +3633,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -3638,7 +3641,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>146</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>148</v>
       </c>
@@ -3670,7 +3673,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -3678,7 +3681,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>152</v>
       </c>
@@ -3686,7 +3689,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -3694,7 +3697,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>156</v>
       </c>
@@ -3702,7 +3705,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -3710,7 +3713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -3718,7 +3721,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -3726,7 +3729,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -3734,7 +3737,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>166</v>
       </c>
@@ -3742,7 +3745,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -3758,7 +3761,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>172</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>174</v>
       </c>
@@ -3774,7 +3777,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -3782,7 +3785,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>182</v>
       </c>
@@ -3806,7 +3809,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>184</v>
       </c>
@@ -3814,7 +3817,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>186</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>188</v>
       </c>
@@ -3830,7 +3833,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -3838,7 +3841,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -3854,7 +3857,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -3862,7 +3865,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -3878,7 +3881,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -3886,7 +3889,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -3894,7 +3897,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>206</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -3926,7 +3929,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>214</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -3950,7 +3953,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>220</v>
       </c>
@@ -3958,7 +3961,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>222</v>
       </c>
@@ -3966,7 +3969,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>224</v>
       </c>
@@ -3974,7 +3977,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>226</v>
       </c>
@@ -3982,7 +3985,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>230</v>
       </c>
@@ -3998,7 +4001,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4006,7 +4009,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>234</v>
       </c>
@@ -4014,7 +4017,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>236</v>
       </c>
@@ -4022,7 +4025,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>238</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -4038,7 +4041,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>242</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -4054,7 +4057,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>246</v>
       </c>
@@ -4062,7 +4065,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>248</v>
       </c>
@@ -4070,7 +4073,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>250</v>
       </c>
@@ -4078,7 +4081,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>252</v>
       </c>
@@ -4086,7 +4089,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>254</v>
       </c>
@@ -4094,7 +4097,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>256</v>
       </c>
@@ -4102,7 +4105,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>258</v>
       </c>
@@ -4110,7 +4113,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>260</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>262</v>
       </c>
@@ -4126,7 +4129,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>264</v>
       </c>
@@ -4134,7 +4137,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>266</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>268</v>
       </c>
@@ -4150,7 +4153,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>270</v>
       </c>
@@ -4158,7 +4161,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>272</v>
       </c>
@@ -4166,7 +4169,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>274</v>
       </c>
@@ -4174,7 +4177,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>276</v>
       </c>
@@ -4182,7 +4185,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>278</v>
       </c>
@@ -4190,7 +4193,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -4198,7 +4201,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>282</v>
       </c>
@@ -4206,7 +4209,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>284</v>
       </c>
@@ -4214,7 +4217,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>286</v>
       </c>
@@ -4222,7 +4225,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>288</v>
       </c>
@@ -4230,7 +4233,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>290</v>
       </c>
@@ -4238,7 +4241,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>292</v>
       </c>
@@ -4246,7 +4249,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>294</v>
       </c>
@@ -4254,7 +4257,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>296</v>
       </c>
@@ -4262,7 +4265,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>298</v>
       </c>
@@ -4270,7 +4273,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>300</v>
       </c>
@@ -4278,7 +4281,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>302</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>304</v>
       </c>
@@ -4294,7 +4297,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>306</v>
       </c>
@@ -4302,7 +4305,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>308</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>310</v>
       </c>
@@ -4318,7 +4321,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>312</v>
       </c>
@@ -4326,7 +4329,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>314</v>
       </c>
@@ -4334,7 +4337,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>316</v>
       </c>
@@ -4342,7 +4345,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>318</v>
       </c>
@@ -4350,7 +4353,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>320</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>322</v>
       </c>
@@ -4366,7 +4369,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>324</v>
       </c>
@@ -4374,7 +4377,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>326</v>
       </c>
@@ -4382,7 +4385,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>328</v>
       </c>
@@ -4390,7 +4393,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>330</v>
       </c>
@@ -4398,7 +4401,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -4406,7 +4409,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>334</v>
       </c>
@@ -4414,7 +4417,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>338</v>
       </c>
@@ -4430,7 +4433,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -4438,7 +4441,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>342</v>
       </c>
@@ -4446,7 +4449,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>344</v>
       </c>
@@ -4454,7 +4457,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -4462,7 +4465,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -4470,7 +4473,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>350</v>
       </c>
@@ -4478,7 +4481,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>352</v>
       </c>
@@ -4486,7 +4489,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -4494,7 +4497,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>356</v>
       </c>
@@ -4502,7 +4505,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>358</v>
       </c>
@@ -4510,7 +4513,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>360</v>
       </c>
@@ -4518,7 +4521,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>362</v>
       </c>
@@ -4526,7 +4529,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>364</v>
       </c>
@@ -4534,7 +4537,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>366</v>
       </c>
@@ -4542,7 +4545,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>368</v>
       </c>
@@ -4550,7 +4553,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>370</v>
       </c>
@@ -4558,7 +4561,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>372</v>
       </c>
@@ -4566,7 +4569,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>374</v>
       </c>
@@ -4574,7 +4577,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>376</v>
       </c>
@@ -4582,7 +4585,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>378</v>
       </c>
@@ -4590,7 +4593,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>380</v>
       </c>
@@ -4598,7 +4601,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>382</v>
       </c>
@@ -4606,7 +4609,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>384</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>386</v>
       </c>
@@ -4622,7 +4625,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>388</v>
       </c>
@@ -4630,7 +4633,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>390</v>
       </c>
@@ -4638,7 +4641,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>392</v>
       </c>
@@ -4646,7 +4649,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>394</v>
       </c>
@@ -4654,7 +4657,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>396</v>
       </c>
@@ -4662,7 +4665,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>398</v>
       </c>
@@ -4670,7 +4673,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>400</v>
       </c>
@@ -4678,7 +4681,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>402</v>
       </c>
@@ -4686,7 +4689,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>404</v>
       </c>
@@ -4694,7 +4697,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>406</v>
       </c>
@@ -4702,7 +4705,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>408</v>
       </c>
@@ -4710,7 +4713,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>410</v>
       </c>
@@ -4718,7 +4721,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>412</v>
       </c>
@@ -4726,7 +4729,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>414</v>
       </c>
@@ -4734,7 +4737,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>416</v>
       </c>
@@ -4742,7 +4745,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>418</v>
       </c>
@@ -4750,7 +4753,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>420</v>
       </c>
@@ -4758,7 +4761,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>422</v>
       </c>
@@ -4766,7 +4769,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>424</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>426</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>428</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>430</v>
       </c>
@@ -4798,7 +4801,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>432</v>
       </c>
@@ -4806,7 +4809,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>434</v>
       </c>
@@ -4814,7 +4817,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>436</v>
       </c>
@@ -4822,7 +4825,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>438</v>
       </c>
@@ -4830,7 +4833,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>442</v>
       </c>
@@ -4846,7 +4849,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>444</v>
       </c>
@@ -4854,7 +4857,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>446</v>
       </c>
@@ -4862,7 +4865,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>448</v>
       </c>
@@ -4870,7 +4873,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -4878,7 +4881,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>452</v>
       </c>
@@ -4886,7 +4889,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>454</v>
       </c>
@@ -4894,7 +4897,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>456</v>
       </c>
@@ -4902,7 +4905,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>458</v>
       </c>
@@ -4910,7 +4913,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>460</v>
       </c>
@@ -4918,7 +4921,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>462</v>
       </c>
@@ -4926,7 +4929,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>464</v>
       </c>
@@ -4934,7 +4937,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>466</v>
       </c>
@@ -4942,7 +4945,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>468</v>
       </c>
@@ -4950,7 +4953,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>470</v>
       </c>
@@ -4958,7 +4961,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>472</v>
       </c>
@@ -4966,7 +4969,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>474</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>476</v>
       </c>
@@ -4982,7 +4985,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>478</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>480</v>
       </c>
@@ -4998,7 +5001,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>482</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>484</v>
       </c>
@@ -5014,7 +5017,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>486</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>488</v>
       </c>
@@ -5030,7 +5033,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>490</v>
       </c>
@@ -5038,7 +5041,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>492</v>
       </c>
@@ -5046,7 +5049,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>494</v>
       </c>
@@ -5054,7 +5057,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>496</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>498</v>
       </c>
@@ -5070,7 +5073,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>500</v>
       </c>
@@ -5078,7 +5081,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>502</v>
       </c>
@@ -5086,7 +5089,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>504</v>
       </c>
@@ -5094,7 +5097,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>506</v>
       </c>
@@ -5102,7 +5105,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>508</v>
       </c>
@@ -5110,7 +5113,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>510</v>
       </c>
@@ -5118,7 +5121,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>512</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>514</v>
       </c>
@@ -5134,7 +5137,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>516</v>
       </c>
@@ -5142,7 +5145,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>518</v>
       </c>
@@ -5150,7 +5153,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>520</v>
       </c>
@@ -5158,7 +5161,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>522</v>
       </c>
@@ -5166,7 +5169,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>524</v>
       </c>
@@ -5174,7 +5177,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>526</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>528</v>
       </c>
@@ -5190,7 +5193,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>530</v>
       </c>
@@ -5198,7 +5201,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>532</v>
       </c>
@@ -5206,7 +5209,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>534</v>
       </c>
@@ -5214,7 +5217,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>536</v>
       </c>
@@ -5222,7 +5225,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>538</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>540</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>542</v>
       </c>
@@ -5246,7 +5249,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>544</v>
       </c>
@@ -5254,7 +5257,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>546</v>
       </c>
@@ -5262,7 +5265,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>548</v>
       </c>
@@ -5270,7 +5273,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>550</v>
       </c>
@@ -5278,7 +5281,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>552</v>
       </c>
@@ -5286,7 +5289,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>554</v>
       </c>
@@ -5294,7 +5297,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>556</v>
       </c>
@@ -5302,7 +5305,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>558</v>
       </c>
@@ -5310,7 +5313,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>560</v>
       </c>
@@ -5318,7 +5321,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>562</v>
       </c>
@@ -5326,7 +5329,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>564</v>
       </c>
@@ -5334,7 +5337,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>566</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>568</v>
       </c>
@@ -5350,7 +5353,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>570</v>
       </c>
@@ -5358,7 +5361,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>572</v>
       </c>
@@ -5366,7 +5369,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>574</v>
       </c>
@@ -5374,7 +5377,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>576</v>
       </c>
@@ -5382,7 +5385,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>578</v>
       </c>
@@ -5390,7 +5393,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>580</v>
       </c>
@@ -5398,7 +5401,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>582</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>584</v>
       </c>
@@ -5414,7 +5417,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>586</v>
       </c>
@@ -5422,7 +5425,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>588</v>
       </c>
@@ -5430,7 +5433,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>590</v>
       </c>
@@ -5438,7 +5441,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>592</v>
       </c>
@@ -5446,7 +5449,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>594</v>
       </c>
@@ -5454,7 +5457,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>596</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>598</v>
       </c>
@@ -5470,7 +5473,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>600</v>
       </c>
@@ -5478,7 +5481,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>602</v>
       </c>
@@ -5486,7 +5489,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>604</v>
       </c>
@@ -5494,7 +5497,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>606</v>
       </c>
@@ -5502,7 +5505,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>608</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>610</v>
       </c>
@@ -5518,7 +5521,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>612</v>
       </c>
@@ -5526,7 +5529,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>614</v>
       </c>
@@ -5534,7 +5537,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>616</v>
       </c>
@@ -5542,7 +5545,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>618</v>
       </c>
@@ -5550,7 +5553,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>620</v>
       </c>
@@ -5558,7 +5561,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>622</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>624</v>
       </c>
@@ -5574,7 +5577,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>626</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>628</v>
       </c>
@@ -5590,7 +5593,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>630</v>
       </c>
@@ -5598,7 +5601,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>632</v>
       </c>
@@ -5606,7 +5609,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>634</v>
       </c>
@@ -5614,7 +5617,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>636</v>
       </c>
@@ -5622,7 +5625,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>638</v>
       </c>
@@ -5630,7 +5633,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>640</v>
       </c>
@@ -5638,7 +5641,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>642</v>
       </c>
@@ -5646,7 +5649,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>644</v>
       </c>
@@ -5654,7 +5657,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>646</v>
       </c>
@@ -5662,7 +5665,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>648</v>
       </c>
@@ -5670,7 +5673,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>650</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>652</v>
       </c>
@@ -5686,7 +5689,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>468</v>
       </c>
@@ -5694,7 +5697,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>474</v>
       </c>
@@ -5702,7 +5705,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>654</v>
       </c>
@@ -5710,7 +5713,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>480</v>
       </c>
@@ -5718,7 +5721,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>656</v>
       </c>
@@ -5726,7 +5729,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>658</v>
       </c>
@@ -5734,7 +5737,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>660</v>
       </c>
@@ -5742,7 +5745,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>662</v>
       </c>
@@ -5750,7 +5753,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>664</v>
       </c>
@@ -5758,7 +5761,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>666</v>
       </c>
@@ -5766,7 +5769,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>668</v>
       </c>
@@ -5774,7 +5777,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>670</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>500</v>
       </c>
@@ -5790,7 +5793,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>672</v>
       </c>
@@ -5798,7 +5801,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>674</v>
       </c>
@@ -5806,7 +5809,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>676</v>
       </c>
@@ -5814,7 +5817,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>678</v>
       </c>
@@ -5822,7 +5825,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>680</v>
       </c>
@@ -5830,7 +5833,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>682</v>
       </c>
@@ -5838,7 +5841,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>684</v>
       </c>
@@ -5846,7 +5849,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>508</v>
       </c>
@@ -5854,7 +5857,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>686</v>
       </c>
@@ -5862,7 +5865,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>688</v>
       </c>
@@ -5870,7 +5873,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>690</v>
       </c>
@@ -5878,7 +5881,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>692</v>
       </c>
@@ -5886,7 +5889,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>694</v>
       </c>
@@ -5894,7 +5897,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>696</v>
       </c>
@@ -5902,7 +5905,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>698</v>
       </c>
@@ -5910,7 +5913,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>700</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>702</v>
       </c>
@@ -5926,7 +5929,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>704</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>706</v>
       </c>
@@ -5942,7 +5945,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>708</v>
       </c>
@@ -5950,7 +5953,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>534</v>
       </c>
@@ -5958,7 +5961,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>710</v>
       </c>
@@ -5966,7 +5969,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>712</v>
       </c>
@@ -5974,7 +5977,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>714</v>
       </c>
@@ -5982,7 +5985,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>716</v>
       </c>
@@ -5990,7 +5993,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>718</v>
       </c>
@@ -5998,7 +6001,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>720</v>
       </c>
@@ -6006,7 +6009,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>722</v>
       </c>
@@ -6014,7 +6017,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>724</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>726</v>
       </c>
@@ -6030,7 +6033,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>548</v>
       </c>
@@ -6038,7 +6041,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>728</v>
       </c>
@@ -6046,7 +6049,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>552</v>
       </c>
@@ -6054,7 +6057,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>730</v>
       </c>
@@ -6062,7 +6065,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>732</v>
       </c>
@@ -6070,7 +6073,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>734</v>
       </c>
@@ -6078,7 +6081,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>736</v>
       </c>
@@ -6086,7 +6089,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>738</v>
       </c>
@@ -6094,7 +6097,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>740</v>
       </c>
@@ -6102,7 +6105,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>742</v>
       </c>
@@ -6110,7 +6113,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>744</v>
       </c>
@@ -6118,7 +6121,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>746</v>
       </c>
@@ -6126,7 +6129,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>748</v>
       </c>
@@ -6134,7 +6137,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>568</v>
       </c>
@@ -6142,7 +6145,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>750</v>
       </c>
@@ -6150,7 +6153,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>752</v>
       </c>
@@ -6158,7 +6161,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>754</v>
       </c>
@@ -6166,7 +6169,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>756</v>
       </c>
@@ -6174,7 +6177,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>758</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>760</v>
       </c>
@@ -6190,7 +6193,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>762</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>764</v>
       </c>
@@ -6206,7 +6209,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>766</v>
       </c>
@@ -6214,7 +6217,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>768</v>
       </c>
@@ -6222,7 +6225,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>770</v>
       </c>
@@ -6230,7 +6233,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>772</v>
       </c>
@@ -6238,7 +6241,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>774</v>
       </c>
@@ -6246,7 +6249,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>776</v>
       </c>
@@ -6254,7 +6257,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>778</v>
       </c>
@@ -6262,7 +6265,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>42249921</v>
       </c>
@@ -6270,7 +6273,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>28720479</v>
       </c>
@@ -6278,7 +6281,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>25938406</v>
       </c>
@@ -6286,7 +6289,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>24836712</v>
       </c>
@@ -6294,7 +6297,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>25293914</v>
       </c>
@@ -6302,7 +6305,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>24020350</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>36253233</v>
       </c>
@@ -6318,7 +6321,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>30543896</v>
       </c>
@@ -6326,7 +6329,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>33848789</v>
       </c>
@@ -6334,7 +6337,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>31400553</v>
       </c>
@@ -6342,7 +6345,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>24426294</v>
       </c>
@@ -6350,7 +6353,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>22358829</v>
       </c>
@@ -6358,7 +6361,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>42516588</v>
       </c>
@@ -6366,7 +6369,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>22658475</v>
       </c>
@@ -6374,7 +6377,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>34696887</v>
       </c>
@@ -6382,7 +6385,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>28720232</v>
       </c>
@@ -6390,7 +6393,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>35507698</v>
       </c>
@@ -6398,7 +6401,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>22358400</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>23633749</v>
       </c>
@@ -6414,7 +6417,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>29797813</v>
       </c>
@@ -6422,7 +6425,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>23381084</v>
       </c>
@@ -6430,7 +6433,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>21113917</v>
       </c>
@@ -6438,7 +6441,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>39007947</v>
       </c>
@@ -6446,7 +6449,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>42711654</v>
       </c>
@@ -6454,7 +6457,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>35736626</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>22659091</v>
       </c>
@@ -6470,7 +6473,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>23721828</v>
       </c>
@@ -6478,7 +6481,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>32860121</v>
       </c>
@@ -6486,7 +6489,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>39007643</v>
       </c>
@@ -6494,7 +6497,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>35734810</v>
       </c>
@@ -6502,7 +6505,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>28475420</v>
       </c>
@@ -6510,7 +6513,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>25649234</v>
       </c>
@@ -6518,7 +6521,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>33585379</v>
       </c>
@@ -6526,7 +6529,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>27618572</v>
       </c>
@@ -6534,7 +6537,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>25132739</v>
       </c>
@@ -6542,7 +6545,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>22659699</v>
       </c>
@@ -6550,7 +6553,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>28727956</v>
       </c>
@@ -6558,7 +6561,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>28005986</v>
       </c>
@@ -6566,7 +6569,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>22754866</v>
       </c>
@@ -6574,7 +6577,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>21926882</v>
       </c>
@@ -6582,7 +6585,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>23417577</v>
       </c>
@@ -6590,7 +6593,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>37742475</v>
       </c>
@@ -6598,7 +6601,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>20624880</v>
       </c>
@@ -6606,7 +6609,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>20943321</v>
       </c>
@@ -6614,7 +6617,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>22958991</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>24283825</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>33095701</v>
       </c>
@@ -6638,7 +6641,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>28040737</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>24316586</v>
       </c>
@@ -6654,7 +6657,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>39011556</v>
       </c>
@@ -6662,7 +6665,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>29889038</v>
       </c>
@@ -6670,7 +6673,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>23027947</v>
       </c>
@@ -6678,7 +6681,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>23567086</v>
       </c>
@@ -6686,7 +6689,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>25938790</v>
       </c>
@@ -6694,7 +6697,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>25167459</v>
       </c>
@@ -6702,7 +6705,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>29621426</v>
       </c>
@@ -6710,7 +6713,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>32693381</v>
       </c>
@@ -6718,7 +6721,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>27350109</v>
       </c>
@@ -6726,7 +6729,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>30483502</v>
       </c>
@@ -6734,7 +6737,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>22673191</v>
       </c>
@@ -6742,7 +6745,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>26790199</v>
       </c>
@@ -6750,7 +6753,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>26791373</v>
       </c>
@@ -6758,7 +6761,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>31612151</v>
       </c>
@@ -6766,7 +6769,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>29889140</v>
       </c>
@@ -6774,7 +6777,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>33966629</v>
       </c>
@@ -6782,7 +6785,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>34920114</v>
       </c>
@@ -6790,7 +6793,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>35852166</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>34698849</v>
       </c>
@@ -6806,7 +6809,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>30473276</v>
       </c>
@@ -6814,7 +6817,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>41054898</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>41054263</v>
       </c>
@@ -6830,7 +6833,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>37741781</v>
       </c>
@@ -6838,7 +6841,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>33653268</v>
       </c>
@@ -6846,7 +6849,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>28475611</v>
       </c>
@@ -6854,7 +6857,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>32447643</v>
       </c>
@@ -6862,7 +6865,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>38015916</v>
       </c>
@@ -6870,7 +6873,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>24685334</v>
       </c>
@@ -6878,7 +6881,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>23380754</v>
       </c>
@@ -6886,7 +6889,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>29889022</v>
       </c>
@@ -6894,7 +6897,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>25118938</v>
       </c>
@@ -6902,7 +6905,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>45212741</v>
       </c>
@@ -6910,7 +6913,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>29264972</v>
       </c>
@@ -6918,7 +6921,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>34698649</v>
       </c>
@@ -6926,7 +6929,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>22705636</v>
       </c>
@@ -6934,7 +6937,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>34047511</v>
       </c>
@@ -6942,7 +6945,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>33846154</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>43489601</v>
       </c>
@@ -6958,7 +6961,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>28691608</v>
       </c>
@@ -6966,7 +6969,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>39652320</v>
       </c>
@@ -6974,7 +6977,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>24480148</v>
       </c>
@@ -6982,7 +6985,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>38077507</v>
       </c>
@@ -6990,7 +6993,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>28691512</v>
       </c>
@@ -6998,7 +7001,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>29176478</v>
       </c>
@@ -7006,7 +7009,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>22998994</v>
       </c>
@@ -7014,7 +7017,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>23189759</v>
       </c>
@@ -7022,7 +7025,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>30346214</v>
       </c>
@@ -7030,7 +7033,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>40469608</v>
       </c>
@@ -7038,7 +7041,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>33236934</v>
       </c>
@@ -7046,7 +7049,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>32624526</v>
       </c>
@@ -7054,7 +7057,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>28570734</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>26878735</v>
       </c>
@@ -7070,7 +7073,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>42805589</v>
       </c>
@@ -7078,7 +7081,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>31929750</v>
       </c>
@@ -7086,7 +7089,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>27350544</v>
       </c>
@@ -7094,7 +7097,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>32860413</v>
       </c>
@@ -7102,7 +7105,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>26790203</v>
       </c>
@@ -7110,7 +7113,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>24693939</v>
       </c>
@@ -7118,7 +7121,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>44062314</v>
       </c>
@@ -7126,7 +7129,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>26287456</v>
       </c>
@@ -7134,7 +7137,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>30688248</v>
       </c>
@@ -7142,7 +7145,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>37298216</v>
       </c>
@@ -7150,7 +7153,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>24526494</v>
       </c>
@@ -7158,7 +7161,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>23545139</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>25649754</v>
       </c>
@@ -7174,7 +7177,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>25714406</v>
       </c>
@@ -7182,7 +7185,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>22394173</v>
       </c>
@@ -7190,7 +7193,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>22227369</v>
       </c>
@@ -7198,7 +7201,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>25462507</v>
       </c>
@@ -7206,7 +7209,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>31442398</v>
       </c>
@@ -7214,7 +7217,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>29165996</v>
       </c>
@@ -7222,7 +7225,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>22207049</v>
       </c>
@@ -7230,7 +7233,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>22064306</v>
       </c>
@@ -7238,7 +7241,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>38460584</v>
       </c>
@@ -7246,7 +7249,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>32007429</v>
       </c>
@@ -7254,7 +7257,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>29407884</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>37507155</v>
       </c>
@@ -7270,7 +7273,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>22353650</v>
       </c>
@@ -7278,7 +7281,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>21358460</v>
       </c>
@@ -7286,7 +7289,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>35922801</v>
       </c>
@@ -7294,7 +7297,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>21358208</v>
       </c>
@@ -7302,12 +7305,20 @@
         <v>907</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>42516135</v>
       </c>
       <c r="B530" t="s">
         <v>908</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A531">
+        <v>24234442</v>
+      </c>
+      <c r="B531" t="s">
+        <v>909</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -27,7 +27,7 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>GOMEZ MARCELO D</t>
+    <t>GOMEZ MARCELO D.</t>
   </si>
 </sst>
 </file>
@@ -361,11 +361,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>23977476</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2">
-        <v>23977476</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="8472"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="906">
   <si>
     <t>DNI</t>
   </si>
@@ -27,7 +27,2716 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>GOMEZ MARCELO D.</t>
+    <t>25938790</t>
+  </si>
+  <si>
+    <t>21358078</t>
+  </si>
+  <si>
+    <t>31633022</t>
+  </si>
+  <si>
+    <t>33585215</t>
+  </si>
+  <si>
+    <t>32140317</t>
+  </si>
+  <si>
+    <t>24020387</t>
+  </si>
+  <si>
+    <t>25235267</t>
+  </si>
+  <si>
+    <t>44316665</t>
+  </si>
+  <si>
+    <t>32860358</t>
+  </si>
+  <si>
+    <t>29264972</t>
+  </si>
+  <si>
+    <t>22997803</t>
+  </si>
+  <si>
+    <t>40266078</t>
+  </si>
+  <si>
+    <t>29176391</t>
+  </si>
+  <si>
+    <t>41641380</t>
+  </si>
+  <si>
+    <t>37317352</t>
+  </si>
+  <si>
+    <t>25549818</t>
+  </si>
+  <si>
+    <t>31044010</t>
+  </si>
+  <si>
+    <t>28088836</t>
+  </si>
+  <si>
+    <t>23313993</t>
+  </si>
+  <si>
+    <t>41776139</t>
+  </si>
+  <si>
+    <t>32808209</t>
+  </si>
+  <si>
+    <t>34921414</t>
+  </si>
+  <si>
+    <t>22597626</t>
+  </si>
+  <si>
+    <t>24948017</t>
+  </si>
+  <si>
+    <t>43339747</t>
+  </si>
+  <si>
+    <t>27764037</t>
+  </si>
+  <si>
+    <t>31633291</t>
+  </si>
+  <si>
+    <t>29264277</t>
+  </si>
+  <si>
+    <t>39182783</t>
+  </si>
+  <si>
+    <t>26791373</t>
+  </si>
+  <si>
+    <t>22788303</t>
+  </si>
+  <si>
+    <t>40469608</t>
+  </si>
+  <si>
+    <t>39956307</t>
+  </si>
+  <si>
+    <t>28475399</t>
+  </si>
+  <si>
+    <t>35540958</t>
+  </si>
+  <si>
+    <t>40591335</t>
+  </si>
+  <si>
+    <t>26547884</t>
+  </si>
+  <si>
+    <t>32938192</t>
+  </si>
+  <si>
+    <t>39425333</t>
+  </si>
+  <si>
+    <t>39011581</t>
+  </si>
+  <si>
+    <t>38015916</t>
+  </si>
+  <si>
+    <t>21611516</t>
+  </si>
+  <si>
+    <t>24948239</t>
+  </si>
+  <si>
+    <t>36424280</t>
+  </si>
+  <si>
+    <t>24658607</t>
+  </si>
+  <si>
+    <t>42226338</t>
+  </si>
+  <si>
+    <t>28836306</t>
+  </si>
+  <si>
+    <t>30207271</t>
+  </si>
+  <si>
+    <t>33542493</t>
+  </si>
+  <si>
+    <t>42163190</t>
+  </si>
+  <si>
+    <t>22998994</t>
+  </si>
+  <si>
+    <t>24038971</t>
+  </si>
+  <si>
+    <t>29507754</t>
+  </si>
+  <si>
+    <t>25649754</t>
+  </si>
+  <si>
+    <t>35857424</t>
+  </si>
+  <si>
+    <t>34920250</t>
+  </si>
+  <si>
+    <t>28888531</t>
+  </si>
+  <si>
+    <t>24091788</t>
+  </si>
+  <si>
+    <t>28376681</t>
+  </si>
+  <si>
+    <t>43376753</t>
+  </si>
+  <si>
+    <t>40593773</t>
+  </si>
+  <si>
+    <t>23134176</t>
+  </si>
+  <si>
+    <t>22227369</t>
+  </si>
+  <si>
+    <t>35505524</t>
+  </si>
+  <si>
+    <t>23378930</t>
+  </si>
+  <si>
+    <t>41957633</t>
+  </si>
+  <si>
+    <t>38216143</t>
+  </si>
+  <si>
+    <t>30768369</t>
+  </si>
+  <si>
+    <t>31637344</t>
+  </si>
+  <si>
+    <t>32689387</t>
+  </si>
+  <si>
+    <t>27617420</t>
+  </si>
+  <si>
+    <t>29889040</t>
+  </si>
+  <si>
+    <t>33846154</t>
+  </si>
+  <si>
+    <t>38462016</t>
+  </si>
+  <si>
+    <t>43489601</t>
+  </si>
+  <si>
+    <t>33824661</t>
+  </si>
+  <si>
+    <t>34047511</t>
+  </si>
+  <si>
+    <t>39008802</t>
+  </si>
+  <si>
+    <t>40265282</t>
+  </si>
+  <si>
+    <t>33166539</t>
+  </si>
+  <si>
+    <t>40368871</t>
+  </si>
+  <si>
+    <t>28698273</t>
+  </si>
+  <si>
+    <t>39954564</t>
+  </si>
+  <si>
+    <t>24948044</t>
+  </si>
+  <si>
+    <t>20275510</t>
+  </si>
+  <si>
+    <t>29481420</t>
+  </si>
+  <si>
+    <t>28243055</t>
+  </si>
+  <si>
+    <t>22997906</t>
+  </si>
+  <si>
+    <t>34590320</t>
+  </si>
+  <si>
+    <t>24879776</t>
+  </si>
+  <si>
+    <t>28742660</t>
+  </si>
+  <si>
+    <t>32353250</t>
+  </si>
+  <si>
+    <t>28720656</t>
+  </si>
+  <si>
+    <t>23046816</t>
+  </si>
+  <si>
+    <t>28570734</t>
+  </si>
+  <si>
+    <t>36586207</t>
+  </si>
+  <si>
+    <t>32860471</t>
+  </si>
+  <si>
+    <t>39995825</t>
+  </si>
+  <si>
+    <t>32689745</t>
+  </si>
+  <si>
+    <t>24735473</t>
+  </si>
+  <si>
+    <t>30768543</t>
+  </si>
+  <si>
+    <t>21359584</t>
+  </si>
+  <si>
+    <t>35023545</t>
+  </si>
+  <si>
+    <t>31401507</t>
+  </si>
+  <si>
+    <t>34062332</t>
+  </si>
+  <si>
+    <t>36253292</t>
+  </si>
+  <si>
+    <t>35735583</t>
+  </si>
+  <si>
+    <t>23735503</t>
+  </si>
+  <si>
+    <t>28726347</t>
+  </si>
+  <si>
+    <t>38075570</t>
+  </si>
+  <si>
+    <t>39524637</t>
+  </si>
+  <si>
+    <t>35508892</t>
+  </si>
+  <si>
+    <t>31510070</t>
+  </si>
+  <si>
+    <t>24480148</t>
+  </si>
+  <si>
+    <t>34861374</t>
+  </si>
+  <si>
+    <t>32724101</t>
+  </si>
+  <si>
+    <t>36254114</t>
+  </si>
+  <si>
+    <t>29996963</t>
+  </si>
+  <si>
+    <t>34193964</t>
+  </si>
+  <si>
+    <t>31812750</t>
+  </si>
+  <si>
+    <t>26790199</t>
+  </si>
+  <si>
+    <t>26791267</t>
+  </si>
+  <si>
+    <t>29621426</t>
+  </si>
+  <si>
+    <t>38462967</t>
+  </si>
+  <si>
+    <t>35849116</t>
+  </si>
+  <si>
+    <t>28243919</t>
+  </si>
+  <si>
+    <t>31612151</t>
+  </si>
+  <si>
+    <t>24948340</t>
+  </si>
+  <si>
+    <t>28263330</t>
+  </si>
+  <si>
+    <t>24331464</t>
+  </si>
+  <si>
+    <t>23977768</t>
+  </si>
+  <si>
+    <t>33766697</t>
+  </si>
+  <si>
+    <t>29557897</t>
+  </si>
+  <si>
+    <t>35734728</t>
+  </si>
+  <si>
+    <t>30688248</t>
+  </si>
+  <si>
+    <t>31812653</t>
+  </si>
+  <si>
+    <t>30091137</t>
+  </si>
+  <si>
+    <t>26288232</t>
+  </si>
+  <si>
+    <t>28444448</t>
+  </si>
+  <si>
+    <t>26790662</t>
+  </si>
+  <si>
+    <t>24526494</t>
+  </si>
+  <si>
+    <t>33793757</t>
+  </si>
+  <si>
+    <t>29889140</t>
+  </si>
+  <si>
+    <t>26184924</t>
+  </si>
+  <si>
+    <t>22063365</t>
+  </si>
+  <si>
+    <t>30768456</t>
+  </si>
+  <si>
+    <t>25938062</t>
+  </si>
+  <si>
+    <t>32693381</t>
+  </si>
+  <si>
+    <t>33836577</t>
+  </si>
+  <si>
+    <t>22403163</t>
+  </si>
+  <si>
+    <t>31129536</t>
+  </si>
+  <si>
+    <t>25252982</t>
+  </si>
+  <si>
+    <t>40728333</t>
+  </si>
+  <si>
+    <t>28475611</t>
+  </si>
+  <si>
+    <t>22496588</t>
+  </si>
+  <si>
+    <t>29058219</t>
+  </si>
+  <si>
+    <t>23576194</t>
+  </si>
+  <si>
+    <t>41297188</t>
+  </si>
+  <si>
+    <t>30708968</t>
+  </si>
+  <si>
+    <t>18542025</t>
+  </si>
+  <si>
+    <t>32689022</t>
+  </si>
+  <si>
+    <t>23498141</t>
+  </si>
+  <si>
+    <t>33236630</t>
+  </si>
+  <si>
+    <t>29889022</t>
+  </si>
+  <si>
+    <t>27784046</t>
+  </si>
+  <si>
+    <t>27260920</t>
+  </si>
+  <si>
+    <t>29034892</t>
+  </si>
+  <si>
+    <t>24689934</t>
+  </si>
+  <si>
+    <t>24836599</t>
+  </si>
+  <si>
+    <t>32454349</t>
+  </si>
+  <si>
+    <t>28691512</t>
+  </si>
+  <si>
+    <t>27041941</t>
+  </si>
+  <si>
+    <t>26831361</t>
+  </si>
+  <si>
+    <t>21361540</t>
+  </si>
+  <si>
+    <t>22291766</t>
+  </si>
+  <si>
+    <t>35149329</t>
+  </si>
+  <si>
+    <t>29588018</t>
+  </si>
+  <si>
+    <t>28020998</t>
+  </si>
+  <si>
+    <t>23381088</t>
+  </si>
+  <si>
+    <t>25167119</t>
+  </si>
+  <si>
+    <t>34698649</t>
+  </si>
+  <si>
+    <t>35923242</t>
+  </si>
+  <si>
+    <t>26791092</t>
+  </si>
+  <si>
+    <t>25573317</t>
+  </si>
+  <si>
+    <t>34920112</t>
+  </si>
+  <si>
+    <t>42858441</t>
+  </si>
+  <si>
+    <t>21361896</t>
+  </si>
+  <si>
+    <t>38076680</t>
+  </si>
+  <si>
+    <t>37741781</t>
+  </si>
+  <si>
+    <t>41531659</t>
+  </si>
+  <si>
+    <t>41909067</t>
+  </si>
+  <si>
+    <t>24038054</t>
+  </si>
+  <si>
+    <t>21360534</t>
+  </si>
+  <si>
+    <t>22904364</t>
+  </si>
+  <si>
+    <t>37531215</t>
+  </si>
+  <si>
+    <t>26360347</t>
+  </si>
+  <si>
+    <t>25786427</t>
+  </si>
+  <si>
+    <t>23977864</t>
+  </si>
+  <si>
+    <t>35153426</t>
+  </si>
+  <si>
+    <t>30483703</t>
+  </si>
+  <si>
+    <t>34054299</t>
+  </si>
+  <si>
+    <t>26287456</t>
+  </si>
+  <si>
+    <t>31183495</t>
+  </si>
+  <si>
+    <t>22003386</t>
+  </si>
+  <si>
+    <t>33585145</t>
+  </si>
+  <si>
+    <t>28005787</t>
+  </si>
+  <si>
+    <t>31005291</t>
+  </si>
+  <si>
+    <t>34111462</t>
+  </si>
+  <si>
+    <t>23982654</t>
+  </si>
+  <si>
+    <t>36034208</t>
+  </si>
+  <si>
+    <t>23189759</t>
+  </si>
+  <si>
+    <t>41083294</t>
+  </si>
+  <si>
+    <t>35023667</t>
+  </si>
+  <si>
+    <t>32624526</t>
+  </si>
+  <si>
+    <t>39652724</t>
+  </si>
+  <si>
+    <t>24693939</t>
+  </si>
+  <si>
+    <t>30071212</t>
+  </si>
+  <si>
+    <t>22327877</t>
+  </si>
+  <si>
+    <t>29758069</t>
+  </si>
+  <si>
+    <t>29507930</t>
+  </si>
+  <si>
+    <t>36687700</t>
+  </si>
+  <si>
+    <t>23791694</t>
+  </si>
+  <si>
+    <t>39011460</t>
+  </si>
+  <si>
+    <t>25714406</t>
+  </si>
+  <si>
+    <t>38594322</t>
+  </si>
+  <si>
+    <t>28475289</t>
+  </si>
+  <si>
+    <t>31044279</t>
+  </si>
+  <si>
+    <t>28218612</t>
+  </si>
+  <si>
+    <t>33542391</t>
+  </si>
+  <si>
+    <t>26287553</t>
+  </si>
+  <si>
+    <t>32929541</t>
+  </si>
+  <si>
+    <t>27916706</t>
+  </si>
+  <si>
+    <t>35210165</t>
+  </si>
+  <si>
+    <t>34921355</t>
+  </si>
+  <si>
+    <t>32447643</t>
+  </si>
+  <si>
+    <t>27424825</t>
+  </si>
+  <si>
+    <t>31372237</t>
+  </si>
+  <si>
+    <t>32860413</t>
+  </si>
+  <si>
+    <t>35849137</t>
+  </si>
+  <si>
+    <t>29174766</t>
+  </si>
+  <si>
+    <t>23567086</t>
+  </si>
+  <si>
+    <t>38463696</t>
+  </si>
+  <si>
+    <t>34255785</t>
+  </si>
+  <si>
+    <t>30709458</t>
+  </si>
+  <si>
+    <t>26717736</t>
+  </si>
+  <si>
+    <t>27614081</t>
+  </si>
+  <si>
+    <t>24234532</t>
+  </si>
+  <si>
+    <t>22394173</t>
+  </si>
+  <si>
+    <t>41054689</t>
+  </si>
+  <si>
+    <t>22011651</t>
+  </si>
+  <si>
+    <t>29427250</t>
+  </si>
+  <si>
+    <t>18512033</t>
+  </si>
+  <si>
+    <t>24168512</t>
+  </si>
+  <si>
+    <t>28967984</t>
+  </si>
+  <si>
+    <t>28218511</t>
+  </si>
+  <si>
+    <t>33058726</t>
+  </si>
+  <si>
+    <t>34328943</t>
+  </si>
+  <si>
+    <t>26878735</t>
+  </si>
+  <si>
+    <t>30768546</t>
+  </si>
+  <si>
+    <t>33591885</t>
+  </si>
+  <si>
+    <t>27784815</t>
+  </si>
+  <si>
+    <t>28773601</t>
+  </si>
+  <si>
+    <t>39790589</t>
+  </si>
+  <si>
+    <t>25590318</t>
+  </si>
+  <si>
+    <t>31214229</t>
+  </si>
+  <si>
+    <t>22003602</t>
+  </si>
+  <si>
+    <t>34062403</t>
+  </si>
+  <si>
+    <t>29481342</t>
+  </si>
+  <si>
+    <t>33460625</t>
+  </si>
+  <si>
+    <t>23982696</t>
+  </si>
+  <si>
+    <t>33653268</t>
+  </si>
+  <si>
+    <t>32689353</t>
+  </si>
+  <si>
+    <t>27527828</t>
+  </si>
+  <si>
+    <t>35508964</t>
+  </si>
+  <si>
+    <t>31514109</t>
+  </si>
+  <si>
+    <t>29529656</t>
+  </si>
+  <si>
+    <t>21360110</t>
+  </si>
+  <si>
+    <t>38463693</t>
+  </si>
+  <si>
+    <t>27350109</t>
+  </si>
+  <si>
+    <t>38077507</t>
+  </si>
+  <si>
+    <t>23378720</t>
+  </si>
+  <si>
+    <t>34195028</t>
+  </si>
+  <si>
+    <t>41270878</t>
+  </si>
+  <si>
+    <t>27692001</t>
+  </si>
+  <si>
+    <t>28243469</t>
+  </si>
+  <si>
+    <t>21610090</t>
+  </si>
+  <si>
+    <t>36587847</t>
+  </si>
+  <si>
+    <t>25118938</t>
+  </si>
+  <si>
+    <t>33321722</t>
+  </si>
+  <si>
+    <t>29740987</t>
+  </si>
+  <si>
+    <t>35851429</t>
+  </si>
+  <si>
+    <t>37462087</t>
+  </si>
+  <si>
+    <t>24244588</t>
+  </si>
+  <si>
+    <t>21362663</t>
+  </si>
+  <si>
+    <t>22065100</t>
+  </si>
+  <si>
+    <t>31129932</t>
+  </si>
+  <si>
+    <t>21610137</t>
+  </si>
+  <si>
+    <t>30626591</t>
+  </si>
+  <si>
+    <t>32354359</t>
+  </si>
+  <si>
+    <t>20505067</t>
+  </si>
+  <si>
+    <t>31510739</t>
+  </si>
+  <si>
+    <t>24948792</t>
+  </si>
+  <si>
+    <t>25938076</t>
+  </si>
+  <si>
+    <t>20302274</t>
+  </si>
+  <si>
+    <t>38590823</t>
+  </si>
+  <si>
+    <t>38015814</t>
+  </si>
+  <si>
+    <t>34875969</t>
+  </si>
+  <si>
+    <t>22935616</t>
+  </si>
+  <si>
+    <t>25937702</t>
+  </si>
+  <si>
+    <t>29992536</t>
+  </si>
+  <si>
+    <t>21357706</t>
+  </si>
+  <si>
+    <t>24301776</t>
+  </si>
+  <si>
+    <t>27350957</t>
+  </si>
+  <si>
+    <t>36175681</t>
+  </si>
+  <si>
+    <t>22107306</t>
+  </si>
+  <si>
+    <t>45264486</t>
+  </si>
+  <si>
+    <t>31979400</t>
+  </si>
+  <si>
+    <t>22658634</t>
+  </si>
+  <si>
+    <t>39954625</t>
+  </si>
+  <si>
+    <t>39920089</t>
+  </si>
+  <si>
+    <t>30568025</t>
+  </si>
+  <si>
+    <t>18515039</t>
+  </si>
+  <si>
+    <t>27350544</t>
+  </si>
+  <si>
+    <t>28967988</t>
+  </si>
+  <si>
+    <t>36250401</t>
+  </si>
+  <si>
+    <t>32116785</t>
+  </si>
+  <si>
+    <t>26441626</t>
+  </si>
+  <si>
+    <t>41321909</t>
+  </si>
+  <si>
+    <t>29371693</t>
+  </si>
+  <si>
+    <t>24972343</t>
+  </si>
+  <si>
+    <t>26790203</t>
+  </si>
+  <si>
+    <t>30631066</t>
+  </si>
+  <si>
+    <t>31098504</t>
+  </si>
+  <si>
+    <t>29098038</t>
+  </si>
+  <si>
+    <t>34920563</t>
+  </si>
+  <si>
+    <t>29889038</t>
+  </si>
+  <si>
+    <t>35848301</t>
+  </si>
+  <si>
+    <t>26740703</t>
+  </si>
+  <si>
+    <t>24464052</t>
+  </si>
+  <si>
+    <t>31125541</t>
+  </si>
+  <si>
+    <t>17120081</t>
+  </si>
+  <si>
+    <t>32116552</t>
+  </si>
+  <si>
+    <t>36250107</t>
+  </si>
+  <si>
+    <t>22438126</t>
+  </si>
+  <si>
+    <t>28005372</t>
+  </si>
+  <si>
+    <t>37742342</t>
+  </si>
+  <si>
+    <t>36034140</t>
+  </si>
+  <si>
+    <t>27268829</t>
+  </si>
+  <si>
+    <t>30634134</t>
+  </si>
+  <si>
+    <t>39793237</t>
+  </si>
+  <si>
+    <t>33460611</t>
+  </si>
+  <si>
+    <t>26611976</t>
+  </si>
+  <si>
+    <t>39184078</t>
+  </si>
+  <si>
+    <t>25938634</t>
+  </si>
+  <si>
+    <t>36423327</t>
+  </si>
+  <si>
+    <t>25118960</t>
+  </si>
+  <si>
+    <t>29176478</t>
+  </si>
+  <si>
+    <t>34698849</t>
+  </si>
+  <si>
+    <t>31869190</t>
+  </si>
+  <si>
+    <t>29176054</t>
+  </si>
+  <si>
+    <t>22741180</t>
+  </si>
+  <si>
+    <t>26790007</t>
+  </si>
+  <si>
+    <t>20275847</t>
+  </si>
+  <si>
+    <t>35857614</t>
+  </si>
+  <si>
+    <t>24331478</t>
+  </si>
+  <si>
+    <t>22003434</t>
+  </si>
+  <si>
+    <t>22003316</t>
+  </si>
+  <si>
+    <t>39010882</t>
+  </si>
+  <si>
+    <t>30634913</t>
+  </si>
+  <si>
+    <t>43489066</t>
+  </si>
+  <si>
+    <t>35509126</t>
+  </si>
+  <si>
+    <t>28967232</t>
+  </si>
+  <si>
+    <t>22107238</t>
+  </si>
+  <si>
+    <t>25550549</t>
+  </si>
+  <si>
+    <t>27574468</t>
+  </si>
+  <si>
+    <t>34915707</t>
+  </si>
+  <si>
+    <t>29960150</t>
+  </si>
+  <si>
+    <t>30872546</t>
+  </si>
+  <si>
+    <t>42805589</t>
+  </si>
+  <si>
+    <t>32807441</t>
+  </si>
+  <si>
+    <t>35852166</t>
+  </si>
+  <si>
+    <t>18011237</t>
+  </si>
+  <si>
+    <t>20344716</t>
+  </si>
+  <si>
+    <t>31401286</t>
+  </si>
+  <si>
+    <t>26791241</t>
+  </si>
+  <si>
+    <t>21360428</t>
+  </si>
+  <si>
+    <t>41321985</t>
+  </si>
+  <si>
+    <t>21375907</t>
+  </si>
+  <si>
+    <t>31370678</t>
+  </si>
+  <si>
+    <t>30688478</t>
+  </si>
+  <si>
+    <t>31929750</t>
+  </si>
+  <si>
+    <t>34047688</t>
+  </si>
+  <si>
+    <t>32807801</t>
+  </si>
+  <si>
+    <t>37833233</t>
+  </si>
+  <si>
+    <t>43078029</t>
+  </si>
+  <si>
+    <t>26611330</t>
+  </si>
+  <si>
+    <t>41468942</t>
+  </si>
+  <si>
+    <t>29621468</t>
+  </si>
+  <si>
+    <t>22159146</t>
+  </si>
+  <si>
+    <t>30243868</t>
+  </si>
+  <si>
+    <t>33715091</t>
+  </si>
+  <si>
+    <t>24685334</t>
+  </si>
+  <si>
+    <t>22358379</t>
+  </si>
+  <si>
+    <t>35505461</t>
+  </si>
+  <si>
+    <t>25714472</t>
+  </si>
+  <si>
+    <t>37924686</t>
+  </si>
+  <si>
+    <t>27527938</t>
+  </si>
+  <si>
+    <t>32938114</t>
+  </si>
+  <si>
+    <t>35852486</t>
+  </si>
+  <si>
+    <t>28040440</t>
+  </si>
+  <si>
+    <t>29621183</t>
+  </si>
+  <si>
+    <t>36377307</t>
+  </si>
+  <si>
+    <t>35848287</t>
+  </si>
+  <si>
+    <t>25938967</t>
+  </si>
+  <si>
+    <t>37297759</t>
+  </si>
+  <si>
+    <t>30920272</t>
+  </si>
+  <si>
+    <t>42163764</t>
+  </si>
+  <si>
+    <t>41054009</t>
+  </si>
+  <si>
+    <t>32454499</t>
+  </si>
+  <si>
+    <t>31129641</t>
+  </si>
+  <si>
+    <t>24480426</t>
+  </si>
+  <si>
+    <t>27406797</t>
+  </si>
+  <si>
+    <t>33117660</t>
+  </si>
+  <si>
+    <t>39010057</t>
+  </si>
+  <si>
+    <t>22753593</t>
+  </si>
+  <si>
+    <t>22227370</t>
+  </si>
+  <si>
+    <t>32878003</t>
+  </si>
+  <si>
+    <t>38015746</t>
+  </si>
+  <si>
+    <t>30892789</t>
+  </si>
+  <si>
+    <t>42356896</t>
+  </si>
+  <si>
+    <t>38460584</t>
+  </si>
+  <si>
+    <t>27261140</t>
+  </si>
+  <si>
+    <t>38075342</t>
+  </si>
+  <si>
+    <t>21935770</t>
+  </si>
+  <si>
+    <t>31129543</t>
+  </si>
+  <si>
+    <t>26354224</t>
+  </si>
+  <si>
+    <t>36253215</t>
+  </si>
+  <si>
+    <t>33672552</t>
+  </si>
+  <si>
+    <t>29481582</t>
+  </si>
+  <si>
+    <t>32807934</t>
+  </si>
+  <si>
+    <t>24480179</t>
+  </si>
+  <si>
+    <t>31442398</t>
+  </si>
+  <si>
+    <t>28786225</t>
+  </si>
+  <si>
+    <t>28727916</t>
+  </si>
+  <si>
+    <t>24087598</t>
+  </si>
+  <si>
+    <t>18420141</t>
+  </si>
+  <si>
+    <t>25649373</t>
+  </si>
+  <si>
+    <t>25649306</t>
+  </si>
+  <si>
+    <t>31812622</t>
+  </si>
+  <si>
+    <t>33236803</t>
+  </si>
+  <si>
+    <t>31005506</t>
+  </si>
+  <si>
+    <t>CABRERA MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>TOLOMEO MARIA SILVINA</t>
+  </si>
+  <si>
+    <t>MONTANA CRISTINA VANESA</t>
+  </si>
+  <si>
+    <t>MOLINA LORENA GISELLE</t>
+  </si>
+  <si>
+    <t>VEGA CASTILLA VANINA NOELIA</t>
+  </si>
+  <si>
+    <t>ALANIZ MARTA CESILIA</t>
+  </si>
+  <si>
+    <t>ZEPEDA SILVANA ANDREA</t>
+  </si>
+  <si>
+    <t>BALMACEDA GOMEZ TAMARA NATALI</t>
+  </si>
+  <si>
+    <t>SANCHEZ JOHANA MARIANELA</t>
+  </si>
+  <si>
+    <t>PONCE FELIPUCHE CRISTINA NATALIA</t>
+  </si>
+  <si>
+    <t>ARAYA ANDREA FABIANA</t>
+  </si>
+  <si>
+    <t>VEGA MELANIE YAMILA</t>
+  </si>
+  <si>
+    <t>LUNA VERA EMELINA SUSANA</t>
+  </si>
+  <si>
+    <t>GUZMAN ROCIO MARCELA</t>
+  </si>
+  <si>
+    <t>ALCUCERO MARIA BELEN</t>
+  </si>
+  <si>
+    <t>TELLO MARTA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>FLORES MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ ROCIO DEL PILAR</t>
+  </si>
+  <si>
+    <t>AVILA GABRIELA ISABEL</t>
+  </si>
+  <si>
+    <t>CATALDO DIAZ CARLA NOEM</t>
+  </si>
+  <si>
+    <t>GONZALEZ MOLINA MARIANELA</t>
+  </si>
+  <si>
+    <t>BAZAN CUELLO FERNANDO ARIEL</t>
+  </si>
+  <si>
+    <t>FARIAS MUÑOZ GLADYS MIRTHA</t>
+  </si>
+  <si>
+    <t>SANCHEZ MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>PEÑALOZA GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>SIGAMPA VANESA MARISOL</t>
+  </si>
+  <si>
+    <t>SANCHEZ ESCAMILLA MIRIAN</t>
+  </si>
+  <si>
+    <t>PALACIO DANIELA ELIANA</t>
+  </si>
+  <si>
+    <t>AVENDAÑO VERA LORENA GISEL</t>
+  </si>
+  <si>
+    <t>BORGES ALEJANDRA CRISTINA</t>
+  </si>
+  <si>
+    <t>MARTIN DELIA BARBARA</t>
+  </si>
+  <si>
+    <t>CARRIZO ARACENA MARIA ALDANA</t>
+  </si>
+  <si>
+    <t>SALINAS LOPEZ CARLA GABRIELA</t>
+  </si>
+  <si>
+    <t>BOLADO ISMAEL EMILIO</t>
+  </si>
+  <si>
+    <t>RAMOS CAMACHO SAMUEL EXEQUIEL</t>
+  </si>
+  <si>
+    <t>STABILE GILDA JAZMN</t>
+  </si>
+  <si>
+    <t>VIVARES ROSANA NOELIA</t>
+  </si>
+  <si>
+    <t>ESCUDERO BORBORE SILVANA BELEN</t>
+  </si>
+  <si>
+    <t>HERRERA LUCILA VIRGINIA EDITH</t>
+  </si>
+  <si>
+    <t>FRIAS FATIMA CELESTE</t>
+  </si>
+  <si>
+    <t>VARELA FIGUEROA CAREN ALESANDRA</t>
+  </si>
+  <si>
+    <t>LORENZO MARIA ROSA</t>
+  </si>
+  <si>
+    <t>ASTUDILLO CARINA LORENA</t>
+  </si>
+  <si>
+    <t>ROSSOMANDO MANCHADO PAOLA ANTONELLA</t>
+  </si>
+  <si>
+    <t>ROVIRA GOMEZ MARIA VERONICA</t>
+  </si>
+  <si>
+    <t>DIAZ GORDILLO LUDMILA</t>
+  </si>
+  <si>
+    <t>SUAREZ GEMA LETICIA</t>
+  </si>
+  <si>
+    <t>BARBOZA EMILIA YOLANDA</t>
+  </si>
+  <si>
+    <t>OLIVERA GISELA ROMINA</t>
+  </si>
+  <si>
+    <t>BARAZA MENENDEZ FERNANDA GUADALUPE</t>
+  </si>
+  <si>
+    <t>PEREZ IVANA VERONICA</t>
+  </si>
+  <si>
+    <t>PAEZ GRACIELA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ LUQUE MAYRA JULIETA</t>
+  </si>
+  <si>
+    <t>VALENZUELA HERRERO MARIANA ELENA</t>
+  </si>
+  <si>
+    <t>BALLESTER LEANDRA EMILCE</t>
+  </si>
+  <si>
+    <t>AGÜERO MELISA VICTORIA</t>
+  </si>
+  <si>
+    <t>GARAY MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>MUNOZ GABRIELA ELISA</t>
+  </si>
+  <si>
+    <t>CARRIZO CARLA VIVIANA</t>
+  </si>
+  <si>
+    <t>BARRIONUEVO TAPIA BRISA JAZMIN</t>
+  </si>
+  <si>
+    <t>CASTRO MARIA CAROLINA</t>
+  </si>
+  <si>
+    <t>PUIGGRAS ANDREA VANESA</t>
+  </si>
+  <si>
+    <t>TIZERA MARIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>VELASCO MALBERTI MARIA EMILIA</t>
+  </si>
+  <si>
+    <t>MARTIN RUEDA ROLANDO MIGUEL</t>
+  </si>
+  <si>
+    <t>ADORNO CARRIZO AGUSTINA GUADALUPE</t>
+  </si>
+  <si>
+    <t>GUEVARA GAITAN KARINA MICAELA</t>
+  </si>
+  <si>
+    <t>TORRES VALERIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>QUIROGA DIAZ NATALI SOLEDAD</t>
+  </si>
+  <si>
+    <t>RAMIREZ FREDES ANA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>PUEBLA MACIAS JESICA ELVIRA</t>
+  </si>
+  <si>
+    <t>PENA CECILIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>GOMEZ VERONICA VIVIANA</t>
+  </si>
+  <si>
+    <t>GOMEZ BATTEZZATI AGOSTINA DEL PILAR</t>
+  </si>
+  <si>
+    <t>ROMERO NOELIA MARIBEL</t>
+  </si>
+  <si>
+    <t>INGLESES VERGARA EMILIO ARIEL</t>
+  </si>
+  <si>
+    <t>BONTEMPO GABRIEL AUGUSTO</t>
+  </si>
+  <si>
+    <t>NAVARRO MONTIVERO SOFIA MACARENA</t>
+  </si>
+  <si>
+    <t>BONTEMPO NAZARENA FATIMA</t>
+  </si>
+  <si>
+    <t>GODOY ROXANA ANALIA</t>
+  </si>
+  <si>
+    <t>PRADO VALVERDE KARINA NATALIA</t>
+  </si>
+  <si>
+    <t>HOMES ANALIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>ALMEIDA RADICETTI AYELEN NOEMI</t>
+  </si>
+  <si>
+    <t>ILLANES GEMA ELENA</t>
+  </si>
+  <si>
+    <t>MARCHESE CELIA LUCIA</t>
+  </si>
+  <si>
+    <t>BAZAN MARGARITA ROSANA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ MARINA BEATRIZ</t>
+  </si>
+  <si>
+    <t>DURAN CLAUDIA VERANICA</t>
+  </si>
+  <si>
+    <t>PEREIRA ARCE LAURA YESICA</t>
+  </si>
+  <si>
+    <t>NUÑEZ CARINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>DIAZ CASTILLO CECILIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>QUIROGA ALVAREZ MARILIN ELIZABET</t>
+  </si>
+  <si>
+    <t>HASCHER VALERIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>RAMIREZ MARIA SUSANA</t>
+  </si>
+  <si>
+    <t>HERRERA CRISTIAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>MARTI GAMEZ SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>FLORES ESTELA EUNICE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ TAPIA KATHERINA AYELEN</t>
+  </si>
+  <si>
+    <t>GOMEZ MASTROTTA EVELIN GRISEL</t>
+  </si>
+  <si>
+    <t>ABILA PATRICIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>BUSTOS CAROLINA DEL VALLE</t>
+  </si>
+  <si>
+    <t>GARRO MIRIAM RENEE</t>
+  </si>
+  <si>
+    <t>RUARTE LEIVA MARINA SOLEDAD</t>
+  </si>
+  <si>
+    <t>ALVAREZ ANA MARIA</t>
+  </si>
+  <si>
+    <t>PEREZ HECTOR JESUS</t>
+  </si>
+  <si>
+    <t>GONZALEZ MORA ROCIO BELEN</t>
+  </si>
+  <si>
+    <t>ORTEGA YACANTO JOHANA BELEN</t>
+  </si>
+  <si>
+    <t>PUTELLI MIRTA EUGENIA</t>
+  </si>
+  <si>
+    <t>NAVEDA MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ GUTIERREZ KATIA AIDA</t>
+  </si>
+  <si>
+    <t>GALLARDO MERINO JOHANA MARIANELA</t>
+  </si>
+  <si>
+    <t>DELGADO SALAZAR MARTIN NICOLAS</t>
+  </si>
+  <si>
+    <t>OYOLA MORALES MAYRA VERONICA</t>
+  </si>
+  <si>
+    <t>PONCE SELVA LORENA</t>
+  </si>
+  <si>
+    <t>PINTO GARCIA MARCELA INES</t>
+  </si>
+  <si>
+    <t>CAMPILLAY NOELIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>BAZAN MORLAS JIMENA ANABEL</t>
+  </si>
+  <si>
+    <t>PEDROL CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>VALENZUELA ORO MARIA FLORENCIA</t>
+  </si>
+  <si>
+    <t>AVILA ENRIQUE GASTON</t>
+  </si>
+  <si>
+    <t>BLANC RODRIGUEZ CARLA YANINA</t>
+  </si>
+  <si>
+    <t>DURAN SINGLA MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>ESPEJO CRISTIAN MAURICIO</t>
+  </si>
+  <si>
+    <t>ASENCIO MICAELA KAREN RITA</t>
+  </si>
+  <si>
+    <t>OTINANO OZAN SILVINA DEL VALLE</t>
+  </si>
+  <si>
+    <t>ANDAN SILVINA VANESA</t>
+  </si>
+  <si>
+    <t>TORRES VALERIA VIRGINIA</t>
+  </si>
+  <si>
+    <t>ESCOBAR CARINA ISABEL</t>
+  </si>
+  <si>
+    <t>LORENTE NATALIA SILVANA</t>
+  </si>
+  <si>
+    <t>TORRES LORENA EVANGELINA</t>
+  </si>
+  <si>
+    <t>ALONSO MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>NAVAS ECHENIQUE ELIO IVN</t>
+  </si>
+  <si>
+    <t>GAMERO VILANIS MARIA NOELIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ BELLI JULIETA</t>
+  </si>
+  <si>
+    <t>BUSTOS SALINAS FLAVIA ROMINA</t>
+  </si>
+  <si>
+    <t>RUARTE MARIA JOSE</t>
+  </si>
+  <si>
+    <t>LOPEZ VERONICA PAOLA</t>
+  </si>
+  <si>
+    <t>ESPEJO PATRICIA MABEL</t>
+  </si>
+  <si>
+    <t>VERA KARINA BEATRIZ</t>
+  </si>
+  <si>
+    <t>CASTRO ERICA VANESA</t>
+  </si>
+  <si>
+    <t>SOLIS CAROLINA ROSANA</t>
+  </si>
+  <si>
+    <t>HUERTA GISELE DORA</t>
+  </si>
+  <si>
+    <t>GONZALEZ GILYAN MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>ZAPPALA YANINA IVANA</t>
+  </si>
+  <si>
+    <t>SOLIS ROSA BEATRIZ</t>
+  </si>
+  <si>
+    <t>QUIROGA MARISA FABIANA</t>
+  </si>
+  <si>
+    <t>ESPINOSA GARBO CECILIA CELINA</t>
+  </si>
+  <si>
+    <t>LUNA DAHIANA VERNICA</t>
+  </si>
+  <si>
+    <t>MAGGIO ROSTOLL MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ CLAUDIA ANDREA</t>
+  </si>
+  <si>
+    <t>CARROZZO FLORES MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>LLOPIS PENNATE LAURA BEATRIZ</t>
+  </si>
+  <si>
+    <t>TALQUENCA VEGA ANDREA PAULA</t>
+  </si>
+  <si>
+    <t>SAMPER MARIA CRISTINA</t>
+  </si>
+  <si>
+    <t>ESPEJO ANA MARIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ CECILIA BELEN</t>
+  </si>
+  <si>
+    <t>SALAS CASTRO ANA CARINA</t>
+  </si>
+  <si>
+    <t>CARRION QUIROGA GERMAN GABRIEL</t>
+  </si>
+  <si>
+    <t>COLOMBO MARTIN EXEQUIEL</t>
+  </si>
+  <si>
+    <t>GODOY DENISE CLORINDA</t>
+  </si>
+  <si>
+    <t>SANCHEZ MARIA PAULA</t>
+  </si>
+  <si>
+    <t>FIGUEROA JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ROMERO DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ROSALES LORENA ELIZABETH</t>
+  </si>
+  <si>
+    <t>MERCADO HEBER EDGAR</t>
+  </si>
+  <si>
+    <t>MALDONADO MARCELA LORENA</t>
+  </si>
+  <si>
+    <t>CAROSELLI ALEJANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>MERCADO PATRICIA VERÔNICA</t>
+  </si>
+  <si>
+    <t>VALDEZ VANESA MARIA</t>
+  </si>
+  <si>
+    <t>HOGALDE ZUBIETE MARIANA BELEN</t>
+  </si>
+  <si>
+    <t>ONTIVEROS NATALIA LORENA</t>
+  </si>
+  <si>
+    <t>HEREDIA CECILIA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>FLORES PATRICIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>TEJADA PATRICIA ROSANA</t>
+  </si>
+  <si>
+    <t>CALLEJA LAURA SILVANA</t>
+  </si>
+  <si>
+    <t>CABRERA LANGHI ANA CELESTE</t>
+  </si>
+  <si>
+    <t>BORDON GABRIELA YANINA</t>
+  </si>
+  <si>
+    <t>QUINTEROS MARIA CELINA</t>
+  </si>
+  <si>
+    <t>CASTRO CARINA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>PESSINA MARIANO ARTURO</t>
+  </si>
+  <si>
+    <t>GARCIA TORRES MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ROSALES SAAVEDRA KARINA BELEN</t>
+  </si>
+  <si>
+    <t>MARTINEZ LUCIA GABRIELA</t>
+  </si>
+  <si>
+    <t>CORTEZ MERCADO JULIA ELENA</t>
+  </si>
+  <si>
+    <t>VIDABLE PAEZ MARIA AGUSTINA</t>
+  </si>
+  <si>
+    <t>CASIVAR CARLA MARIANA</t>
+  </si>
+  <si>
+    <t>PAEZ CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>RECABARREN MARIA AGOSTINA</t>
+  </si>
+  <si>
+    <t>BERNAL BLANCO ROCIO CRISTINA</t>
+  </si>
+  <si>
+    <t>LIMA ANALIA CARLOTA JUANA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ ROLDAN WALTER ESEQUIEL</t>
+  </si>
+  <si>
+    <t>GONZALEZ SILVANA ELENA</t>
+  </si>
+  <si>
+    <t>RIMOLO SANDRA JUANA</t>
+  </si>
+  <si>
+    <t>PORTUGAL FERNANDEZ OLGA YOLANDA</t>
+  </si>
+  <si>
+    <t>ROMERO ALVARADO MARIANO ABEL</t>
+  </si>
+  <si>
+    <t>GUTIERREZ CECILIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>D'ANGELO VANESSA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>BUSTOS ANA MARIA</t>
+  </si>
+  <si>
+    <t>OSSA FEDERICO ANA VICTORIA</t>
+  </si>
+  <si>
+    <t>ARG£ELLO MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARTI GAMEZ RUBEN GABRIEL</t>
+  </si>
+  <si>
+    <t>CASTRO FLORES EMILCE NOELIA</t>
+  </si>
+  <si>
+    <t>MIRANDA ANA ROSANA</t>
+  </si>
+  <si>
+    <t>LEON ANALIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MUÑOZ JOFRE ERICA PATRICIA</t>
+  </si>
+  <si>
+    <t>ARIAS VEGA LAURA HAIDEE</t>
+  </si>
+  <si>
+    <t>TULA ELSA LIDIA</t>
+  </si>
+  <si>
+    <t>ROJAS YOLANDA ANDREA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>GONZALEZ GRACIELA DECIDERIA</t>
+  </si>
+  <si>
+    <t>NAVARRETE JUANA ANA NOEMI</t>
+  </si>
+  <si>
+    <t>SANCHEZ MONICA VIVIANA</t>
+  </si>
+  <si>
+    <t>MEDRANO JOFRE EMILIANA MACARENA</t>
+  </si>
+  <si>
+    <t>GAMBA SEGOVIA OSCAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>GONZALEZ SALINAS ANTONIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>RIVADAY ENRIQUE ANTONIO</t>
+  </si>
+  <si>
+    <t>CASTRACANI CAROLA ANDREA</t>
+  </si>
+  <si>
+    <t>GUARDIA FLAVIA LETICIA</t>
+  </si>
+  <si>
+    <t>FIGUEROA NATALIA MARCELA</t>
+  </si>
+  <si>
+    <t>ALAMINO ANALI CELESTE SOLEDAD</t>
+  </si>
+  <si>
+    <t>PAEZ PAOLA MABEL</t>
+  </si>
+  <si>
+    <t>MORETTI ANALIA CECILIA</t>
+  </si>
+  <si>
+    <t>AGUERO CLAUDIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>VIDELA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>ACIAR FERNANDA NOELIA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ PEREZ FABIANA GRISELDA</t>
+  </si>
+  <si>
+    <t>ESPIN ELIZABETH CLARA</t>
+  </si>
+  <si>
+    <t>GALIÑANES NATALIA PAOLA</t>
+  </si>
+  <si>
+    <t>RIZZO GIL MARIANELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>BERTOL MANRIQUE CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>CABALLERO GONZALEZ JOSE EMILIO</t>
+  </si>
+  <si>
+    <t>PASTOR VIDABLE VANESA NOEM</t>
+  </si>
+  <si>
+    <t>LOPEZ OSCAR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>FLORES LUCILA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GAMES GONZALEZ MARA BELN</t>
+  </si>
+  <si>
+    <t>DONOSO MYRIAM BEATRIZ</t>
+  </si>
+  <si>
+    <t>PAROLDI DEBORA</t>
+  </si>
+  <si>
+    <t>PONCE FELIPUCHE MARCELA ANALIA</t>
+  </si>
+  <si>
+    <t>YACANTE TAMARA ERICA</t>
+  </si>
+  <si>
+    <t>ALVAREZ FARIAS GISELA JESUS</t>
+  </si>
+  <si>
+    <t>MUÆOZ IVANA PATRICIA</t>
+  </si>
+  <si>
+    <t>CORIA AUGUSTO ANDREA LILIANA</t>
+  </si>
+  <si>
+    <t>QUIROGA VERON LEONARDO MARTIN</t>
+  </si>
+  <si>
+    <t>GARCIA YESICA EDITH</t>
+  </si>
+  <si>
+    <t>ALGAÑARAS CASIVAR CINTIA BELÉN</t>
+  </si>
+  <si>
+    <t>LOPEZ PAULINA ISABEL</t>
+  </si>
+  <si>
+    <t>YAÑEZ VALERIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>CORDOBA CLAUDIA CARINA</t>
+  </si>
+  <si>
+    <t>AG£ERO MARIELA INËS</t>
+  </si>
+  <si>
+    <t>CRAVERO GIMENEZ SOFIA DANIELA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA ALEJANDRA FABIANA</t>
+  </si>
+  <si>
+    <t>BLANCO VANESA BEATRIZ</t>
+  </si>
+  <si>
+    <t>ROMERO FLAVIO RUBEN</t>
+  </si>
+  <si>
+    <t>CARABAJAL MARIA ADELINA</t>
+  </si>
+  <si>
+    <t>ALCANTARO ROSA PAOLA</t>
+  </si>
+  <si>
+    <t>AMARFIL YAÆEZ MARIA JOSE</t>
+  </si>
+  <si>
+    <t>VILDOZO CARINA JOHANA</t>
+  </si>
+  <si>
+    <t>VERA MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>ESCUDERO NATALIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>YANZN ELIZABETH LEONOR</t>
+  </si>
+  <si>
+    <t>FLORES LINARES JOSE LUIS EMILIANO</t>
+  </si>
+  <si>
+    <t>SAMBRIZZI FEDERICO SALVADOR</t>
+  </si>
+  <si>
+    <t>BECERRA CORREA MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ ADRIANA ANGELA GABRIELA</t>
+  </si>
+  <si>
+    <t>GODOY CASTRO LINA FABIANA</t>
+  </si>
+  <si>
+    <t>RIVEROS ADRIANA ANTONIA</t>
+  </si>
+  <si>
+    <t>ECHEVARRIA MERCEDES BEATRIZ</t>
+  </si>
+  <si>
+    <t>GUERRA ROMINA VALERIA</t>
+  </si>
+  <si>
+    <t>LISI MELISA SORAYA</t>
+  </si>
+  <si>
+    <t>CANADAS CALIVAR MARCIA ROMINA</t>
+  </si>
+  <si>
+    <t>FERRER MACIAS MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>LOPEZ FERNANDEZ ANDREA VIVIANA</t>
+  </si>
+  <si>
+    <t>VALENZUELA ORO LISANDRO ALFREDO</t>
+  </si>
+  <si>
+    <t>OVIEDO MARÌA GEMA</t>
+  </si>
+  <si>
+    <t>MARADONA DAYANA SELVA</t>
+  </si>
+  <si>
+    <t>PONCE MOLINERO LAURA VALERIA</t>
+  </si>
+  <si>
+    <t>VELASQUE CABALLERO VALERIA YANINA</t>
+  </si>
+  <si>
+    <t>VILANOVA LOPEZ SANDRA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SAEZ MALLAMACI BRUNO</t>
+  </si>
+  <si>
+    <t>ROBLEDO ANA PATRICIA</t>
+  </si>
+  <si>
+    <t>MUOZ VELAZQUEZ MARISOL ALEJANDRA</t>
+  </si>
+  <si>
+    <t>BRAGAGNOLO STELLA MARYS</t>
+  </si>
+  <si>
+    <t>PASTORIZA CRISTINA VERONICA</t>
+  </si>
+  <si>
+    <t>VEGA FACUNDO MARTIN</t>
+  </si>
+  <si>
+    <t>ZABALETA LILIANA ELIZABETH</t>
+  </si>
+  <si>
+    <t>MORALES VANESA ESTELA</t>
+  </si>
+  <si>
+    <t>GUILLEN BETINA LUCIA</t>
+  </si>
+  <si>
+    <t>CABALLERO JESICA ROSMARI</t>
+  </si>
+  <si>
+    <t>DELGADO IVAN MARCELO</t>
+  </si>
+  <si>
+    <t>COLOMBO RODRIGUEZ ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ACIAR ONTIVEROS GEMMA ENCARNACION</t>
+  </si>
+  <si>
+    <t>AHUMADA ORTIZ JAQUELINE ANDREA</t>
+  </si>
+  <si>
+    <t>CANTONI LIHUE</t>
+  </si>
+  <si>
+    <t>GOMEZ MARCELA MONICA</t>
+  </si>
+  <si>
+    <t>CAMACHO ADRIANA MONICA</t>
+  </si>
+  <si>
+    <t>TEJADA SARA BEATRIZ</t>
+  </si>
+  <si>
+    <t>MARATTA AMARFIL LUCIANA BELEN</t>
+  </si>
+  <si>
+    <t>CORREA CORTS ELSA GABRIELA</t>
+  </si>
+  <si>
+    <t>IBAÆEZ GABRIELA JESSICA</t>
+  </si>
+  <si>
+    <t>SIMON DESIREE DEL VALLE</t>
+  </si>
+  <si>
+    <t>LUCERO HILDA CLARISA BETTINA</t>
+  </si>
+  <si>
+    <t>TOBAR LOURDES NORMA</t>
+  </si>
+  <si>
+    <t>LACIAR JAVIER ALBERTO</t>
+  </si>
+  <si>
+    <t>ZARATE ANDREA MARCELA</t>
+  </si>
+  <si>
+    <t>CHIRINO NAVAS ANA MARIA</t>
+  </si>
+  <si>
+    <t>FLORES ESCUDERO DAYANA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YAVANTE BAZAN ANDREA MARISEL</t>
+  </si>
+  <si>
+    <t>DE NARDO GINA ORNELLA</t>
+  </si>
+  <si>
+    <t>ORTIZ VERONICA SILVINA</t>
+  </si>
+  <si>
+    <t>MARIN VERONICA CECILIA</t>
+  </si>
+  <si>
+    <t>RIVAS BERNARDO OSCAR</t>
+  </si>
+  <si>
+    <t>GAY MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>OVIEDO SILVIA ADRIANA</t>
+  </si>
+  <si>
+    <t>ESPEJO PAEZ FANY EUGENIA</t>
+  </si>
+  <si>
+    <t>BLANCO MAIRA AYELEN</t>
+  </si>
+  <si>
+    <t>CASTRO ANALIA GRACIELA</t>
+  </si>
+  <si>
+    <t>AGÜERO FABRICIO GABRIEL</t>
+  </si>
+  <si>
+    <t>TEJADA FALCON MIRTHA JOHANA</t>
+  </si>
+  <si>
+    <t>CORZO GRACIELA EDIT</t>
+  </si>
+  <si>
+    <t>ILLANES GUEVARA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>RIVERO SOFIA DANIELA</t>
+  </si>
+  <si>
+    <t>LARA GABRIELA NATALIA</t>
+  </si>
+  <si>
+    <t>CIANI CLAUDIA GRACIELA</t>
+  </si>
+  <si>
+    <t>CASTILLO ROSANA FORTUNATA</t>
+  </si>
+  <si>
+    <t>LESCURA GABRIELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ALMARCHA GONZALEZ YANELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>BARBOZA MENENDEZ CINTIA YANINA</t>
+  </si>
+  <si>
+    <t>BALMACEDA VIVIANA MARIA</t>
+  </si>
+  <si>
+    <t>JOFRE OTAROLA NAZARENO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>OLAECHEA MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>SOSA NATALIA VANESA</t>
+  </si>
+  <si>
+    <t>MONTERO ZAPATA ROSANA MARCELA</t>
+  </si>
+  <si>
+    <t>CORDOBA GARAY MARIA INES</t>
+  </si>
+  <si>
+    <t>HUERTA FERNANDEZ MARIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>LUNA ANIBAL JULIO</t>
+  </si>
+  <si>
+    <t>BUSTOS CELINA PAOLA</t>
+  </si>
+  <si>
+    <t>GONZALEZ PONTORIERO CECILIA BETIANA</t>
+  </si>
+  <si>
+    <t>ASTUDILLO TAMARA PAMELA</t>
+  </si>
+  <si>
+    <t>PALACIO ANALIA VERONICA</t>
+  </si>
+  <si>
+    <t>PERRONE PAEZ CLAUDIA BERENICE</t>
+  </si>
+  <si>
+    <t>PAROLDI TATIANA YAEL</t>
+  </si>
+  <si>
+    <t>ROCHA NORMA VIVIANA</t>
+  </si>
+  <si>
+    <t>LUNA VANINA GISELLE</t>
+  </si>
+  <si>
+    <t>VIDAL MAYRA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>CASTRACANI SIREROL CLAUDIA MARIELA</t>
+  </si>
+  <si>
+    <t>MARANO ROSA VERONICA</t>
+  </si>
+  <si>
+    <t>VARAS GOMEZ MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t>MORETA NAIR MARIANELA</t>
+  </si>
+  <si>
+    <t>ANDAN VIVIANA PAOLA</t>
+  </si>
+  <si>
+    <t>GUAJARDO BALMACEDA VANESA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJOS ZAPATA CELESTE NOELIA</t>
+  </si>
+  <si>
+    <t>CAMPOS MARIÑO JESICA NATALIA</t>
+  </si>
+  <si>
+    <t>ROSAS LAURA ANDREA</t>
+  </si>
+  <si>
+    <t>SAAVEDRA LOPEZ LUCIANA</t>
+  </si>
+  <si>
+    <t>DE LA TORRE MARTIN MARIA</t>
+  </si>
+  <si>
+    <t>MERINO MAYRA AYELEN</t>
+  </si>
+  <si>
+    <t>PEREZ RODRIGO CELINA</t>
+  </si>
+  <si>
+    <t>ACCORONI LUBER ANDREA GABRIELA</t>
+  </si>
+  <si>
+    <t>NORIEGA CAROLINA LAURA</t>
+  </si>
+  <si>
+    <t>PONCE ZAIDA JOHANA</t>
+  </si>
+  <si>
+    <t>PEREZ BEDINI MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>GUERRERO SILVANA MONICA</t>
+  </si>
+  <si>
+    <t>PELLEGRINI VERONICA ELISA</t>
+  </si>
+  <si>
+    <t>MORALES RICARDO MARCELO</t>
+  </si>
+  <si>
+    <t>ORTIZ ALICIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ NORMA BEATRIZ</t>
+  </si>
+  <si>
+    <t>MOLINA MARISA ISABEL</t>
+  </si>
+  <si>
+    <t>POBLETE NIEVES MABEL</t>
+  </si>
+  <si>
+    <t>MORALES ROCIO MABEL</t>
+  </si>
+  <si>
+    <t>SILVA TEJADA ANGELINA SILVANA</t>
+  </si>
+  <si>
+    <t>CALIVA BRISA ARIADNA</t>
+  </si>
+  <si>
+    <t>TEJADA FONZALIDA MICAELA ANAHI</t>
+  </si>
+  <si>
+    <t>ESPINOZA CASTRO LILIANA ELENA</t>
+  </si>
+  <si>
+    <t>MURCIANO GRACIELA ANDREA</t>
+  </si>
+  <si>
+    <t>RANEA PAZ MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ABREGO MARIA GABRIELA</t>
+  </si>
+  <si>
+    <t>SAAVEDRA MARTINEZ MARIANA NOELIA</t>
+  </si>
+  <si>
+    <t>ACOSTA HEREDIA YANINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SANCHEZ ERIKA</t>
+  </si>
+  <si>
+    <t>ESPEJO MARIA AYELEN</t>
+  </si>
+  <si>
+    <t>ZAVALETA CLARISA SILVINA</t>
+  </si>
+  <si>
+    <t>CABRERA LANGHI NATALIA ROMINA</t>
+  </si>
+  <si>
+    <t>SALAS GOMEZ SANDRA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ROSSELOT SANDRA MABEL</t>
+  </si>
+  <si>
+    <t>VERA MARIA JOS</t>
+  </si>
+  <si>
+    <t>LEZCANO FONSALIDA VALERIA INES</t>
+  </si>
+  <si>
+    <t>YACANTE MERCADO FABIANA EDITH</t>
+  </si>
+  <si>
+    <t>RIOS CORVALAN AYELÉN MICAELA</t>
+  </si>
+  <si>
+    <t>QUIROGA MARIA IRENE</t>
+  </si>
+  <si>
+    <t>MONTENEGRO MARIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ECHENIQUE GUIDA LUCRECIA LETICIA</t>
+  </si>
+  <si>
+    <t>SILVA MALLEA MARIA BELEN</t>
+  </si>
+  <si>
+    <t>DONOSO AGUILERA GIMENA TATIANA</t>
+  </si>
+  <si>
+    <t>GOMEZ NIGRES PAMELA BEATRIZ</t>
+  </si>
+  <si>
+    <t>CLEVERS MARTINA SOFIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ CERDERA ROCIO GUADALUPE</t>
+  </si>
+  <si>
+    <t>AVILA VERONICA EDITH</t>
+  </si>
+  <si>
+    <t>TORRES CARDOZO BRISA AILEN</t>
+  </si>
+  <si>
+    <t>ZAPATA PAULA CECILIA</t>
+  </si>
+  <si>
+    <t>BUSTOS ADRIAN ALBERTO</t>
+  </si>
+  <si>
+    <t>MORRA PRESNO ROBERTO JAVIER</t>
+  </si>
+  <si>
+    <t>ILLANEZ EDUARDO IGNACIO</t>
+  </si>
+  <si>
+    <t>VAN DER HORST SILVINA NOEMI</t>
+  </si>
+  <si>
+    <t>ORTIZ PATRICIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>ROJAS GISELLA ELIZABETH</t>
+  </si>
+  <si>
+    <t>LUCERO BRIZUELA ALEJANDRA LIDIA</t>
+  </si>
+  <si>
+    <t>CANO FERNANDA GABRIELA</t>
+  </si>
+  <si>
+    <t>TEJADA SILVINA NOELIA</t>
+  </si>
+  <si>
+    <t>VILLAFAÑE YOHANA SOLEDAD</t>
+  </si>
+  <si>
+    <t>GOMEZ VANESA GISEL</t>
+  </si>
+  <si>
+    <t>CASTRO BALMACEDA CELIA CAROLINA</t>
+  </si>
+  <si>
+    <t>RETA TORRES DANIELA SOLEDAD</t>
+  </si>
+  <si>
+    <t>QUILPATAY ROSAURA DESIDERIA</t>
+  </si>
+  <si>
+    <t>VEDIA MARIANELA JOHANA</t>
+  </si>
+  <si>
+    <t>DAVILA NANCY NATALIA</t>
+  </si>
+  <si>
+    <t>MELIAN MARIANA</t>
+  </si>
+  <si>
+    <t>BRIZUELA MARIANELA MARTA</t>
+  </si>
+  <si>
+    <t>GUEVARA AXEL LEONEL</t>
+  </si>
+  <si>
+    <t>FLORES FLORES PRISCILA TAMARA</t>
+  </si>
+  <si>
+    <t>DIAZ CAÑADA CECILIA VANESA</t>
+  </si>
+  <si>
+    <t>MERITELLO MONICA DANIELA</t>
+  </si>
+  <si>
+    <t>GOMEZ SONIA FABIANA</t>
+  </si>
+  <si>
+    <t>MOREIRA OLGA ELIZABET</t>
+  </si>
+  <si>
+    <t>ZALAZAR CINTIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ARGANARAZ MARTI CINTHIA ANAHI</t>
+  </si>
+  <si>
+    <t>ORIHUELA MARIELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>TIZERA MARIA VANESA</t>
+  </si>
+  <si>
+    <t>PAEZ ELIANA GISELA</t>
+  </si>
+  <si>
+    <t>ALVAREZ GABRIELA DEL MILAGRO</t>
+  </si>
+  <si>
+    <t>GONZALEZ ALANIZ GRACIELA SOLEDAD</t>
+  </si>
+  <si>
+    <t>QUINTERO MILAGROS TAMARA</t>
+  </si>
+  <si>
+    <t>RUL EVELIN DAYANA</t>
+  </si>
+  <si>
+    <t>PEREZ TELLO IVANA DEL VALLE</t>
+  </si>
+  <si>
+    <t>GONZALEZ EMILI TAMARA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ MARIO LUIS</t>
+  </si>
+  <si>
+    <t>OLMEDO GOYOCHEA JOHANA DANIELA</t>
+  </si>
+  <si>
+    <t>RIOS ERICA NATALIA</t>
+  </si>
+  <si>
+    <t>CARRASCO RIVERO GABRIELA SOLEDAD</t>
+  </si>
+  <si>
+    <t>RUSSO MUÆOZ MARIA JIMENA</t>
+  </si>
+  <si>
+    <t>PUERTAS LOPEZ MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>ARROYO ELBA MABEL</t>
+  </si>
+  <si>
+    <t>GATICA MARIA JOSE</t>
+  </si>
+  <si>
+    <t>FACHINETTI PAOLA MABEL BENITA</t>
+  </si>
+  <si>
+    <t>TEJADA DEBORA VALERIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ VERONICA GEMA</t>
+  </si>
+  <si>
+    <t>RUIZ RIVEROS ANA MARIA</t>
+  </si>
+  <si>
+    <t>GODOY CLAUDIA LUCRECIA DEL VALLE</t>
+  </si>
+  <si>
+    <t>QUILPATAY ANTONIA ANDREA</t>
+  </si>
+  <si>
+    <t>CABRERA CARINA ANDREA</t>
+  </si>
+  <si>
+    <t>CORRIENTE ROMINA BELEN</t>
+  </si>
+  <si>
+    <t>FLORES MOYANO GABRIELA YESICA</t>
+  </si>
+  <si>
+    <t>CORZO NOELIA NOEMI</t>
+  </si>
+  <si>
+    <t>LOPEZ EVELYN</t>
+  </si>
+  <si>
+    <t>BERNAL BLANCO PAULA ALEJANDRA</t>
   </si>
 </sst>
 </file>
@@ -345,14 +3054,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B456"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="2" width="52.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -360,12 +3069,3644 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>23977476</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+      <c r="B234" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+      <c r="B235" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+      <c r="B237" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+      <c r="B240" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>241</v>
+      </c>
+      <c r="B241" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>242</v>
+      </c>
+      <c r="B242" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>243</v>
+      </c>
+      <c r="B243" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>244</v>
+      </c>
+      <c r="B244" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>245</v>
+      </c>
+      <c r="B245" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+      <c r="B246" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+      <c r="B247" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+      <c r="B248" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+      <c r="B249" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+      <c r="B250" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+      <c r="B251" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+      <c r="B252" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>253</v>
+      </c>
+      <c r="B253" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>254</v>
+      </c>
+      <c r="B254" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+      <c r="B255" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>256</v>
+      </c>
+      <c r="B256" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>257</v>
+      </c>
+      <c r="B257" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>258</v>
+      </c>
+      <c r="B258" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>259</v>
+      </c>
+      <c r="B259" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+      <c r="B260" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+      <c r="B261" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+      <c r="B262" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>263</v>
+      </c>
+      <c r="B263" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>264</v>
+      </c>
+      <c r="B264" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>265</v>
+      </c>
+      <c r="B265" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>266</v>
+      </c>
+      <c r="B266" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>267</v>
+      </c>
+      <c r="B267" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>268</v>
+      </c>
+      <c r="B268" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>269</v>
+      </c>
+      <c r="B269" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>270</v>
+      </c>
+      <c r="B270" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>271</v>
+      </c>
+      <c r="B271" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>272</v>
+      </c>
+      <c r="B272" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>273</v>
+      </c>
+      <c r="B273" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>274</v>
+      </c>
+      <c r="B274" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>275</v>
+      </c>
+      <c r="B275" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>276</v>
+      </c>
+      <c r="B276" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>277</v>
+      </c>
+      <c r="B277" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>278</v>
+      </c>
+      <c r="B278" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>279</v>
+      </c>
+      <c r="B279" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>280</v>
+      </c>
+      <c r="B280" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>281</v>
+      </c>
+      <c r="B281" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>282</v>
+      </c>
+      <c r="B282" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>283</v>
+      </c>
+      <c r="B283" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>284</v>
+      </c>
+      <c r="B284" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>285</v>
+      </c>
+      <c r="B285" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>286</v>
+      </c>
+      <c r="B286" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>287</v>
+      </c>
+      <c r="B287" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>288</v>
+      </c>
+      <c r="B288" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>289</v>
+      </c>
+      <c r="B289" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>290</v>
+      </c>
+      <c r="B290" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>291</v>
+      </c>
+      <c r="B291" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>292</v>
+      </c>
+      <c r="B292" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>293</v>
+      </c>
+      <c r="B293" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>294</v>
+      </c>
+      <c r="B294" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>295</v>
+      </c>
+      <c r="B295" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>296</v>
+      </c>
+      <c r="B296" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>297</v>
+      </c>
+      <c r="B297" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>298</v>
+      </c>
+      <c r="B298" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>299</v>
+      </c>
+      <c r="B299" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>300</v>
+      </c>
+      <c r="B300" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>301</v>
+      </c>
+      <c r="B301" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>302</v>
+      </c>
+      <c r="B302" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>303</v>
+      </c>
+      <c r="B303" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>304</v>
+      </c>
+      <c r="B304" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>305</v>
+      </c>
+      <c r="B305" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>306</v>
+      </c>
+      <c r="B306" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>307</v>
+      </c>
+      <c r="B307" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>308</v>
+      </c>
+      <c r="B308" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>309</v>
+      </c>
+      <c r="B309" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>310</v>
+      </c>
+      <c r="B310" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>98</v>
+      </c>
+      <c r="B311" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>316</v>
+      </c>
+      <c r="B317" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>317</v>
+      </c>
+      <c r="B318" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>318</v>
+      </c>
+      <c r="B319" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>319</v>
+      </c>
+      <c r="B320" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>320</v>
+      </c>
+      <c r="B321" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>321</v>
+      </c>
+      <c r="B322" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>322</v>
+      </c>
+      <c r="B323" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>335</v>
+      </c>
+      <c r="B336" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>336</v>
+      </c>
+      <c r="B337" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>337</v>
+      </c>
+      <c r="B338" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>338</v>
+      </c>
+      <c r="B339" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>341</v>
+      </c>
+      <c r="B342" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>342</v>
+      </c>
+      <c r="B343" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>343</v>
+      </c>
+      <c r="B344" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>345</v>
+      </c>
+      <c r="B346" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>346</v>
+      </c>
+      <c r="B347" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>347</v>
+      </c>
+      <c r="B348" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>348</v>
+      </c>
+      <c r="B349" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>349</v>
+      </c>
+      <c r="B350" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>350</v>
+      </c>
+      <c r="B351" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>351</v>
+      </c>
+      <c r="B352" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>352</v>
+      </c>
+      <c r="B353" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>353</v>
+      </c>
+      <c r="B354" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>354</v>
+      </c>
+      <c r="B355" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>355</v>
+      </c>
+      <c r="B356" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>356</v>
+      </c>
+      <c r="B357" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>357</v>
+      </c>
+      <c r="B358" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>358</v>
+      </c>
+      <c r="B359" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>372</v>
+      </c>
+      <c r="B373" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>373</v>
+      </c>
+      <c r="B374" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>374</v>
+      </c>
+      <c r="B375" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>375</v>
+      </c>
+      <c r="B376" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>376</v>
+      </c>
+      <c r="B377" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>377</v>
+      </c>
+      <c r="B378" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>378</v>
+      </c>
+      <c r="B379" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>379</v>
+      </c>
+      <c r="B380" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>380</v>
+      </c>
+      <c r="B381" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>381</v>
+      </c>
+      <c r="B382" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>382</v>
+      </c>
+      <c r="B383" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>383</v>
+      </c>
+      <c r="B384" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>384</v>
+      </c>
+      <c r="B385" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>385</v>
+      </c>
+      <c r="B386" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>386</v>
+      </c>
+      <c r="B387" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>387</v>
+      </c>
+      <c r="B388" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>388</v>
+      </c>
+      <c r="B389" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>389</v>
+      </c>
+      <c r="B390" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>390</v>
+      </c>
+      <c r="B391" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>391</v>
+      </c>
+      <c r="B392" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>392</v>
+      </c>
+      <c r="B393" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>393</v>
+      </c>
+      <c r="B394" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>394</v>
+      </c>
+      <c r="B395" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>395</v>
+      </c>
+      <c r="B396" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>396</v>
+      </c>
+      <c r="B397" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>397</v>
+      </c>
+      <c r="B398" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>398</v>
+      </c>
+      <c r="B399" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>399</v>
+      </c>
+      <c r="B400" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>400</v>
+      </c>
+      <c r="B401" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>401</v>
+      </c>
+      <c r="B402" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>402</v>
+      </c>
+      <c r="B403" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>403</v>
+      </c>
+      <c r="B404" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>404</v>
+      </c>
+      <c r="B405" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>405</v>
+      </c>
+      <c r="B406" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>406</v>
+      </c>
+      <c r="B407" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>407</v>
+      </c>
+      <c r="B408" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>408</v>
+      </c>
+      <c r="B409" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>409</v>
+      </c>
+      <c r="B410" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>410</v>
+      </c>
+      <c r="B411" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>411</v>
+      </c>
+      <c r="B412" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>412</v>
+      </c>
+      <c r="B413" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>413</v>
+      </c>
+      <c r="B414" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>414</v>
+      </c>
+      <c r="B415" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>415</v>
+      </c>
+      <c r="B416" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>416</v>
+      </c>
+      <c r="B417" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>417</v>
+      </c>
+      <c r="B418" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>418</v>
+      </c>
+      <c r="B419" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>419</v>
+      </c>
+      <c r="B420" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>421</v>
+      </c>
+      <c r="B422" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>422</v>
+      </c>
+      <c r="B423" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>423</v>
+      </c>
+      <c r="B424" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>424</v>
+      </c>
+      <c r="B425" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>425</v>
+      </c>
+      <c r="B426" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>426</v>
+      </c>
+      <c r="B427" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>427</v>
+      </c>
+      <c r="B428" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>430</v>
+      </c>
+      <c r="B431" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>431</v>
+      </c>
+      <c r="B432" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>433</v>
+      </c>
+      <c r="B434" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>434</v>
+      </c>
+      <c r="B435" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>435</v>
+      </c>
+      <c r="B436" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>436</v>
+      </c>
+      <c r="B437" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>437</v>
+      </c>
+      <c r="B438" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>438</v>
+      </c>
+      <c r="B439" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>439</v>
+      </c>
+      <c r="B440" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>440</v>
+      </c>
+      <c r="B441" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>441</v>
+      </c>
+      <c r="B442" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>442</v>
+      </c>
+      <c r="B443" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>443</v>
+      </c>
+      <c r="B444" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>444</v>
+      </c>
+      <c r="B445" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>445</v>
+      </c>
+      <c r="B446" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>446</v>
+      </c>
+      <c r="B447" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>447</v>
+      </c>
+      <c r="B448" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>448</v>
+      </c>
+      <c r="B449" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>449</v>
+      </c>
+      <c r="B450" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>450</v>
+      </c>
+      <c r="B451" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>451</v>
+      </c>
+      <c r="B452" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>452</v>
+      </c>
+      <c r="B453" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>41054898</v>
+      </c>
+      <c r="B454" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>41054263</v>
+      </c>
+      <c r="B455" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>37741781</v>
+      </c>
+      <c r="B456" t="s">
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/asistentes.xlsx
+++ b/asistentes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="907">
   <si>
     <t>DNI</t>
   </si>
@@ -2737,6 +2737,9 @@
   </si>
   <si>
     <t>BERNAL BLANCO PAULA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ZAMBRANO CASTRO ANGELO LEONELO</t>
   </si>
 </sst>
 </file>
@@ -3054,7 +3057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -6709,6 +6712,14 @@
         <v>641</v>
       </c>
     </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>37298216</v>
+      </c>
+      <c r="B457" t="s">
+        <v>906</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
